--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="902" count="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="903" count="903">
   <si>
     <t>XC001</t>
   </si>
@@ -2734,6 +2734,9 @@
   </si>
   <si>
     <t>13957391917   18962500118   温州商区13幢1号</t>
+  </si>
+  <si>
+    <t>13957391917   18962500118   温州路99号</t>
   </si>
 </sst>
 </file>
@@ -3285,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N325"/>
+  <dimension ref="A1:O325"/>
   <sheetFormatPr defaultRowHeight="13.5" defaultColWidth="10"/>
   <cols>
     <col min="1" max="9" customWidth="0" width="9.0" style="1"/>
@@ -3363,7 +3366,7 @@
         <v>899</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" spans="8:8">
@@ -11242,7 +11245,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="13.5" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11251,7 +11254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="13.5" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="963">
   <si>
     <t>XC001</t>
   </si>
@@ -1512,9 +1512,6 @@
     <t>100*150T8 4/2斜</t>
   </si>
   <si>
-    <t>17*4*225*44</t>
-  </si>
-  <si>
     <t>100D*150T800</t>
   </si>
   <si>
@@ -1722,9 +1719,6 @@
     <t>T400横条2*1</t>
   </si>
   <si>
-    <t>16*4+30</t>
-  </si>
-  <si>
     <t>100*75*150</t>
   </si>
   <si>
@@ -1848,9 +1842,6 @@
     <t>100D半光*35S-3/3斜</t>
   </si>
   <si>
-    <t>16*4*42</t>
-  </si>
-  <si>
     <t>100*35</t>
   </si>
   <si>
@@ -1938,9 +1929,6 @@
     <t>17*4*29</t>
   </si>
   <si>
-    <t>120*T800</t>
-  </si>
-  <si>
     <t>米克380</t>
   </si>
   <si>
@@ -2401,12 +2389,6 @@
   </si>
   <si>
     <t>XC301</t>
-  </si>
-  <si>
-    <t>39梭多乐绵</t>
-  </si>
-  <si>
-    <t>16*4*39</t>
   </si>
   <si>
     <t>XC302</t>
@@ -2703,33 +2685,277 @@
     <t>网纹3/3-220</t>
   </si>
   <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">40S*35S 酷3/3斜 </t>
   </si>
   <si>
-    <t>白坯370克</t>
-  </si>
-  <si>
     <t xml:space="preserve">40S*35S 酷3/3斜  加厚 </t>
   </si>
   <si>
     <t>16*4*31</t>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+  </si>
+  <si>
+    <t>16*4+28</t>
+  </si>
+  <si>
+    <t>238克</t>
+  </si>
+  <si>
+    <t>16*4*40</t>
+  </si>
+  <si>
+    <t>120*150T800</t>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t>37梭多乐绵</t>
+  </si>
+  <si>
+    <t>16*4*37</t>
+  </si>
+  <si>
+    <t>白坯300克</t>
+  </si>
+  <si>
+    <t>16*4*44</t>
+  </si>
+  <si>
+    <t>白坯368克</t>
+  </si>
+  <si>
+    <t>XC325</t>
+  </si>
+  <si>
+    <t>XC326</t>
+  </si>
+  <si>
+    <t>XC327</t>
+  </si>
+  <si>
+    <t>XC328</t>
+  </si>
+  <si>
+    <t>XC329</t>
+  </si>
+  <si>
+    <t>XC330</t>
+  </si>
+  <si>
+    <t>XC331</t>
+  </si>
+  <si>
+    <t>XC332</t>
+  </si>
+  <si>
+    <t>XC333</t>
+  </si>
+  <si>
+    <t>XC334</t>
+  </si>
+  <si>
+    <t>XC335</t>
+  </si>
+  <si>
+    <t>XC336</t>
+  </si>
+  <si>
+    <t>XC337</t>
+  </si>
+  <si>
+    <t>XC338</t>
+  </si>
+  <si>
+    <t>XC339</t>
+  </si>
+  <si>
+    <t>XC340</t>
+  </si>
+  <si>
+    <t>XC341</t>
+  </si>
+  <si>
+    <t>XC342</t>
+  </si>
+  <si>
+    <t>XC343</t>
+  </si>
+  <si>
+    <t>XC344</t>
+  </si>
+  <si>
+    <t>XC345</t>
+  </si>
+  <si>
+    <t>XC346</t>
+  </si>
+  <si>
+    <t>XC347</t>
+  </si>
+  <si>
+    <t>XC348</t>
+  </si>
+  <si>
+    <t>XC349</t>
+  </si>
+  <si>
+    <t>XC350</t>
+  </si>
+  <si>
+    <t>XC351</t>
+  </si>
+  <si>
+    <t>XC352</t>
+  </si>
+  <si>
+    <t>XC353</t>
+  </si>
+  <si>
+    <t>XC354</t>
+  </si>
+  <si>
+    <t>XC355</t>
+  </si>
+  <si>
+    <t>XC356</t>
+  </si>
+  <si>
+    <t>XC357</t>
+  </si>
+  <si>
+    <t>XC358</t>
+  </si>
+  <si>
+    <t>XC359</t>
+  </si>
+  <si>
+    <t>XC360</t>
+  </si>
+  <si>
+    <t>XC361</t>
+  </si>
+  <si>
+    <t>XC362</t>
+  </si>
+  <si>
+    <t>XC363</t>
+  </si>
+  <si>
+    <t>XC364</t>
+  </si>
+  <si>
+    <t>XC365</t>
+  </si>
+  <si>
+    <t>XC366</t>
+  </si>
+  <si>
+    <t>XC367</t>
+  </si>
+  <si>
+    <t>XC368</t>
+  </si>
+  <si>
+    <t>XC369</t>
+  </si>
+  <si>
+    <t>XC370</t>
+  </si>
+  <si>
+    <t>XC371</t>
+  </si>
+  <si>
+    <t>XC372</t>
+  </si>
+  <si>
+    <t>XC373</t>
+  </si>
+  <si>
+    <t>XC374</t>
+  </si>
+  <si>
+    <t>XC375</t>
+  </si>
+  <si>
+    <t>XC376</t>
+  </si>
+  <si>
+    <t>XC377</t>
+  </si>
+  <si>
+    <t>XC378</t>
+  </si>
+  <si>
+    <t>XC379</t>
+  </si>
+  <si>
+    <t>XC380</t>
+  </si>
+  <si>
+    <t>XC381</t>
+  </si>
+  <si>
+    <t>XC382</t>
+  </si>
+  <si>
+    <t>XC383</t>
+  </si>
+  <si>
+    <t>XC384</t>
+  </si>
+  <si>
+    <t>XC385</t>
+  </si>
+  <si>
+    <t>XC386</t>
+  </si>
+  <si>
+    <t>XC387</t>
+  </si>
+  <si>
+    <t>XC388</t>
+  </si>
+  <si>
+    <t>XC389</t>
+  </si>
+  <si>
+    <t>XC390</t>
+  </si>
+  <si>
+    <t>XC391</t>
+  </si>
+  <si>
+    <t>XC392</t>
+  </si>
+  <si>
+    <t>XC393</t>
+  </si>
+  <si>
+    <t>XC394</t>
+  </si>
+  <si>
+    <t>XC395</t>
+  </si>
+  <si>
+    <t>XC396</t>
+  </si>
+  <si>
+    <t>XC397</t>
+  </si>
+  <si>
+    <t>XC398</t>
+  </si>
+  <si>
+    <t>XC399</t>
+  </si>
+  <si>
+    <t>XC400</t>
   </si>
 </sst>
 </file>
@@ -3835,7 +4061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M325"/>
+  <dimension ref="A1:M401"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="9" width="9" style="1"/>
@@ -3846,40 +4072,40 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>869</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -3907,13 +4133,13 @@
       </c>
       <c r="I2" s="23"/>
       <c r="J2" s="8" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5193,7 +5419,7 @@
         <v>165</v>
       </c>
       <c r="H53" s="26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I53" s="23"/>
     </row>
@@ -5972,7 +6198,7 @@
         <v>174</v>
       </c>
       <c r="H84" s="31">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="I84" s="23"/>
     </row>
@@ -7753,7 +7979,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="22">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I155" s="23"/>
     </row>
@@ -7992,7 +8218,7 @@
         <v>208</v>
       </c>
       <c r="H164" s="32">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I164" s="23"/>
     </row>
@@ -8059,7 +8285,7 @@
         <v>220</v>
       </c>
       <c r="H167" s="28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I167" s="23"/>
     </row>
@@ -8086,7 +8312,7 @@
         <v>208</v>
       </c>
       <c r="H168" s="28">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I168" s="23"/>
     </row>
@@ -8113,7 +8339,7 @@
         <v>208</v>
       </c>
       <c r="H169" s="28">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I169" s="58"/>
     </row>
@@ -8167,7 +8393,7 @@
         <v>215</v>
       </c>
       <c r="H171" s="58">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I171" s="58"/>
     </row>
@@ -8329,7 +8555,7 @@
         <v>215</v>
       </c>
       <c r="H177" s="28">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I177" s="58"/>
     </row>
@@ -8356,7 +8582,7 @@
         <v>208</v>
       </c>
       <c r="H178" s="28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I178" s="58"/>
     </row>
@@ -8383,7 +8609,7 @@
         <v>208</v>
       </c>
       <c r="H179" s="28">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I179" s="58"/>
     </row>
@@ -8410,7 +8636,7 @@
         <v>208</v>
       </c>
       <c r="H180" s="28">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I180" s="58"/>
     </row>
@@ -8599,7 +8825,7 @@
         <v>215</v>
       </c>
       <c r="H187" s="28">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I187" s="23"/>
     </row>
@@ -8653,7 +8879,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="28">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I189" s="23"/>
     </row>
@@ -8665,28 +8891,28 @@
         <v>497</v>
       </c>
       <c r="C190" s="22" t="s">
+        <v>875</v>
+      </c>
+      <c r="D190" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="D190" s="22" t="s">
-        <v>499</v>
-      </c>
       <c r="E190" s="23">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="F190" s="14">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="G190" s="23">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="H190" s="22">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I190" s="23"/>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B191" s="28" t="s">
         <v>461</v>
@@ -8713,7 +8939,7 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B192" s="37"/>
       <c r="C192" s="37"/>
@@ -8726,7 +8952,7 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B193" s="37"/>
       <c r="C193" s="37"/>
@@ -8739,10 +8965,10 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="B194" s="48" t="s">
         <v>503</v>
-      </c>
-      <c r="B194" s="48" t="s">
-        <v>504</v>
       </c>
       <c r="C194" s="49" t="s">
         <v>391</v>
@@ -8766,13 +8992,13 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B195" s="48" t="s">
         <v>505</v>
       </c>
-      <c r="B195" s="48" t="s">
+      <c r="C195" s="49" t="s">
         <v>506</v>
-      </c>
-      <c r="C195" s="49" t="s">
-        <v>507</v>
       </c>
       <c r="D195" s="50" t="s">
         <v>41</v>
@@ -8793,16 +9019,16 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="B196" s="51" t="s">
         <v>508</v>
       </c>
-      <c r="B196" s="51" t="s">
+      <c r="C196" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="C196" s="51" t="s">
+      <c r="D196" s="51" t="s">
         <v>510</v>
-      </c>
-      <c r="D196" s="51" t="s">
-        <v>511</v>
       </c>
       <c r="E196" s="51">
         <v>105</v>
@@ -8820,10 +9046,10 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="B197" s="51" t="s">
         <v>512</v>
-      </c>
-      <c r="B197" s="51" t="s">
-        <v>513</v>
       </c>
       <c r="C197" s="51" t="s">
         <v>395</v>
@@ -8841,22 +9067,22 @@
         <v>215</v>
       </c>
       <c r="H197" s="51">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I197" s="44"/>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B198" s="51" t="s">
         <v>514</v>
       </c>
-      <c r="B198" s="51" t="s">
+      <c r="C198" s="51" t="s">
         <v>515</v>
       </c>
-      <c r="C198" s="51" t="s">
+      <c r="D198" s="51" t="s">
         <v>516</v>
-      </c>
-      <c r="D198" s="51" t="s">
-        <v>517</v>
       </c>
       <c r="E198" s="51">
         <v>129</v>
@@ -8868,22 +9094,22 @@
         <v>215</v>
       </c>
       <c r="H198" s="51">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I198" s="44"/>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="B199" s="51" t="s">
         <v>518</v>
-      </c>
-      <c r="B199" s="51" t="s">
-        <v>519</v>
       </c>
       <c r="C199" s="51" t="s">
         <v>407</v>
       </c>
       <c r="D199" s="51" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E199" s="51">
         <v>95</v>
@@ -8895,13 +9121,13 @@
         <v>215</v>
       </c>
       <c r="H199" s="51">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I199" s="44"/>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B200" s="40"/>
       <c r="C200" s="40"/>
@@ -8914,7 +9140,7 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B201" s="22"/>
       <c r="C201" s="22"/>
@@ -8927,7 +9153,7 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B202" s="22"/>
       <c r="C202" s="22"/>
@@ -8940,7 +9166,7 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B203" s="22"/>
       <c r="C203" s="22"/>
@@ -8953,16 +9179,16 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="B204" s="34" t="s">
         <v>525</v>
       </c>
-      <c r="B204" s="34" t="s">
+      <c r="C204" s="34" t="s">
         <v>526</v>
       </c>
-      <c r="C204" s="34" t="s">
+      <c r="D204" s="34" t="s">
         <v>527</v>
-      </c>
-      <c r="D204" s="34" t="s">
-        <v>528</v>
       </c>
       <c r="E204" s="34"/>
       <c r="F204" s="18">
@@ -8978,16 +9204,16 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B205" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="B205" s="34" t="s">
+      <c r="C205" s="34" t="s">
         <v>530</v>
       </c>
-      <c r="C205" s="34" t="s">
+      <c r="D205" s="52" t="s">
         <v>531</v>
-      </c>
-      <c r="D205" s="52" t="s">
-        <v>532</v>
       </c>
       <c r="E205" s="34">
         <v>47</v>
@@ -9005,16 +9231,16 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="B206" s="34" t="s">
         <v>533</v>
       </c>
-      <c r="B206" s="34" t="s">
+      <c r="C206" s="34" t="s">
         <v>534</v>
       </c>
-      <c r="C206" s="34" t="s">
-        <v>535</v>
-      </c>
       <c r="D206" s="52" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E206" s="34">
         <v>47</v>
@@ -9032,10 +9258,10 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B207" s="37" t="s">
         <v>536</v>
-      </c>
-      <c r="B207" s="37" t="s">
-        <v>537</v>
       </c>
       <c r="C207" s="22" t="s">
         <v>55</v>
@@ -9055,13 +9281,13 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B208" s="37" t="s">
         <v>538</v>
       </c>
-      <c r="B208" s="37" t="s">
+      <c r="C208" s="22" t="s">
         <v>539</v>
-      </c>
-      <c r="C208" s="22" t="s">
-        <v>540</v>
       </c>
       <c r="D208" s="22" t="s">
         <v>41</v>
@@ -9082,10 +9308,10 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="B209" s="22" t="s">
         <v>541</v>
-      </c>
-      <c r="B209" s="22" t="s">
-        <v>542</v>
       </c>
       <c r="C209" s="22" t="s">
         <v>158</v>
@@ -9105,7 +9331,7 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B210" s="22"/>
       <c r="C210" s="22"/>
@@ -9118,13 +9344,13 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="B211" s="22" t="s">
         <v>544</v>
       </c>
-      <c r="B211" s="22" t="s">
+      <c r="C211" s="22" t="s">
         <v>545</v>
-      </c>
-      <c r="C211" s="22" t="s">
-        <v>546</v>
       </c>
       <c r="D211" s="22" t="s">
         <v>41</v>
@@ -9143,13 +9369,13 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="B212" s="53" t="s">
         <v>547</v>
       </c>
-      <c r="B212" s="53" t="s">
+      <c r="C212" s="53" t="s">
         <v>548</v>
-      </c>
-      <c r="C212" s="53" t="s">
-        <v>549</v>
       </c>
       <c r="D212" s="53" t="s">
         <v>149</v>
@@ -9168,16 +9394,16 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="B213" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="B213" s="22" t="s">
+      <c r="C213" s="22" t="s">
         <v>551</v>
       </c>
-      <c r="C213" s="22" t="s">
-        <v>552</v>
-      </c>
       <c r="D213" s="22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E213" s="22">
         <v>52</v>
@@ -9189,19 +9415,19 @@
         <v>178</v>
       </c>
       <c r="H213" s="22">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I213" s="44"/>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="B214" s="22" t="s">
         <v>553</v>
       </c>
-      <c r="B214" s="22" t="s">
-        <v>554</v>
-      </c>
       <c r="C214" s="53" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D214" s="53" t="s">
         <v>149</v>
@@ -9220,7 +9446,7 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B215" s="40"/>
       <c r="C215" s="40"/>
@@ -9233,16 +9459,16 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="B216" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="B216" s="22" t="s">
+      <c r="C216" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="C216" s="22" t="s">
+      <c r="D216" s="22" t="s">
         <v>558</v>
-      </c>
-      <c r="D216" s="22" t="s">
-        <v>559</v>
       </c>
       <c r="E216" s="22">
         <v>69</v>
@@ -9258,7 +9484,7 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B217" s="40"/>
       <c r="C217" s="40"/>
@@ -9271,7 +9497,7 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B218" s="22"/>
       <c r="C218" s="22"/>
@@ -9284,16 +9510,16 @@
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="B219" s="53" t="s">
         <v>562</v>
       </c>
-      <c r="B219" s="53" t="s">
+      <c r="C219" s="53" t="s">
         <v>563</v>
       </c>
-      <c r="C219" s="53" t="s">
+      <c r="D219" s="53" t="s">
         <v>564</v>
-      </c>
-      <c r="D219" s="53" t="s">
-        <v>565</v>
       </c>
       <c r="E219" s="53">
         <v>90</v>
@@ -9311,22 +9537,22 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="B220" s="22" t="s">
         <v>566</v>
       </c>
-      <c r="B220" s="22" t="s">
+      <c r="C220" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="D220" s="39" t="s">
         <v>567</v>
       </c>
-      <c r="C220" s="22" t="s">
-        <v>568</v>
-      </c>
-      <c r="D220" s="39" t="s">
-        <v>569</v>
-      </c>
       <c r="E220" s="22">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F220" s="12">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G220" s="23">
         <v>215</v>
@@ -9334,17 +9560,19 @@
       <c r="H220" s="22">
         <v>3.5</v>
       </c>
-      <c r="I220" s="23"/>
+      <c r="I220" s="23" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="B221" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="C221" s="22" t="s">
         <v>570</v>
-      </c>
-      <c r="B221" s="22" t="s">
-        <v>571</v>
-      </c>
-      <c r="C221" s="22" t="s">
-        <v>572</v>
       </c>
       <c r="D221" s="39" t="s">
         <v>3</v>
@@ -9362,21 +9590,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="44" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="B222" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="C222" s="22" t="s">
         <v>574</v>
       </c>
-      <c r="B222" s="22" t="s">
-        <v>575</v>
-      </c>
-      <c r="C222" s="22" t="s">
-        <v>576</v>
-      </c>
       <c r="D222" s="39" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E222" s="22">
         <v>115</v>
@@ -9394,13 +9622,13 @@
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="B223" s="53" t="s">
+        <v>576</v>
+      </c>
+      <c r="C223" s="53" t="s">
         <v>577</v>
-      </c>
-      <c r="B223" s="53" t="s">
-        <v>578</v>
-      </c>
-      <c r="C223" s="53" t="s">
-        <v>579</v>
       </c>
       <c r="D223" s="45" t="s">
         <v>3</v>
@@ -9421,16 +9649,16 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="B224" s="53" t="s">
+        <v>579</v>
+      </c>
+      <c r="C224" s="53" t="s">
         <v>580</v>
       </c>
-      <c r="B224" s="53" t="s">
+      <c r="D224" s="53" t="s">
         <v>581</v>
-      </c>
-      <c r="C224" s="53" t="s">
-        <v>582</v>
-      </c>
-      <c r="D224" s="53" t="s">
-        <v>583</v>
       </c>
       <c r="E224" s="53">
         <v>120</v>
@@ -9448,13 +9676,13 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B225" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="C225" s="53" t="s">
         <v>584</v>
-      </c>
-      <c r="B225" s="37" t="s">
-        <v>585</v>
-      </c>
-      <c r="C225" s="53" t="s">
-        <v>586</v>
       </c>
       <c r="D225" s="53" t="s">
         <v>456</v>
@@ -9469,16 +9697,16 @@
         <v>215</v>
       </c>
       <c r="H225" s="53">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I225" s="23"/>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="12" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B226" s="53" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C226" s="53" t="s">
         <v>243</v>
@@ -9496,16 +9724,16 @@
         <v>215</v>
       </c>
       <c r="H226" s="53">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I226" s="44"/>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" s="12" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B227" s="53" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C227" s="53" t="s">
         <v>243</v>
@@ -9523,16 +9751,16 @@
         <v>215</v>
       </c>
       <c r="H227" s="53">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I227" s="44"/>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" s="12" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B228" s="53" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C228" s="53" t="s">
         <v>466</v>
@@ -9550,16 +9778,16 @@
         <v>215</v>
       </c>
       <c r="H228" s="53">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I228" s="23"/>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B229" s="53" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C229" s="53" t="s">
         <v>466</v>
@@ -9577,16 +9805,16 @@
         <v>215</v>
       </c>
       <c r="H229" s="53">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I229" s="23"/>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="12" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B230" s="41" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C230" s="41" t="s">
         <v>484</v>
@@ -9604,13 +9832,13 @@
         <v>215</v>
       </c>
       <c r="H230" s="41">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I230" s="23"/>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B231" s="28"/>
       <c r="C231" s="28"/>
@@ -9623,7 +9851,7 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="12" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B232" s="53"/>
       <c r="C232" s="53"/>
@@ -9636,16 +9864,16 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B233" s="53" t="s">
+        <v>598</v>
+      </c>
+      <c r="C233" s="53" t="s">
         <v>599</v>
       </c>
-      <c r="B233" s="53" t="s">
+      <c r="D233" s="53" t="s">
         <v>600</v>
-      </c>
-      <c r="C233" s="53" t="s">
-        <v>601</v>
-      </c>
-      <c r="D233" s="53" t="s">
-        <v>602</v>
       </c>
       <c r="E233" s="53"/>
       <c r="F233" s="17"/>
@@ -9659,16 +9887,16 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="C234" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="B234" s="17" t="s">
+      <c r="D234" s="45" t="s">
         <v>604</v>
-      </c>
-      <c r="C234" s="17" t="s">
-        <v>605</v>
-      </c>
-      <c r="D234" s="45" t="s">
-        <v>606</v>
       </c>
       <c r="E234" s="17">
         <v>190</v>
@@ -9680,24 +9908,24 @@
         <v>215</v>
       </c>
       <c r="H234" s="17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I234" s="55" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B235" s="41" t="s">
+        <v>607</v>
+      </c>
+      <c r="C235" s="41" t="s">
+        <v>878</v>
+      </c>
+      <c r="D235" s="41" t="s">
         <v>608</v>
-      </c>
-      <c r="B235" s="41" t="s">
-        <v>609</v>
-      </c>
-      <c r="C235" s="41" t="s">
-        <v>610</v>
-      </c>
-      <c r="D235" s="41" t="s">
-        <v>611</v>
       </c>
       <c r="E235" s="41">
         <v>155</v>
@@ -9706,27 +9934,27 @@
         <v>230</v>
       </c>
       <c r="G235" s="54">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H235" s="41">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I235" s="54" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" s="12" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B236" s="41" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C236" s="41" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="D236" s="41" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E236" s="41">
         <v>170</v>
@@ -9741,21 +9969,21 @@
         <v>5</v>
       </c>
       <c r="I236" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B237" s="41" t="s">
+        <v>614</v>
+      </c>
+      <c r="C237" s="41" t="s">
+        <v>615</v>
+      </c>
+      <c r="D237" s="41" t="s">
         <v>616</v>
-      </c>
-      <c r="B237" s="41" t="s">
-        <v>617</v>
-      </c>
-      <c r="C237" s="41" t="s">
-        <v>618</v>
-      </c>
-      <c r="D237" s="41" t="s">
-        <v>619</v>
       </c>
       <c r="E237" s="41">
         <v>155</v>
@@ -9770,12 +9998,12 @@
         <v>4.8</v>
       </c>
       <c r="I237" s="54" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="12" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
@@ -9788,16 +10016,16 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="12" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B239" s="41" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C239" s="41" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D239" s="41" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E239" s="17">
         <v>180</v>
@@ -9812,21 +10040,21 @@
         <v>5.5</v>
       </c>
       <c r="I239" s="55" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B240" s="41" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C240" s="41" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D240" s="41" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E240" s="17">
         <v>190</v>
@@ -9841,21 +10069,21 @@
         <v>5.7</v>
       </c>
       <c r="I240" s="55" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B241" s="41" t="s">
+        <v>627</v>
+      </c>
+      <c r="C241" s="41" t="s">
+        <v>628</v>
+      </c>
+      <c r="D241" s="23" t="s">
         <v>629</v>
-      </c>
-      <c r="B241" s="41" t="s">
-        <v>630</v>
-      </c>
-      <c r="C241" s="41" t="s">
-        <v>631</v>
-      </c>
-      <c r="D241" s="23" t="s">
-        <v>632</v>
       </c>
       <c r="E241" s="41">
         <v>150</v>
@@ -9870,21 +10098,21 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="54" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="12" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B242" s="41" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C242" s="41" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D242" s="41" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E242" s="17">
         <v>160</v>
@@ -9899,21 +10127,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" s="12" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B243" s="41" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C243" s="41" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D243" s="41" t="s">
-        <v>640</v>
+        <v>879</v>
       </c>
       <c r="E243" s="17">
         <v>190</v>
@@ -9925,28 +10153,40 @@
         <v>220</v>
       </c>
       <c r="H243" s="53">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I243" s="55" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="B244" s="9"/>
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
+        <v>638</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="C244" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D244" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="E244" s="9">
+        <v>150</v>
+      </c>
       <c r="F244" s="9"/>
-      <c r="G244" s="9"/>
-      <c r="H244" s="9"/>
+      <c r="G244" s="9">
+        <v>220</v>
+      </c>
+      <c r="H244" s="9">
+        <v>3.9</v>
+      </c>
       <c r="I244" s="55"/>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="12" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
@@ -9959,13 +10199,13 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" s="12" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B246" s="28" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C246" s="28" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D246" s="59" t="s">
         <v>445</v>
@@ -9986,13 +10226,13 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" s="57" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B247" s="28" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C247" s="28" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D247" s="59" t="s">
         <v>456</v>
@@ -10013,13 +10253,13 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="57" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B248" s="28" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C248" s="28" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D248" s="28" t="s">
         <v>456</v>
@@ -10040,10 +10280,10 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="57" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B249" s="28" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C249" s="28" t="s">
         <v>459</v>
@@ -10067,10 +10307,10 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="57" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B250" s="28" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C250" s="28" t="s">
         <v>158</v>
@@ -10085,7 +10325,7 @@
         <v>150</v>
       </c>
       <c r="G250" s="58">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H250" s="58">
         <v>3.4</v>
@@ -10094,13 +10334,13 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" s="57" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B251" s="28" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D251" s="28" t="s">
         <v>445</v>
@@ -10115,16 +10355,16 @@
         <v>215</v>
       </c>
       <c r="H251" s="28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I251" s="58"/>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" s="57" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B252" s="28" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C252" s="28" t="s">
         <v>459</v>
@@ -10148,13 +10388,13 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" s="57" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B253" s="28" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C253" s="28" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D253" s="28" t="s">
         <v>445</v>
@@ -10169,28 +10409,28 @@
         <v>215</v>
       </c>
       <c r="H253" s="28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I253" s="58"/>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" s="57" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B254" s="28" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D254" s="28" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E254" s="28">
         <v>190</v>
       </c>
       <c r="F254" s="57">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G254" s="58">
         <v>215</v>
@@ -10199,18 +10439,18 @@
         <v>5.5</v>
       </c>
       <c r="I254" s="55" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" s="57" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B255" s="28" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C255" s="28" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D255" s="28" t="s">
         <v>445</v>
@@ -10225,28 +10465,28 @@
         <v>208</v>
       </c>
       <c r="H255" s="63">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I255" s="55"/>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="12" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C256" s="28" t="s">
         <v>339</v>
       </c>
       <c r="D256" s="45" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E256" s="17">
         <v>185</v>
       </c>
       <c r="F256" s="17">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G256" s="19">
         <v>215</v>
@@ -10255,15 +10495,15 @@
         <v>5.3</v>
       </c>
       <c r="I256" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" s="12" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C257" s="17" t="s">
         <v>326</v>
@@ -10287,20 +10527,34 @@
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="12" t="s">
-        <v>673</v>
-      </c>
-      <c r="B258" s="17"/>
-      <c r="C258" s="17"/>
-      <c r="D258" s="17"/>
-      <c r="E258" s="17"/>
-      <c r="F258" s="17"/>
-      <c r="G258" s="17"/>
-      <c r="H258" s="11"/>
+        <v>669</v>
+      </c>
+      <c r="B258" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="C258" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D258" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="E258" s="17">
+        <v>108</v>
+      </c>
+      <c r="F258" s="17">
+        <v>160</v>
+      </c>
+      <c r="G258" s="17">
+        <v>215</v>
+      </c>
+      <c r="H258" s="11">
+        <v>3.6</v>
+      </c>
       <c r="I258" s="11"/>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="12" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
@@ -10313,7 +10567,7 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="12" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
@@ -10326,16 +10580,16 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="12" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B261" s="22" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C261" s="22" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D261" s="39" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E261" s="22">
         <v>108</v>
@@ -10353,16 +10607,16 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="12" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B262" s="22" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C262" s="22" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D262" s="39" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E262" s="22">
         <v>87</v>
@@ -10380,16 +10634,16 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="12" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B263" s="37" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C263" s="37" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D263" s="37" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E263" s="37">
         <v>115</v>
@@ -10401,22 +10655,22 @@
         <v>208</v>
       </c>
       <c r="H263" s="37">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I263" s="11"/>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="12" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B264" s="22" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C264" s="22" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="E264" s="22">
         <v>70</v>
@@ -10434,16 +10688,16 @@
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="12" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B265" s="53" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C265" s="53" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D265" s="53" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E265" s="53">
         <v>102</v>
@@ -10461,16 +10715,16 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="12" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B266" s="53" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C266" s="53" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D266" s="53" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E266" s="53">
         <v>78</v>
@@ -10482,19 +10736,19 @@
         <v>215</v>
       </c>
       <c r="H266" s="53">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I266" s="11"/>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="12" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B267" s="22" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C267" s="22" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D267" s="39" t="s">
         <v>149</v>
@@ -10515,7 +10769,7 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="12" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
@@ -10528,7 +10782,7 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="12" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
@@ -10541,7 +10795,7 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="12" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
@@ -10554,7 +10808,7 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="12" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
@@ -10567,7 +10821,7 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="12" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
@@ -10580,7 +10834,7 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="12" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
@@ -10593,7 +10847,7 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="12" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
@@ -10606,7 +10860,7 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="12" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
@@ -10619,7 +10873,7 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="12" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
@@ -10632,16 +10886,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="12" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B277" s="17" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C277" s="17" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D277" s="17" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="E277" s="17">
         <v>105</v>
@@ -10659,16 +10913,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="12" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B278" s="37" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D278" s="37" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E278" s="37">
         <v>159</v>
@@ -10686,13 +10940,13 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B279" s="22" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C279" s="39" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D279" s="22" t="s">
         <v>149</v>
@@ -10713,16 +10967,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="12" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B280" s="22" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C280" s="39" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E280" s="22"/>
       <c r="F280" s="12">
@@ -10738,13 +10992,13 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="12" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B281" s="22" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C281" s="39" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D281" s="22" t="s">
         <v>149</v>
@@ -10765,13 +11019,13 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="12" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B282" s="22" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C282" s="39" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D282" s="22" t="s">
         <v>41</v>
@@ -10786,19 +11040,19 @@
         <v>215</v>
       </c>
       <c r="H282" s="22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I282" s="11"/>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="12" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B283" s="22" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C283" s="39" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D283" s="22" t="s">
         <v>41</v>
@@ -10819,16 +11073,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="12" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B284" s="37" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C284" s="17" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D284" s="17" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E284" s="17">
         <v>80</v>
@@ -10840,22 +11094,22 @@
         <v>208</v>
       </c>
       <c r="H284" s="11">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I284" s="11"/>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="12" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B285" s="22" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C285" s="39" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D285" s="17" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E285" s="22">
         <v>73</v>
@@ -10867,22 +11121,22 @@
         <v>208</v>
       </c>
       <c r="H285" s="22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I285" s="11"/>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="12" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B286" s="17" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C286" s="17" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="D286" s="17" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E286" s="17">
         <v>85</v>
@@ -10900,16 +11154,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="12" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B287" s="17" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C287" s="17" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D287" s="17" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E287" s="17">
         <v>88</v>
@@ -10921,19 +11175,19 @@
         <v>218</v>
       </c>
       <c r="H287" s="17">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I287" s="10"/>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="12" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B288" s="37" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C288" s="37" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D288" s="45" t="s">
         <v>3</v>
@@ -10954,16 +11208,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="12" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B289" s="22" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C289" s="22" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D289" s="39" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E289" s="22">
         <v>135</v>
@@ -10975,21 +11229,21 @@
         <v>215</v>
       </c>
       <c r="H289" s="22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I289" s="23" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" s="12" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B290" s="34" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C290" s="34" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D290" s="56" t="s">
         <v>41</v>
@@ -11010,16 +11264,16 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="12" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B291" s="43" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C291" s="43" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D291" s="43" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E291" s="43">
         <v>88</v>
@@ -11031,22 +11285,22 @@
         <v>220</v>
       </c>
       <c r="H291" s="43">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I291" s="10"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="12" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B292" s="43" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C292" s="43" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D292" s="43" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E292" s="43">
         <v>80</v>
@@ -11064,13 +11318,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="12" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B293" s="18" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C293" s="43" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D293" s="43" t="s">
         <v>41</v>
@@ -11091,16 +11345,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="12" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B294" s="28" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C294" s="28" t="s">
         <v>466</v>
       </c>
       <c r="D294" s="28" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E294" s="28">
         <v>150</v>
@@ -11112,22 +11366,22 @@
         <v>215</v>
       </c>
       <c r="H294" s="28">
-        <v>5.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="I294" s="10"/>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="12" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B295" s="22" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C295" s="22" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E295" s="22"/>
       <c r="F295" s="12"/>
@@ -11141,16 +11395,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="12" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B296" s="53" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C296" s="53" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="D296" s="53" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E296" s="53"/>
       <c r="F296" s="17">
@@ -11166,16 +11420,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="12" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B297" s="28" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C297" s="28" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D297" s="59" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E297" s="28">
         <v>125</v>
@@ -11193,7 +11447,7 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="12" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B298" s="18"/>
       <c r="C298" s="43"/>
@@ -11206,16 +11460,16 @@
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="12" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B299" s="41" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C299" s="41" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="D299" s="41" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E299" s="41">
         <v>124</v>
@@ -11230,12 +11484,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="54" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="12" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
@@ -11248,7 +11502,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="12" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
@@ -11261,16 +11515,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="12" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>795</v>
+        <v>882</v>
       </c>
       <c r="C302" s="23" t="s">
-        <v>796</v>
+        <v>883</v>
       </c>
       <c r="D302" s="23" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E302" s="23">
         <v>150</v>
@@ -11288,16 +11542,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="12" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B303" s="22" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="C303" s="22" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="E303" s="23">
         <v>140</v>
@@ -11315,16 +11569,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="12" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B304" s="43" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C304" s="43" t="s">
         <v>256</v>
       </c>
       <c r="D304" s="43" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="E304" s="43">
         <v>90</v>
@@ -11339,21 +11593,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="44" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="12" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B305" s="17" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="C305" s="17" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="D305" s="28" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="E305" s="17">
         <v>215</v>
@@ -11371,7 +11625,7 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="12" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
@@ -11384,7 +11638,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="12" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
@@ -11397,7 +11651,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="12" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
@@ -11410,7 +11664,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="12" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
@@ -11423,7 +11677,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="12" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
@@ -11436,16 +11690,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="12" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="B311" s="53" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="C311" s="53" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D311" s="53" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="E311" s="53">
         <v>85</v>
@@ -11457,22 +11711,22 @@
         <v>215</v>
       </c>
       <c r="H311" s="53">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I311" s="10"/>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="12" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="B312" s="22" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="C312" s="22" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="E312" s="22">
         <v>73</v>
@@ -11490,7 +11744,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="12" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
@@ -11503,7 +11757,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="12" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
@@ -11516,16 +11770,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="12" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B315" s="17" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C315" s="17" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="D315" s="23" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="E315" s="17">
         <v>116</v>
@@ -11537,24 +11791,24 @@
         <v>225</v>
       </c>
       <c r="H315" s="10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I315" s="10" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="12" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B316" s="17" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="D316" s="23" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="E316" s="17">
         <v>160</v>
@@ -11569,21 +11823,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="10" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="12" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="B317" s="23" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C317" s="23" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="D317" s="23" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="E317" s="23">
         <v>110</v>
@@ -11598,21 +11852,21 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="23" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="12" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="B318" s="23" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C318" s="23" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="D318" s="23" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="E318" s="23">
         <v>110</v>
@@ -11624,22 +11878,22 @@
         <v>208</v>
       </c>
       <c r="H318" s="23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I318" s="23"/>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="12" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="B319" s="28" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C319" s="28" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="D319" s="28" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="E319" s="28">
         <v>205</v>
@@ -11654,27 +11908,27 @@
         <v>5.5</v>
       </c>
       <c r="I319" s="23" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="12" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="B320" s="28" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C320" s="28" t="s">
-        <v>623</v>
+        <v>885</v>
       </c>
       <c r="D320" s="28" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E320" s="28">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F320" s="57">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G320" s="58">
         <v>218</v>
@@ -11683,21 +11937,21 @@
         <v>6</v>
       </c>
       <c r="I320" s="23" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="12" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="B321" s="28" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C321" s="28" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="D321" s="28" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E321" s="28">
         <v>138</v>
@@ -11712,21 +11966,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="23" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="12" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="B322" s="28" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="C322" s="28" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D322" s="28" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="E322" s="28">
         <v>225</v>
@@ -11741,21 +11995,21 @@
         <v>6</v>
       </c>
       <c r="I322" s="23" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="12" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="B323" s="28" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C323" s="28" t="s">
         <v>92</v>
       </c>
       <c r="D323" s="28" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E323" s="28">
         <v>155</v>
@@ -11770,21 +12024,21 @@
         <v>4.8</v>
       </c>
       <c r="I323" s="23" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="B324" s="28" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C324" s="28" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="D324" s="28" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="E324" s="28">
         <v>220</v>
@@ -11799,12 +12053,12 @@
         <v>6.2</v>
       </c>
       <c r="I324" s="23" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="12" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
@@ -11814,6 +12068,386 @@
       <c r="G325" s="17"/>
       <c r="H325" s="10"/>
       <c r="I325" s="10"/>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326" s="1" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328" s="1" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329" s="1" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331" s="1" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333" s="1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334" s="1" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335" s="1" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="1" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="1" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="1" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="1" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="1" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="1" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="1" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="1" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="1" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="1" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="1" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="1" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="1" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="1" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="1" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="1" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="1" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="1" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="1" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="1" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="1" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="1" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="1" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="1" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="1" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="1" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="1" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="1" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="1" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="1" t="s">
+        <v>962</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="957">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2181,1073 +2181,773 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>XC325</t>
+  </si>
+  <si>
+    <t>XC326</t>
+  </si>
+  <si>
+    <t>XC327</t>
+  </si>
+  <si>
+    <t>XC328</t>
+  </si>
+  <si>
+    <t>XC329</t>
+  </si>
+  <si>
+    <t>XC330</t>
+  </si>
+  <si>
+    <t>XC331</t>
+  </si>
+  <si>
+    <t>XC332</t>
+  </si>
+  <si>
+    <t>XC333</t>
+  </si>
+  <si>
+    <t>XC334</t>
+  </si>
+  <si>
+    <t>XC335</t>
+  </si>
+  <si>
+    <t>XC336</t>
+  </si>
+  <si>
+    <t>XC337</t>
+  </si>
+  <si>
+    <t>XC338</t>
+  </si>
+  <si>
+    <t>XC339</t>
+  </si>
+  <si>
+    <t>XC340</t>
+  </si>
+  <si>
+    <t>XC341</t>
+  </si>
+  <si>
+    <t>XC342</t>
+  </si>
+  <si>
+    <t>XC343</t>
+  </si>
+  <si>
+    <t>XC344</t>
+  </si>
+  <si>
+    <t>XC345</t>
+  </si>
+  <si>
+    <t>XC346</t>
+  </si>
+  <si>
+    <t>XC347</t>
+  </si>
+  <si>
+    <t>XC348</t>
+  </si>
+  <si>
+    <t>XC349</t>
+  </si>
+  <si>
+    <t>XC350</t>
+  </si>
+  <si>
+    <t>XC351</t>
+  </si>
+  <si>
+    <t>XC352</t>
+  </si>
+  <si>
+    <t>XC353</t>
+  </si>
+  <si>
+    <t>XC354</t>
+  </si>
+  <si>
+    <t>XC355</t>
+  </si>
+  <si>
+    <t>XC356</t>
+  </si>
+  <si>
+    <t>XC357</t>
+  </si>
+  <si>
+    <t>XC358</t>
+  </si>
+  <si>
+    <t>XC359</t>
+  </si>
+  <si>
+    <t>XC360</t>
+  </si>
+  <si>
+    <t>XC361</t>
+  </si>
+  <si>
+    <t>XC362</t>
+  </si>
+  <si>
+    <t>XC363</t>
+  </si>
+  <si>
+    <t>XC364</t>
+  </si>
+  <si>
+    <t>XC365</t>
+  </si>
+  <si>
+    <t>XC366</t>
+  </si>
+  <si>
+    <t>XC367</t>
+  </si>
+  <si>
+    <t>XC368</t>
+  </si>
+  <si>
+    <t>XC369</t>
+  </si>
+  <si>
+    <t>XC370</t>
+  </si>
+  <si>
+    <t>XC371</t>
+  </si>
+  <si>
+    <t>XC372</t>
+  </si>
+  <si>
+    <t>XC373</t>
+  </si>
+  <si>
+    <t>XC374</t>
+  </si>
+  <si>
+    <t>XC375</t>
+  </si>
+  <si>
+    <t>XC376</t>
+  </si>
+  <si>
+    <t>XC377</t>
+  </si>
+  <si>
+    <t>XC378</t>
+  </si>
+  <si>
+    <t>XC379</t>
+  </si>
+  <si>
+    <t>XC380</t>
+  </si>
+  <si>
+    <t>XC381</t>
+  </si>
+  <si>
+    <t>XC382</t>
+  </si>
+  <si>
+    <t>XC383</t>
+  </si>
+  <si>
+    <t>XC384</t>
+  </si>
+  <si>
+    <t>XC385</t>
+  </si>
+  <si>
+    <t>XC386</t>
+  </si>
+  <si>
+    <t>XC387</t>
+  </si>
+  <si>
+    <t>XC388</t>
+  </si>
+  <si>
+    <t>XC389</t>
+  </si>
+  <si>
+    <t>XC390</t>
+  </si>
+  <si>
+    <t>XC391</t>
+  </si>
+  <si>
+    <t>XC392</t>
+  </si>
+  <si>
     <t>XC001</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
+  </si>
+  <si>
+    <t>17*4*44</t>
+  </si>
+  <si>
+    <t>120*35S</t>
+  </si>
+  <si>
+    <t>米克370</t>
   </si>
   <si>
     <t>120D扁平3/3斜-45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克370</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*2T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克368</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵细双斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>30*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
   </si>
   <si>
     <t>天丝棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*35S 酷3/3斜 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态棉</t>
   </si>
   <si>
     <t>16*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*35S 酷3/3斜  加厚 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">生态棉 加厚 </t>
   </si>
   <si>
     <t>16*4*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC325</t>
-  </si>
-  <si>
-    <t>XC326</t>
-  </si>
-  <si>
-    <t>XC327</t>
-  </si>
-  <si>
-    <t>XC328</t>
-  </si>
-  <si>
-    <t>XC329</t>
-  </si>
-  <si>
-    <t>XC330</t>
-  </si>
-  <si>
-    <t>XC331</t>
-  </si>
-  <si>
-    <t>XC332</t>
-  </si>
-  <si>
-    <t>XC333</t>
-  </si>
-  <si>
-    <t>XC334</t>
-  </si>
-  <si>
-    <t>XC335</t>
-  </si>
-  <si>
-    <t>XC336</t>
-  </si>
-  <si>
-    <t>XC337</t>
-  </si>
-  <si>
-    <t>XC338</t>
-  </si>
-  <si>
-    <t>XC339</t>
-  </si>
-  <si>
-    <t>XC340</t>
-  </si>
-  <si>
-    <t>XC341</t>
-  </si>
-  <si>
-    <t>XC342</t>
-  </si>
-  <si>
-    <t>XC343</t>
-  </si>
-  <si>
-    <t>XC344</t>
-  </si>
-  <si>
-    <t>XC345</t>
-  </si>
-  <si>
-    <t>XC346</t>
-  </si>
-  <si>
-    <t>XC347</t>
-  </si>
-  <si>
-    <t>XC348</t>
-  </si>
-  <si>
-    <t>XC349</t>
-  </si>
-  <si>
-    <t>XC350</t>
-  </si>
-  <si>
-    <t>XC351</t>
-  </si>
-  <si>
-    <t>XC352</t>
-  </si>
-  <si>
-    <t>XC353</t>
-  </si>
-  <si>
-    <t>XC354</t>
-  </si>
-  <si>
-    <t>XC355</t>
-  </si>
-  <si>
-    <t>XC356</t>
-  </si>
-  <si>
-    <t>XC357</t>
-  </si>
-  <si>
-    <t>XC358</t>
-  </si>
-  <si>
-    <t>XC359</t>
-  </si>
-  <si>
-    <t>XC360</t>
-  </si>
-  <si>
-    <t>XC361</t>
-  </si>
-  <si>
-    <t>XC362</t>
-  </si>
-  <si>
-    <t>XC363</t>
-  </si>
-  <si>
-    <t>XC364</t>
-  </si>
-  <si>
-    <t>XC365</t>
-  </si>
-  <si>
-    <t>XC366</t>
-  </si>
-  <si>
-    <t>XC367</t>
-  </si>
-  <si>
-    <t>XC368</t>
-  </si>
-  <si>
-    <t>XC369</t>
-  </si>
-  <si>
-    <t>XC370</t>
-  </si>
-  <si>
-    <t>XC371</t>
-  </si>
-  <si>
-    <t>XC372</t>
-  </si>
-  <si>
-    <t>XC373</t>
-  </si>
-  <si>
-    <t>XC374</t>
-  </si>
-  <si>
-    <t>XC375</t>
-  </si>
-  <si>
-    <t>XC376</t>
-  </si>
-  <si>
-    <t>XC377</t>
-  </si>
-  <si>
-    <t>XC378</t>
-  </si>
-  <si>
-    <t>XC379</t>
-  </si>
-  <si>
-    <t>XC380</t>
-  </si>
-  <si>
-    <t>XC381</t>
-  </si>
-  <si>
-    <t>XC382</t>
-  </si>
-  <si>
-    <t>XC383</t>
-  </si>
-  <si>
-    <t>XC384</t>
-  </si>
-  <si>
-    <t>XC385</t>
-  </si>
-  <si>
-    <t>XC386</t>
-  </si>
-  <si>
-    <t>XC387</t>
-  </si>
-  <si>
-    <t>XC388</t>
-  </si>
-  <si>
-    <t>XC389</t>
-  </si>
-  <si>
-    <t>XC390</t>
-  </si>
-  <si>
-    <t>XC391</t>
-  </si>
-  <si>
-    <t>XC392</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -3345,13 +3045,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="18">
@@ -4416,16 +4109,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="13" t="s">
-        <v>703</v>
+        <v>771</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>704</v>
+        <v>772</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>705</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14">
         <v>79</v>
@@ -5112,7 +4805,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>706</v>
+        <v>773</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>46</v>
@@ -5137,7 +4830,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>707</v>
+        <v>774</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>46</v>
@@ -5789,7 +5482,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>135</v>
@@ -6316,7 +6009,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>709</v>
+        <v>73</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>144</v>
@@ -7666,7 +7359,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>710</v>
+        <v>776</v>
       </c>
       <c r="D131" s="28" t="s">
         <v>148</v>
@@ -8204,7 +7897,7 @@
         <v>208</v>
       </c>
       <c r="H152" s="17">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I152" s="15"/>
     </row>
@@ -8425,7 +8118,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="26" t="s">
-        <v>711</v>
+        <v>777</v>
       </c>
       <c r="C161" s="26" t="s">
         <v>413</v>
@@ -8506,7 +8199,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="26" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
       <c r="C164" s="26" t="s">
         <v>422</v>
@@ -8533,10 +8226,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="26" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
       <c r="C165" s="26" t="s">
-        <v>714</v>
+        <v>780</v>
       </c>
       <c r="D165" s="26" t="s">
         <v>414</v>
@@ -8573,13 +8266,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>715</v>
+        <v>781</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>716</v>
+        <v>782</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>717</v>
+        <v>783</v>
       </c>
       <c r="E167" s="22">
         <v>80</v>
@@ -8591,7 +8284,7 @@
         <v>220</v>
       </c>
       <c r="H167" s="22">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I167" s="15"/>
     </row>
@@ -8600,13 +8293,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>718</v>
+        <v>784</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>719</v>
+        <v>417</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>720</v>
+        <v>785</v>
       </c>
       <c r="E168" s="22">
         <v>110</v>
@@ -8618,7 +8311,7 @@
         <v>208</v>
       </c>
       <c r="H168" s="22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I168" s="15"/>
     </row>
@@ -8627,7 +8320,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>721</v>
+        <v>786</v>
       </c>
       <c r="C169" s="22" t="s">
         <v>428</v>
@@ -8654,7 +8347,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>722</v>
+        <v>787</v>
       </c>
       <c r="C170" s="22" t="s">
         <v>431</v>
@@ -8681,7 +8374,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>723</v>
+        <v>788</v>
       </c>
       <c r="C171" s="22" t="s">
         <v>238</v>
@@ -8735,7 +8428,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>724</v>
+        <v>789</v>
       </c>
       <c r="C173" s="22" t="s">
         <v>436</v>
@@ -8762,7 +8455,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>725</v>
+        <v>790</v>
       </c>
       <c r="C174" s="22" t="s">
         <v>439</v>
@@ -8789,7 +8482,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>32</v>
@@ -8870,7 +8563,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>727</v>
+        <v>792</v>
       </c>
       <c r="C178" s="22" t="s">
         <v>420</v>
@@ -8924,7 +8617,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>728</v>
+        <v>793</v>
       </c>
       <c r="C180" s="22" t="s">
         <v>451</v>
@@ -8951,7 +8644,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>729</v>
+        <v>794</v>
       </c>
       <c r="C181" s="22" t="s">
         <v>445</v>
@@ -8978,7 +8671,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="38" t="s">
-        <v>730</v>
+        <v>795</v>
       </c>
       <c r="C182" s="38" t="s">
         <v>309</v>
@@ -9005,7 +8698,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="38" t="s">
-        <v>731</v>
+        <v>796</v>
       </c>
       <c r="C183" s="38" t="s">
         <v>309</v>
@@ -9059,13 +8752,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>732</v>
+        <v>797</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>733</v>
+        <v>445</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>734</v>
+        <v>429</v>
       </c>
       <c r="E185" s="22">
         <v>112</v>
@@ -9086,7 +8779,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="38" t="s">
-        <v>735</v>
+        <v>798</v>
       </c>
       <c r="C186" s="38" t="s">
         <v>309</v>
@@ -9110,13 +8803,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="13" t="s">
-        <v>736</v>
+        <v>799</v>
       </c>
       <c r="B187" s="22" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D187" s="22" t="s">
         <v>437</v>
@@ -9140,13 +8833,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>738</v>
+        <v>800</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>739</v>
+        <v>272</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>740</v>
+        <v>801</v>
       </c>
       <c r="E188" s="22">
         <v>110</v>
@@ -9167,7 +8860,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>741</v>
+        <v>802</v>
       </c>
       <c r="C189" s="22" t="s">
         <v>445</v>
@@ -9185,7 +8878,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="22">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I189" s="15"/>
     </row>
@@ -9194,13 +8887,13 @@
         <v>464</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>742</v>
+        <v>803</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>743</v>
+        <v>804</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E190" s="15">
         <v>152</v>
@@ -9221,10 +8914,10 @@
         <v>465</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>746</v>
+        <v>238</v>
       </c>
       <c r="D191" s="22" t="s">
         <v>437</v>
@@ -9274,10 +8967,10 @@
         <v>468</v>
       </c>
       <c r="B194" s="45" t="s">
-        <v>747</v>
+        <v>806</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>748</v>
+        <v>385</v>
       </c>
       <c r="D194" s="47" t="s">
         <v>148</v>
@@ -9301,7 +8994,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="C195" s="46" t="s">
         <v>470</v>
@@ -9328,10 +9021,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="49" t="s">
-        <v>750</v>
+        <v>808</v>
       </c>
       <c r="C196" s="49" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="D196" s="49" t="s">
         <v>472</v>
@@ -9355,10 +9048,10 @@
         <v>473</v>
       </c>
       <c r="B197" s="49" t="s">
-        <v>752</v>
+        <v>810</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>753</v>
+        <v>389</v>
       </c>
       <c r="D197" s="49" t="s">
         <v>386</v>
@@ -9382,7 +9075,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="49" t="s">
-        <v>754</v>
+        <v>811</v>
       </c>
       <c r="C198" s="49" t="s">
         <v>475</v>
@@ -9409,13 +9102,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>755</v>
+        <v>812</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>756</v>
+        <v>401</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="E199" s="49">
         <v>95</v>
@@ -9427,7 +9120,7 @@
         <v>215</v>
       </c>
       <c r="H199" s="49">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I199" s="41"/>
     </row>
@@ -9593,7 +9286,7 @@
         <v>496</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="D208" s="14" t="s">
         <v>39</v>
@@ -9608,7 +9301,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="14">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I208" s="15"/>
     </row>
@@ -9656,7 +9349,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>759</v>
+        <v>815</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>39</v>
@@ -9678,10 +9371,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="39" t="s">
-        <v>760</v>
+        <v>816</v>
       </c>
       <c r="C212" s="39" t="s">
-        <v>761</v>
+        <v>817</v>
       </c>
       <c r="D212" s="39" t="s">
         <v>144</v>
@@ -9721,7 +9414,7 @@
         <v>178</v>
       </c>
       <c r="H213" s="14">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I213" s="41"/>
     </row>
@@ -9733,7 +9426,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="39" t="s">
-        <v>761</v>
+        <v>817</v>
       </c>
       <c r="D214" s="39" t="s">
         <v>144</v>
@@ -9846,10 +9539,10 @@
         <v>519</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>762</v>
+        <v>818</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>763</v>
+        <v>819</v>
       </c>
       <c r="D220" s="53" t="s">
         <v>520</v>
@@ -9867,7 +9560,7 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="15" t="s">
-        <v>764</v>
+        <v>820</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9875,13 +9568,13 @@
         <v>521</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>765</v>
+        <v>821</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>766</v>
+        <v>822</v>
       </c>
       <c r="D221" s="53" t="s">
-        <v>767</v>
+        <v>1</v>
       </c>
       <c r="E221" s="14">
         <v>100</v>
@@ -9896,7 +9589,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="41" t="s">
-        <v>768</v>
+        <v>823</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9904,13 +9597,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>770</v>
+        <v>825</v>
       </c>
       <c r="D222" s="53" t="s">
-        <v>771</v>
+        <v>520</v>
       </c>
       <c r="E222" s="14">
         <v>115</v>
@@ -9958,13 +9651,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="39" t="s">
-        <v>772</v>
+        <v>826</v>
       </c>
       <c r="C224" s="39" t="s">
-        <v>773</v>
+        <v>827</v>
       </c>
       <c r="D224" s="39" t="s">
-        <v>774</v>
+        <v>828</v>
       </c>
       <c r="E224" s="39">
         <v>120</v>
@@ -10012,10 +9705,10 @@
         <v>530</v>
       </c>
       <c r="B226" s="39" t="s">
-        <v>775</v>
+        <v>829</v>
       </c>
       <c r="C226" s="39" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D226" s="39" t="s">
         <v>437</v>
@@ -10039,10 +9732,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="39" t="s">
-        <v>776</v>
+        <v>830</v>
       </c>
       <c r="C227" s="39" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D227" s="39" t="s">
         <v>437</v>
@@ -10196,13 +9889,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="56" t="s">
-        <v>777</v>
+        <v>831</v>
       </c>
       <c r="C234" s="56" t="s">
-        <v>778</v>
+        <v>832</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="E234" s="56">
         <v>190</v>
@@ -10217,7 +9910,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="57" t="s">
-        <v>780</v>
+        <v>834</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -10225,13 +9918,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>781</v>
+        <v>835</v>
       </c>
       <c r="C235" s="55" t="s">
-        <v>782</v>
+        <v>836</v>
       </c>
       <c r="D235" s="55" t="s">
-        <v>783</v>
+        <v>837</v>
       </c>
       <c r="E235" s="55">
         <v>155</v>
@@ -10267,13 +9960,13 @@
         <v>548</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>784</v>
+        <v>838</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>549</v>
       </c>
       <c r="D237" s="55" t="s">
-        <v>785</v>
+        <v>839</v>
       </c>
       <c r="E237" s="55">
         <v>155</v>
@@ -10295,27 +9988,43 @@
       <c r="A238" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="B238" s="42"/>
-      <c r="C238" s="42"/>
-      <c r="D238" s="42"/>
-      <c r="E238" s="42"/>
-      <c r="F238" s="42"/>
-      <c r="G238" s="42"/>
-      <c r="H238" s="42"/>
-      <c r="I238" s="42"/>
+      <c r="B238" s="42" t="s">
+        <v>840</v>
+      </c>
+      <c r="C238" s="42" t="s">
+        <v>841</v>
+      </c>
+      <c r="D238" s="42" t="s">
+        <v>842</v>
+      </c>
+      <c r="E238" s="42">
+        <v>190</v>
+      </c>
+      <c r="F238" s="42">
+        <v>270</v>
+      </c>
+      <c r="G238" s="42">
+        <v>216</v>
+      </c>
+      <c r="H238" s="42">
+        <v>5.8</v>
+      </c>
+      <c r="I238" s="42" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="13" t="s">
         <v>551</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>786</v>
+        <v>844</v>
       </c>
       <c r="C239" s="55" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="D239" s="55" t="s">
-        <v>788</v>
+        <v>842</v>
       </c>
       <c r="E239" s="56">
         <v>180</v>
@@ -10327,10 +10036,10 @@
         <v>220</v>
       </c>
       <c r="H239" s="55">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I239" s="57" t="s">
-        <v>789</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -10338,13 +10047,13 @@
         <v>552</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>790</v>
+        <v>846</v>
       </c>
       <c r="C240" s="55" t="s">
-        <v>791</v>
+        <v>847</v>
       </c>
       <c r="D240" s="55" t="s">
-        <v>788</v>
+        <v>842</v>
       </c>
       <c r="E240" s="56">
         <v>190</v>
@@ -10359,7 +10068,7 @@
         <v>5.5</v>
       </c>
       <c r="I240" s="57" t="s">
-        <v>792</v>
+        <v>848</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10367,10 +10076,10 @@
         <v>553</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>793</v>
+        <v>849</v>
       </c>
       <c r="C241" s="55" t="s">
-        <v>794</v>
+        <v>850</v>
       </c>
       <c r="D241" s="15" t="s">
         <v>554</v>
@@ -10388,7 +10097,7 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="58" t="s">
-        <v>795</v>
+        <v>851</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10396,13 +10105,13 @@
         <v>555</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="C242" s="55" t="s">
-        <v>797</v>
+        <v>853</v>
       </c>
       <c r="D242" s="55" t="s">
-        <v>788</v>
+        <v>842</v>
       </c>
       <c r="E242" s="56">
         <v>160</v>
@@ -10417,7 +10126,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="57" t="s">
-        <v>798</v>
+        <v>854</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10425,13 +10134,13 @@
         <v>556</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>799</v>
+        <v>855</v>
       </c>
       <c r="C243" s="55" t="s">
-        <v>800</v>
+        <v>856</v>
       </c>
       <c r="D243" s="55" t="s">
-        <v>801</v>
+        <v>857</v>
       </c>
       <c r="E243" s="56">
         <v>190</v>
@@ -10446,7 +10155,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="57" t="s">
-        <v>802</v>
+        <v>858</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10454,13 +10163,13 @@
         <v>557</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>803</v>
+        <v>859</v>
       </c>
       <c r="C244" s="55" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="D244" s="55" t="s">
-        <v>801</v>
+        <v>857</v>
       </c>
       <c r="E244" s="55">
         <v>150</v>
@@ -10492,13 +10201,13 @@
         <v>559</v>
       </c>
       <c r="B246" s="22" t="s">
-        <v>805</v>
+        <v>861</v>
       </c>
       <c r="C246" s="22" t="s">
-        <v>806</v>
+        <v>862</v>
       </c>
       <c r="D246" s="37" t="s">
-        <v>807</v>
+        <v>429</v>
       </c>
       <c r="E246" s="22">
         <v>112</v>
@@ -10519,7 +10228,7 @@
         <v>560</v>
       </c>
       <c r="B247" s="22" t="s">
-        <v>808</v>
+        <v>863</v>
       </c>
       <c r="C247" s="22" t="s">
         <v>529</v>
@@ -10546,7 +10255,7 @@
         <v>561</v>
       </c>
       <c r="B248" s="22" t="s">
-        <v>809</v>
+        <v>864</v>
       </c>
       <c r="C248" s="22" t="s">
         <v>562</v>
@@ -10573,10 +10282,10 @@
         <v>563</v>
       </c>
       <c r="B249" s="22" t="s">
-        <v>810</v>
+        <v>865</v>
       </c>
       <c r="C249" s="22" t="s">
-        <v>811</v>
+        <v>439</v>
       </c>
       <c r="D249" s="22" t="s">
         <v>429</v>
@@ -10600,7 +10309,7 @@
         <v>564</v>
       </c>
       <c r="B250" s="22" t="s">
-        <v>812</v>
+        <v>866</v>
       </c>
       <c r="C250" s="22" t="s">
         <v>153</v>
@@ -10627,7 +10336,7 @@
         <v>565</v>
       </c>
       <c r="B251" s="22" t="s">
-        <v>813</v>
+        <v>867</v>
       </c>
       <c r="C251" s="22" t="s">
         <v>566</v>
@@ -10654,10 +10363,10 @@
         <v>567</v>
       </c>
       <c r="B252" s="22" t="s">
-        <v>814</v>
+        <v>868</v>
       </c>
       <c r="C252" s="22" t="s">
-        <v>811</v>
+        <v>439</v>
       </c>
       <c r="D252" s="22" t="s">
         <v>429</v>
@@ -10681,7 +10390,7 @@
         <v>568</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>815</v>
+        <v>869</v>
       </c>
       <c r="C253" s="22" t="s">
         <v>566</v>
@@ -10708,13 +10417,13 @@
         <v>569</v>
       </c>
       <c r="B254" s="22" t="s">
-        <v>816</v>
+        <v>870</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>817</v>
+        <v>871</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="E254" s="22">
         <v>190</v>
@@ -10729,7 +10438,7 @@
         <v>5.2</v>
       </c>
       <c r="I254" s="57" t="s">
-        <v>802</v>
+        <v>858</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10737,7 +10446,7 @@
         <v>570</v>
       </c>
       <c r="B255" s="22" t="s">
-        <v>819</v>
+        <v>872</v>
       </c>
       <c r="C255" s="22" t="s">
         <v>571</v>
@@ -10764,13 +10473,13 @@
         <v>572</v>
       </c>
       <c r="B256" s="56" t="s">
-        <v>820</v>
+        <v>873</v>
       </c>
       <c r="C256" s="22" t="s">
-        <v>821</v>
+        <v>161</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>822</v>
+        <v>874</v>
       </c>
       <c r="E256" s="56">
         <v>190</v>
@@ -10785,7 +10494,7 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="57" t="s">
-        <v>823</v>
+        <v>875</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10793,13 +10502,13 @@
         <v>573</v>
       </c>
       <c r="B257" s="40" t="s">
-        <v>824</v>
+        <v>876</v>
       </c>
       <c r="C257" s="40" t="s">
-        <v>825</v>
+        <v>321</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>807</v>
+        <v>429</v>
       </c>
       <c r="E257" s="40">
         <v>118</v>
@@ -10820,7 +10529,7 @@
         <v>574</v>
       </c>
       <c r="B258" s="22" t="s">
-        <v>812</v>
+        <v>866</v>
       </c>
       <c r="C258" s="22" t="s">
         <v>153</v>
@@ -10879,7 +10588,7 @@
         <v>579</v>
       </c>
       <c r="D261" s="53" t="s">
-        <v>826</v>
+        <v>877</v>
       </c>
       <c r="E261" s="14">
         <v>108</v>
@@ -10900,7 +10609,7 @@
         <v>580</v>
       </c>
       <c r="B262" s="14" t="s">
-        <v>827</v>
+        <v>878</v>
       </c>
       <c r="C262" s="14" t="s">
         <v>581</v>
@@ -10999,7 +10708,7 @@
         <v>215</v>
       </c>
       <c r="H265" s="39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I265" s="10"/>
     </row>
@@ -11008,13 +10717,13 @@
         <v>595</v>
       </c>
       <c r="B266" s="39" t="s">
-        <v>828</v>
+        <v>879</v>
       </c>
       <c r="C266" s="39" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="D266" s="39" t="s">
-        <v>829</v>
+        <v>880</v>
       </c>
       <c r="E266" s="39">
         <v>78</v>
@@ -11035,13 +10744,13 @@
         <v>596</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>830</v>
+        <v>881</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>831</v>
+        <v>882</v>
       </c>
       <c r="D267" s="53" t="s">
-        <v>832</v>
+        <v>144</v>
       </c>
       <c r="E267" s="14">
         <v>60</v>
@@ -11206,13 +10915,13 @@
         <v>610</v>
       </c>
       <c r="B278" s="31" t="s">
-        <v>833</v>
+        <v>883</v>
       </c>
       <c r="C278" s="31" t="s">
-        <v>834</v>
+        <v>549</v>
       </c>
       <c r="D278" s="31" t="s">
-        <v>835</v>
+        <v>884</v>
       </c>
       <c r="E278" s="31">
         <v>159</v>
@@ -11233,10 +10942,10 @@
         <v>611</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>836</v>
+        <v>885</v>
       </c>
       <c r="C279" s="53" t="s">
-        <v>837</v>
+        <v>886</v>
       </c>
       <c r="D279" s="14" t="s">
         <v>144</v>
@@ -11260,13 +10969,13 @@
         <v>612</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>838</v>
+        <v>887</v>
       </c>
       <c r="C280" s="53" t="s">
-        <v>839</v>
+        <v>888</v>
       </c>
       <c r="D280" s="14" t="s">
-        <v>840</v>
+        <v>489</v>
       </c>
       <c r="E280" s="14"/>
       <c r="F280" s="13">
@@ -11312,7 +11021,7 @@
         <v>616</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>841</v>
+        <v>889</v>
       </c>
       <c r="C282" s="53" t="s">
         <v>617</v>
@@ -11339,10 +11048,10 @@
         <v>618</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>842</v>
+        <v>890</v>
       </c>
       <c r="C283" s="53" t="s">
-        <v>843</v>
+        <v>891</v>
       </c>
       <c r="D283" s="14" t="s">
         <v>39</v>
@@ -11366,13 +11075,13 @@
         <v>619</v>
       </c>
       <c r="B284" s="31" t="s">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="C284" s="40" t="s">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>846</v>
+        <v>894</v>
       </c>
       <c r="E284" s="40">
         <v>80</v>
@@ -11399,7 +11108,7 @@
         <v>622</v>
       </c>
       <c r="D285" s="40" t="s">
-        <v>846</v>
+        <v>894</v>
       </c>
       <c r="E285" s="14">
         <v>73</v>
@@ -11420,10 +11129,10 @@
         <v>623</v>
       </c>
       <c r="B286" s="56" t="s">
-        <v>847</v>
+        <v>895</v>
       </c>
       <c r="C286" s="56" t="s">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="D286" s="56" t="s">
         <v>624</v>
@@ -11447,13 +11156,13 @@
         <v>625</v>
       </c>
       <c r="B287" s="56" t="s">
-        <v>849</v>
+        <v>897</v>
       </c>
       <c r="C287" s="56" t="s">
-        <v>850</v>
+        <v>898</v>
       </c>
       <c r="D287" s="56" t="s">
-        <v>851</v>
+        <v>899</v>
       </c>
       <c r="E287" s="56">
         <v>88</v>
@@ -11474,7 +11183,7 @@
         <v>626</v>
       </c>
       <c r="B288" s="31" t="s">
-        <v>852</v>
+        <v>900</v>
       </c>
       <c r="C288" s="31" t="s">
         <v>627</v>
@@ -11522,7 +11231,7 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="15" t="s">
-        <v>853</v>
+        <v>901</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -11557,7 +11266,7 @@
         <v>635</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>854</v>
+        <v>902</v>
       </c>
       <c r="C291" s="64" t="s">
         <v>636</v>
@@ -11584,7 +11293,7 @@
         <v>638</v>
       </c>
       <c r="B292" s="64" t="s">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="C292" s="64" t="s">
         <v>639</v>
@@ -11611,10 +11320,10 @@
         <v>641</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>856</v>
+        <v>904</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>857</v>
+        <v>905</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11638,13 +11347,13 @@
         <v>642</v>
       </c>
       <c r="B294" s="22" t="s">
-        <v>858</v>
+        <v>906</v>
       </c>
       <c r="C294" s="22" t="s">
-        <v>859</v>
+        <v>445</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>860</v>
+        <v>907</v>
       </c>
       <c r="E294" s="22">
         <v>150</v>
@@ -11665,7 +11374,7 @@
         <v>643</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>861</v>
+        <v>908</v>
       </c>
       <c r="C295" s="14" t="s">
         <v>644</v>
@@ -11713,13 +11422,13 @@
         <v>650</v>
       </c>
       <c r="B297" s="22" t="s">
-        <v>862</v>
+        <v>909</v>
       </c>
       <c r="C297" s="22" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="D297" s="37" t="s">
-        <v>864</v>
+        <v>911</v>
       </c>
       <c r="E297" s="22">
         <v>125</v>
@@ -11740,13 +11449,13 @@
         <v>651</v>
       </c>
       <c r="B298" s="22" t="s">
-        <v>865</v>
+        <v>912</v>
       </c>
       <c r="C298" s="22" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="D298" s="37" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="E298" s="22">
         <v>190</v>
@@ -11761,7 +11470,7 @@
         <v>5.7</v>
       </c>
       <c r="I298" s="15" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -11769,13 +11478,13 @@
         <v>652</v>
       </c>
       <c r="B299" s="55" t="s">
-        <v>869</v>
+        <v>916</v>
       </c>
       <c r="C299" s="55" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="D299" s="55" t="s">
-        <v>871</v>
+        <v>918</v>
       </c>
       <c r="E299" s="55">
         <v>124</v>
@@ -11790,7 +11499,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="58" t="s">
-        <v>872</v>
+        <v>919</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11824,13 +11533,13 @@
         <v>655</v>
       </c>
       <c r="B302" s="15" t="s">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>874</v>
+        <v>921</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="E302" s="15">
         <v>150</v>
@@ -11857,7 +11566,7 @@
         <v>658</v>
       </c>
       <c r="D303" s="14" t="s">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="E303" s="15">
         <v>140</v>
@@ -11881,7 +11590,7 @@
         <v>660</v>
       </c>
       <c r="C304" s="64" t="s">
-        <v>876</v>
+        <v>251</v>
       </c>
       <c r="D304" s="64" t="s">
         <v>661</v>
@@ -11899,7 +11608,7 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="41" t="s">
-        <v>877</v>
+        <v>923</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -11907,13 +11616,13 @@
         <v>662</v>
       </c>
       <c r="B305" s="40" t="s">
-        <v>878</v>
+        <v>924</v>
       </c>
       <c r="C305" s="40" t="s">
-        <v>879</v>
+        <v>925</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>880</v>
+        <v>926</v>
       </c>
       <c r="E305" s="40">
         <v>215</v>
@@ -12002,7 +11711,7 @@
         <v>669</v>
       </c>
       <c r="C311" s="39" t="s">
-        <v>881</v>
+        <v>670</v>
       </c>
       <c r="D311" s="39" t="s">
         <v>671</v>
@@ -12079,13 +11788,13 @@
         <v>677</v>
       </c>
       <c r="B315" s="40" t="s">
-        <v>882</v>
+        <v>927</v>
       </c>
       <c r="C315" s="40" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>884</v>
+        <v>928</v>
       </c>
       <c r="E315" s="40">
         <v>116</v>
@@ -12100,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="I315" s="9" t="s">
-        <v>885</v>
+        <v>929</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -12108,13 +11817,13 @@
         <v>678</v>
       </c>
       <c r="B316" s="40" t="s">
-        <v>886</v>
+        <v>930</v>
       </c>
       <c r="C316" s="40" t="s">
-        <v>887</v>
+        <v>931</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>888</v>
+        <v>932</v>
       </c>
       <c r="E316" s="40">
         <v>160</v>
@@ -12126,10 +11835,10 @@
         <v>215</v>
       </c>
       <c r="H316" s="9">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>889</v>
+        <v>933</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -12137,13 +11846,13 @@
         <v>679</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>890</v>
+        <v>934</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>891</v>
+        <v>935</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>892</v>
+        <v>936</v>
       </c>
       <c r="E317" s="15">
         <v>110</v>
@@ -12158,7 +11867,7 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="15" t="s">
-        <v>893</v>
+        <v>937</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -12166,13 +11875,13 @@
         <v>680</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>890</v>
+        <v>934</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>894</v>
+        <v>938</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>892</v>
+        <v>936</v>
       </c>
       <c r="E318" s="15">
         <v>110</v>
@@ -12193,13 +11902,13 @@
         <v>681</v>
       </c>
       <c r="B319" s="22" t="s">
-        <v>895</v>
+        <v>939</v>
       </c>
       <c r="C319" s="22" t="s">
-        <v>896</v>
+        <v>940</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>897</v>
+        <v>941</v>
       </c>
       <c r="E319" s="22">
         <v>205</v>
@@ -12211,10 +11920,10 @@
         <v>215</v>
       </c>
       <c r="H319" s="22">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I319" s="15" t="s">
-        <v>898</v>
+        <v>942</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -12222,13 +11931,13 @@
         <v>682</v>
       </c>
       <c r="B320" s="22" t="s">
-        <v>899</v>
+        <v>943</v>
       </c>
       <c r="C320" s="22" t="s">
-        <v>900</v>
+        <v>944</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>901</v>
+        <v>945</v>
       </c>
       <c r="E320" s="22">
         <v>182</v>
@@ -12243,7 +11952,7 @@
         <v>5.6</v>
       </c>
       <c r="I320" s="15" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -12251,13 +11960,13 @@
         <v>683</v>
       </c>
       <c r="B321" s="22" t="s">
-        <v>902</v>
+        <v>946</v>
       </c>
       <c r="C321" s="22" t="s">
-        <v>903</v>
+        <v>947</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>904</v>
+        <v>948</v>
       </c>
       <c r="E321" s="22">
         <v>138</v>
@@ -12272,7 +11981,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="15" t="s">
-        <v>905</v>
+        <v>949</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -12280,28 +11989,28 @@
         <v>684</v>
       </c>
       <c r="B322" s="22" t="s">
-        <v>906</v>
+        <v>950</v>
       </c>
       <c r="C322" s="22" t="s">
-        <v>907</v>
+        <v>951</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>897</v>
+        <v>941</v>
       </c>
       <c r="E322" s="22">
         <v>225</v>
       </c>
       <c r="F322" s="35">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G322" s="36">
         <v>215</v>
       </c>
       <c r="H322" s="22">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I322" s="15" t="s">
-        <v>908</v>
+        <v>952</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -12309,13 +12018,13 @@
         <v>685</v>
       </c>
       <c r="B323" s="22" t="s">
-        <v>909</v>
+        <v>953</v>
       </c>
       <c r="C323" s="22" t="s">
-        <v>910</v>
+        <v>88</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>904</v>
+        <v>948</v>
       </c>
       <c r="E323" s="22">
         <v>155</v>
@@ -12327,10 +12036,10 @@
         <v>215</v>
       </c>
       <c r="H323" s="22">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="15" t="s">
-        <v>911</v>
+        <v>954</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -12338,13 +12047,13 @@
         <v>686</v>
       </c>
       <c r="B324" s="22" t="s">
-        <v>912</v>
+        <v>955</v>
       </c>
       <c r="C324" s="22" t="s">
-        <v>913</v>
+        <v>956</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>897</v>
+        <v>941</v>
       </c>
       <c r="E324" s="22">
         <v>220</v>
@@ -12359,7 +12068,7 @@
         <v>6.1</v>
       </c>
       <c r="I324" s="15" t="s">
-        <v>908</v>
+        <v>952</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -12377,7 +12086,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="13" t="s">
-        <v>914</v>
+        <v>703</v>
       </c>
       <c r="B326" s="40"/>
       <c r="C326" s="40"/>
@@ -12390,7 +12099,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="13" t="s">
-        <v>915</v>
+        <v>704</v>
       </c>
       <c r="B327" s="40"/>
       <c r="C327" s="40"/>
@@ -12403,7 +12112,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="13" t="s">
-        <v>916</v>
+        <v>705</v>
       </c>
       <c r="B328" s="40"/>
       <c r="C328" s="40"/>
@@ -12416,7 +12125,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="13" t="s">
-        <v>917</v>
+        <v>706</v>
       </c>
       <c r="B329" s="40"/>
       <c r="C329" s="40"/>
@@ -12429,7 +12138,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="13" t="s">
-        <v>918</v>
+        <v>707</v>
       </c>
       <c r="B330" s="40"/>
       <c r="C330" s="40"/>
@@ -12442,7 +12151,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="13" t="s">
-        <v>919</v>
+        <v>708</v>
       </c>
       <c r="B331" s="40"/>
       <c r="C331" s="40"/>
@@ -12455,7 +12164,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="13" t="s">
-        <v>920</v>
+        <v>709</v>
       </c>
       <c r="B332" s="40"/>
       <c r="C332" s="40"/>
@@ -12468,7 +12177,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="13" t="s">
-        <v>921</v>
+        <v>710</v>
       </c>
       <c r="B333" s="40"/>
       <c r="C333" s="40"/>
@@ -12481,7 +12190,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="13" t="s">
-        <v>922</v>
+        <v>711</v>
       </c>
       <c r="B334" s="40"/>
       <c r="C334" s="40"/>
@@ -12494,7 +12203,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="13" t="s">
-        <v>923</v>
+        <v>712</v>
       </c>
       <c r="B335" s="40"/>
       <c r="C335" s="40"/>
@@ -12507,7 +12216,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="13" t="s">
-        <v>924</v>
+        <v>713</v>
       </c>
       <c r="B336" s="40"/>
       <c r="C336" s="40"/>
@@ -12520,7 +12229,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="13" t="s">
-        <v>925</v>
+        <v>714</v>
       </c>
       <c r="B337" s="40"/>
       <c r="C337" s="40"/>
@@ -12533,7 +12242,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="13" t="s">
-        <v>926</v>
+        <v>715</v>
       </c>
       <c r="B338" s="40"/>
       <c r="C338" s="40"/>
@@ -12546,7 +12255,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="13" t="s">
-        <v>927</v>
+        <v>716</v>
       </c>
       <c r="B339" s="40"/>
       <c r="C339" s="40"/>
@@ -12559,7 +12268,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="13" t="s">
-        <v>928</v>
+        <v>717</v>
       </c>
       <c r="B340" s="40"/>
       <c r="C340" s="40"/>
@@ -12572,7 +12281,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="13" t="s">
-        <v>929</v>
+        <v>718</v>
       </c>
       <c r="B341" s="40"/>
       <c r="C341" s="40"/>
@@ -12585,7 +12294,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="13" t="s">
-        <v>930</v>
+        <v>719</v>
       </c>
       <c r="B342" s="40"/>
       <c r="C342" s="40"/>
@@ -12598,7 +12307,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="13" t="s">
-        <v>931</v>
+        <v>720</v>
       </c>
       <c r="B343" s="40"/>
       <c r="C343" s="40"/>
@@ -12611,7 +12320,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="13" t="s">
-        <v>932</v>
+        <v>721</v>
       </c>
       <c r="B344" s="40"/>
       <c r="C344" s="40"/>
@@ -12624,7 +12333,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="13" t="s">
-        <v>933</v>
+        <v>722</v>
       </c>
       <c r="B345" s="40"/>
       <c r="C345" s="40"/>
@@ -12637,7 +12346,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="13" t="s">
-        <v>934</v>
+        <v>723</v>
       </c>
       <c r="B346" s="40"/>
       <c r="C346" s="40"/>
@@ -12650,7 +12359,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="13" t="s">
-        <v>935</v>
+        <v>724</v>
       </c>
       <c r="B347" s="40"/>
       <c r="C347" s="40"/>
@@ -12663,7 +12372,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="13" t="s">
-        <v>936</v>
+        <v>725</v>
       </c>
       <c r="B348" s="40"/>
       <c r="C348" s="40"/>
@@ -12676,7 +12385,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="13" t="s">
-        <v>937</v>
+        <v>726</v>
       </c>
       <c r="B349" s="40"/>
       <c r="C349" s="40"/>
@@ -12689,7 +12398,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="13" t="s">
-        <v>938</v>
+        <v>727</v>
       </c>
       <c r="B350" s="40"/>
       <c r="C350" s="40"/>
@@ -12702,7 +12411,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="13" t="s">
-        <v>939</v>
+        <v>728</v>
       </c>
       <c r="B351" s="40"/>
       <c r="C351" s="40"/>
@@ -12715,7 +12424,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="13" t="s">
-        <v>940</v>
+        <v>729</v>
       </c>
       <c r="B352" s="40"/>
       <c r="C352" s="40"/>
@@ -12728,7 +12437,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="13" t="s">
-        <v>941</v>
+        <v>730</v>
       </c>
       <c r="B353" s="40"/>
       <c r="C353" s="40"/>
@@ -12741,7 +12450,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="13" t="s">
-        <v>942</v>
+        <v>731</v>
       </c>
       <c r="B354" s="40"/>
       <c r="C354" s="40"/>
@@ -12754,7 +12463,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="13" t="s">
-        <v>943</v>
+        <v>732</v>
       </c>
       <c r="B355" s="40"/>
       <c r="C355" s="40"/>
@@ -12767,7 +12476,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="13" t="s">
-        <v>944</v>
+        <v>733</v>
       </c>
       <c r="B356" s="40"/>
       <c r="C356" s="40"/>
@@ -12780,7 +12489,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="13" t="s">
-        <v>945</v>
+        <v>734</v>
       </c>
       <c r="B357" s="40"/>
       <c r="C357" s="40"/>
@@ -12793,7 +12502,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="13" t="s">
-        <v>946</v>
+        <v>735</v>
       </c>
       <c r="B358" s="40"/>
       <c r="C358" s="40"/>
@@ -12806,7 +12515,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="13" t="s">
-        <v>947</v>
+        <v>736</v>
       </c>
       <c r="B359" s="40"/>
       <c r="C359" s="40"/>
@@ -12819,7 +12528,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="13" t="s">
-        <v>948</v>
+        <v>737</v>
       </c>
       <c r="B360" s="40"/>
       <c r="C360" s="40"/>
@@ -12832,7 +12541,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="13" t="s">
-        <v>949</v>
+        <v>738</v>
       </c>
       <c r="B361" s="40"/>
       <c r="C361" s="40"/>
@@ -12845,7 +12554,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="13" t="s">
-        <v>950</v>
+        <v>739</v>
       </c>
       <c r="B362" s="40"/>
       <c r="C362" s="40"/>
@@ -12858,7 +12567,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="13" t="s">
-        <v>951</v>
+        <v>740</v>
       </c>
       <c r="B363" s="40"/>
       <c r="C363" s="40"/>
@@ -12871,7 +12580,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="13" t="s">
-        <v>952</v>
+        <v>741</v>
       </c>
       <c r="B364" s="40"/>
       <c r="C364" s="40"/>
@@ -12884,7 +12593,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="13" t="s">
-        <v>953</v>
+        <v>742</v>
       </c>
       <c r="B365" s="40"/>
       <c r="C365" s="40"/>
@@ -12897,7 +12606,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="13" t="s">
-        <v>954</v>
+        <v>743</v>
       </c>
       <c r="B366" s="40"/>
       <c r="C366" s="40"/>
@@ -12910,7 +12619,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="13" t="s">
-        <v>955</v>
+        <v>744</v>
       </c>
       <c r="B367" s="40"/>
       <c r="C367" s="40"/>
@@ -12923,7 +12632,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="13" t="s">
-        <v>956</v>
+        <v>745</v>
       </c>
       <c r="B368" s="40"/>
       <c r="C368" s="40"/>
@@ -12936,7 +12645,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="13" t="s">
-        <v>957</v>
+        <v>746</v>
       </c>
       <c r="B369" s="40"/>
       <c r="C369" s="40"/>
@@ -12949,7 +12658,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="13" t="s">
-        <v>958</v>
+        <v>747</v>
       </c>
       <c r="B370" s="40"/>
       <c r="C370" s="40"/>
@@ -12962,7 +12671,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="13" t="s">
-        <v>959</v>
+        <v>748</v>
       </c>
       <c r="B371" s="40"/>
       <c r="C371" s="40"/>
@@ -12975,7 +12684,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="13" t="s">
-        <v>960</v>
+        <v>749</v>
       </c>
       <c r="B372" s="40"/>
       <c r="C372" s="40"/>
@@ -12988,7 +12697,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="13" t="s">
-        <v>961</v>
+        <v>750</v>
       </c>
       <c r="B373" s="40"/>
       <c r="C373" s="40"/>
@@ -13001,7 +12710,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="13" t="s">
-        <v>962</v>
+        <v>751</v>
       </c>
       <c r="B374" s="40"/>
       <c r="C374" s="40"/>
@@ -13014,7 +12723,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="13" t="s">
-        <v>963</v>
+        <v>752</v>
       </c>
       <c r="B375" s="40"/>
       <c r="C375" s="40"/>
@@ -13027,7 +12736,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="13" t="s">
-        <v>964</v>
+        <v>753</v>
       </c>
       <c r="B376" s="40"/>
       <c r="C376" s="40"/>
@@ -13040,7 +12749,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="13" t="s">
-        <v>965</v>
+        <v>754</v>
       </c>
       <c r="B377" s="40"/>
       <c r="C377" s="40"/>
@@ -13053,7 +12762,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="13" t="s">
-        <v>966</v>
+        <v>755</v>
       </c>
       <c r="B378" s="40"/>
       <c r="C378" s="40"/>
@@ -13066,7 +12775,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="13" t="s">
-        <v>967</v>
+        <v>756</v>
       </c>
       <c r="B379" s="40"/>
       <c r="C379" s="40"/>
@@ -13079,7 +12788,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="13" t="s">
-        <v>968</v>
+        <v>757</v>
       </c>
       <c r="B380" s="40"/>
       <c r="C380" s="40"/>
@@ -13092,7 +12801,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="13" t="s">
-        <v>969</v>
+        <v>758</v>
       </c>
       <c r="B381" s="40"/>
       <c r="C381" s="40"/>
@@ -13105,7 +12814,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="13" t="s">
-        <v>970</v>
+        <v>759</v>
       </c>
       <c r="B382" s="40"/>
       <c r="C382" s="40"/>
@@ -13118,7 +12827,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="13" t="s">
-        <v>971</v>
+        <v>760</v>
       </c>
       <c r="B383" s="40"/>
       <c r="C383" s="40"/>
@@ -13131,7 +12840,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="13" t="s">
-        <v>972</v>
+        <v>761</v>
       </c>
       <c r="B384" s="40"/>
       <c r="C384" s="40"/>
@@ -13144,7 +12853,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="13" t="s">
-        <v>973</v>
+        <v>762</v>
       </c>
       <c r="B385" s="40"/>
       <c r="C385" s="40"/>
@@ -13157,7 +12866,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="13" t="s">
-        <v>974</v>
+        <v>763</v>
       </c>
       <c r="B386" s="40"/>
       <c r="C386" s="40"/>
@@ -13170,7 +12879,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="13" t="s">
-        <v>975</v>
+        <v>764</v>
       </c>
       <c r="B387" s="40"/>
       <c r="C387" s="40"/>
@@ -13183,7 +12892,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="13" t="s">
-        <v>976</v>
+        <v>765</v>
       </c>
       <c r="B388" s="40"/>
       <c r="C388" s="40"/>
@@ -13196,7 +12905,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="13" t="s">
-        <v>977</v>
+        <v>766</v>
       </c>
       <c r="B389" s="40"/>
       <c r="C389" s="40"/>
@@ -13209,7 +12918,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="13" t="s">
-        <v>978</v>
+        <v>767</v>
       </c>
       <c r="B390" s="40"/>
       <c r="C390" s="40"/>
@@ -13222,7 +12931,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="13" t="s">
-        <v>979</v>
+        <v>768</v>
       </c>
       <c r="B391" s="40"/>
       <c r="C391" s="40"/>
@@ -13235,7 +12944,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="13" t="s">
-        <v>980</v>
+        <v>769</v>
       </c>
       <c r="B392" s="40"/>
       <c r="C392" s="40"/>
@@ -13248,7 +12957,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="13" t="s">
-        <v>981</v>
+        <v>770</v>
       </c>
       <c r="B393" s="40"/>
       <c r="C393" s="40"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="978">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1924,9 +1924,6 @@
   </si>
   <si>
     <t>XC290</t>
-  </si>
-  <si>
-    <t>20*2*28</t>
   </si>
   <si>
     <t>75*75*2</t>
@@ -2386,568 +2383,856 @@
   </si>
   <si>
     <t>XC001</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克368</t>
-  </si>
-  <si>
-    <t>40S*75D酷丝绵细双斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>30*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*26</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*300T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-  </si>
-  <si>
-    <t>白坯300克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00克</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>天丝棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>生态棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">生态棉 加厚 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -3045,6 +3330,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="18">
@@ -4071,54 +4363,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>699</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>690</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>771</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>772</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1</v>
+        <v>772</v>
       </c>
       <c r="E2" s="14">
         <v>79</v>
@@ -4132,13 +4424,13 @@
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>701</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>700</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6009,7 +6301,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>73</v>
+        <v>776</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>144</v>
@@ -7359,7 +7651,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D131" s="28" t="s">
         <v>148</v>
@@ -7951,7 +8243,7 @@
         <v>208</v>
       </c>
       <c r="H154" s="14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I154" s="15"/>
     </row>
@@ -7978,7 +8270,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I155" s="15"/>
     </row>
@@ -8118,7 +8410,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="26" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C161" s="26" t="s">
         <v>413</v>
@@ -8199,7 +8491,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="26" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C164" s="26" t="s">
         <v>422</v>
@@ -8226,10 +8518,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="26" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C165" s="26" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D165" s="26" t="s">
         <v>414</v>
@@ -8266,13 +8558,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E167" s="22">
         <v>80</v>
@@ -8293,13 +8585,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>417</v>
+        <v>786</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E168" s="22">
         <v>110</v>
@@ -8320,7 +8612,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C169" s="22" t="s">
         <v>428</v>
@@ -8347,7 +8639,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C170" s="22" t="s">
         <v>431</v>
@@ -8374,7 +8666,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C171" s="22" t="s">
         <v>238</v>
@@ -8428,7 +8720,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C173" s="22" t="s">
         <v>436</v>
@@ -8455,7 +8747,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C174" s="22" t="s">
         <v>439</v>
@@ -8482,7 +8774,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>32</v>
@@ -8563,7 +8855,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C178" s="22" t="s">
         <v>420</v>
@@ -8617,7 +8909,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C180" s="22" t="s">
         <v>451</v>
@@ -8644,7 +8936,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C181" s="22" t="s">
         <v>445</v>
@@ -8671,7 +8963,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="38" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C182" s="38" t="s">
         <v>309</v>
@@ -8689,7 +8981,7 @@
         <v>215</v>
       </c>
       <c r="H182" s="38">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I182" s="15"/>
     </row>
@@ -8698,7 +8990,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="38" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C183" s="38" t="s">
         <v>309</v>
@@ -8716,7 +9008,7 @@
         <v>215</v>
       </c>
       <c r="H183" s="38">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I183" s="15"/>
     </row>
@@ -8743,7 +9035,7 @@
         <v>215</v>
       </c>
       <c r="H184" s="39">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I184" s="42"/>
     </row>
@@ -8752,13 +9044,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>445</v>
+        <v>800</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>429</v>
+        <v>801</v>
       </c>
       <c r="E185" s="22">
         <v>112</v>
@@ -8779,7 +9071,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="38" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C186" s="38" t="s">
         <v>309</v>
@@ -8803,13 +9095,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="13" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B187" s="22" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D187" s="22" t="s">
         <v>437</v>
@@ -8833,13 +9125,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>272</v>
+        <v>806</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="E188" s="22">
         <v>110</v>
@@ -8860,7 +9152,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C189" s="22" t="s">
         <v>445</v>
@@ -8887,13 +9179,13 @@
         <v>464</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="E190" s="15">
         <v>152</v>
@@ -8905,7 +9197,7 @@
         <v>215</v>
       </c>
       <c r="H190" s="14">
-        <v>5.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I190" s="15"/>
     </row>
@@ -8914,10 +9206,10 @@
         <v>465</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D191" s="22" t="s">
         <v>437</v>
@@ -8967,10 +9259,10 @@
         <v>468</v>
       </c>
       <c r="B194" s="45" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>385</v>
+        <v>813</v>
       </c>
       <c r="D194" s="47" t="s">
         <v>148</v>
@@ -8985,7 +9277,7 @@
         <v>225</v>
       </c>
       <c r="H194" s="45">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I194" s="41"/>
     </row>
@@ -8994,7 +9286,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="C195" s="46" t="s">
         <v>470</v>
@@ -9012,7 +9304,7 @@
         <v>208</v>
       </c>
       <c r="H195" s="45">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I195" s="41"/>
     </row>
@@ -9021,10 +9313,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="49" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C196" s="49" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D196" s="49" t="s">
         <v>472</v>
@@ -9039,7 +9331,7 @@
         <v>215</v>
       </c>
       <c r="H196" s="49">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I196" s="15"/>
     </row>
@@ -9048,10 +9340,10 @@
         <v>473</v>
       </c>
       <c r="B197" s="49" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>389</v>
+        <v>818</v>
       </c>
       <c r="D197" s="49" t="s">
         <v>386</v>
@@ -9075,7 +9367,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="49" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C198" s="49" t="s">
         <v>475</v>
@@ -9102,13 +9394,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>401</v>
+        <v>821</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E199" s="49">
         <v>95</v>
@@ -9286,7 +9578,7 @@
         <v>496</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D208" s="14" t="s">
         <v>39</v>
@@ -9301,7 +9593,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="14">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I208" s="15"/>
     </row>
@@ -9349,7 +9641,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>39</v>
@@ -9371,10 +9663,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="39" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="C212" s="39" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="D212" s="39" t="s">
         <v>144</v>
@@ -9426,7 +9718,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="39" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="D214" s="39" t="s">
         <v>144</v>
@@ -9539,10 +9831,10 @@
         <v>519</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="D220" s="53" t="s">
         <v>520</v>
@@ -9560,7 +9852,7 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="15" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9568,13 +9860,13 @@
         <v>521</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="D221" s="53" t="s">
-        <v>1</v>
+        <v>832</v>
       </c>
       <c r="E221" s="14">
         <v>100</v>
@@ -9589,7 +9881,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="41" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9597,13 +9889,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="D222" s="53" t="s">
-        <v>520</v>
+        <v>836</v>
       </c>
       <c r="E222" s="14">
         <v>115</v>
@@ -9651,13 +9943,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="39" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="C224" s="39" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="D224" s="39" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="E224" s="39">
         <v>120</v>
@@ -9705,10 +9997,10 @@
         <v>530</v>
       </c>
       <c r="B226" s="39" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="C226" s="39" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D226" s="39" t="s">
         <v>437</v>
@@ -9732,10 +10024,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="39" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="C227" s="39" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D227" s="39" t="s">
         <v>437</v>
@@ -9889,13 +10181,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="56" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="C234" s="56" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="E234" s="56">
         <v>190</v>
@@ -9910,7 +10202,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="57" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9918,13 +10210,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="C235" s="55" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="D235" s="55" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="E235" s="55">
         <v>155</v>
@@ -9960,13 +10252,13 @@
         <v>548</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>549</v>
       </c>
       <c r="D237" s="55" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="E237" s="55">
         <v>155</v>
@@ -9978,7 +10270,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="55">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I237" s="58" t="s">
         <v>546</v>
@@ -9988,29 +10280,29 @@
       <c r="A238" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="B238" s="42" t="s">
-        <v>840</v>
-      </c>
-      <c r="C238" s="42" t="s">
-        <v>841</v>
-      </c>
-      <c r="D238" s="42" t="s">
-        <v>842</v>
-      </c>
-      <c r="E238" s="42">
+      <c r="B238" s="55" t="s">
+        <v>851</v>
+      </c>
+      <c r="C238" s="55" t="s">
+        <v>852</v>
+      </c>
+      <c r="D238" s="55" t="s">
+        <v>853</v>
+      </c>
+      <c r="E238" s="56">
         <v>190</v>
       </c>
-      <c r="F238" s="42">
+      <c r="F238" s="40">
         <v>270</v>
       </c>
-      <c r="G238" s="42">
+      <c r="G238" s="58">
         <v>216</v>
       </c>
-      <c r="H238" s="42">
-        <v>5.8</v>
-      </c>
-      <c r="I238" s="42" t="s">
-        <v>843</v>
+      <c r="H238" s="55">
+        <v>5.7</v>
+      </c>
+      <c r="I238" s="57" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -10018,13 +10310,13 @@
         <v>551</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="C239" s="55" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="D239" s="55" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="E239" s="56">
         <v>180</v>
@@ -10036,10 +10328,10 @@
         <v>220</v>
       </c>
       <c r="H239" s="55">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I239" s="57" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -10047,13 +10339,13 @@
         <v>552</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="C240" s="55" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="D240" s="55" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="E240" s="56">
         <v>190</v>
@@ -10065,10 +10357,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="39">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I240" s="57" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10076,10 +10368,10 @@
         <v>553</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="C241" s="55" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="D241" s="15" t="s">
         <v>554</v>
@@ -10097,7 +10389,7 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="58" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10105,13 +10397,13 @@
         <v>555</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="C242" s="55" t="s">
+        <v>864</v>
+      </c>
+      <c r="D242" s="55" t="s">
         <v>853</v>
-      </c>
-      <c r="D242" s="55" t="s">
-        <v>842</v>
       </c>
       <c r="E242" s="56">
         <v>160</v>
@@ -10126,7 +10418,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="57" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10134,13 +10426,13 @@
         <v>556</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="C243" s="55" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="D243" s="55" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="E243" s="56">
         <v>190</v>
@@ -10155,7 +10447,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="57" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10163,13 +10455,13 @@
         <v>557</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="C244" s="55" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="D244" s="55" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="E244" s="55">
         <v>150</v>
@@ -10201,13 +10493,13 @@
         <v>559</v>
       </c>
       <c r="B246" s="22" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="C246" s="22" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="D246" s="37" t="s">
-        <v>429</v>
+        <v>801</v>
       </c>
       <c r="E246" s="22">
         <v>112</v>
@@ -10228,7 +10520,7 @@
         <v>560</v>
       </c>
       <c r="B247" s="22" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="C247" s="22" t="s">
         <v>529</v>
@@ -10255,7 +10547,7 @@
         <v>561</v>
       </c>
       <c r="B248" s="22" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="C248" s="22" t="s">
         <v>562</v>
@@ -10282,10 +10574,10 @@
         <v>563</v>
       </c>
       <c r="B249" s="22" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="C249" s="22" t="s">
-        <v>439</v>
+        <v>877</v>
       </c>
       <c r="D249" s="22" t="s">
         <v>429</v>
@@ -10294,7 +10586,7 @@
         <v>105</v>
       </c>
       <c r="F249" s="60">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G249" s="36">
         <v>208</v>
@@ -10309,7 +10601,7 @@
         <v>564</v>
       </c>
       <c r="B250" s="22" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C250" s="22" t="s">
         <v>153</v>
@@ -10336,7 +10628,7 @@
         <v>565</v>
       </c>
       <c r="B251" s="22" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="C251" s="22" t="s">
         <v>566</v>
@@ -10363,10 +10655,10 @@
         <v>567</v>
       </c>
       <c r="B252" s="22" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="C252" s="22" t="s">
-        <v>439</v>
+        <v>877</v>
       </c>
       <c r="D252" s="22" t="s">
         <v>429</v>
@@ -10390,7 +10682,7 @@
         <v>568</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="C253" s="22" t="s">
         <v>566</v>
@@ -10417,13 +10709,13 @@
         <v>569</v>
       </c>
       <c r="B254" s="22" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="E254" s="22">
         <v>190</v>
@@ -10435,10 +10727,10 @@
         <v>215</v>
       </c>
       <c r="H254" s="22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I254" s="57" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10446,7 +10738,7 @@
         <v>570</v>
       </c>
       <c r="B255" s="22" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="C255" s="22" t="s">
         <v>571</v>
@@ -10473,13 +10765,13 @@
         <v>572</v>
       </c>
       <c r="B256" s="56" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="C256" s="22" t="s">
-        <v>161</v>
+        <v>886</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="E256" s="56">
         <v>190</v>
@@ -10494,7 +10786,7 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="57" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10502,13 +10794,13 @@
         <v>573</v>
       </c>
       <c r="B257" s="40" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="C257" s="40" t="s">
-        <v>321</v>
+        <v>890</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>429</v>
+        <v>801</v>
       </c>
       <c r="E257" s="40">
         <v>118</v>
@@ -10520,7 +10812,7 @@
         <v>215</v>
       </c>
       <c r="H257" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I257" s="10"/>
     </row>
@@ -10529,7 +10821,7 @@
         <v>574</v>
       </c>
       <c r="B258" s="22" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C258" s="22" t="s">
         <v>153</v>
@@ -10588,7 +10880,7 @@
         <v>579</v>
       </c>
       <c r="D261" s="53" t="s">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="E261" s="14">
         <v>108</v>
@@ -10609,7 +10901,7 @@
         <v>580</v>
       </c>
       <c r="B262" s="14" t="s">
-        <v>878</v>
+        <v>892</v>
       </c>
       <c r="C262" s="14" t="s">
         <v>581</v>
@@ -10717,13 +11009,13 @@
         <v>595</v>
       </c>
       <c r="B266" s="39" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="C266" s="39" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="D266" s="39" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="E266" s="39">
         <v>78</v>
@@ -10744,13 +11036,13 @@
         <v>596</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>881</v>
+        <v>895</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>882</v>
+        <v>896</v>
       </c>
       <c r="D267" s="53" t="s">
-        <v>144</v>
+        <v>897</v>
       </c>
       <c r="E267" s="14">
         <v>60</v>
@@ -10915,13 +11207,13 @@
         <v>610</v>
       </c>
       <c r="B278" s="31" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="C278" s="31" t="s">
-        <v>549</v>
+        <v>899</v>
       </c>
       <c r="D278" s="31" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="E278" s="31">
         <v>159</v>
@@ -10933,7 +11225,7 @@
         <v>212</v>
       </c>
       <c r="H278" s="31">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I278" s="10"/>
     </row>
@@ -10942,10 +11234,10 @@
         <v>611</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>885</v>
+        <v>901</v>
       </c>
       <c r="C279" s="53" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="D279" s="14" t="s">
         <v>144</v>
@@ -10969,13 +11261,13 @@
         <v>612</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="C280" s="53" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="D280" s="14" t="s">
-        <v>489</v>
+        <v>905</v>
       </c>
       <c r="E280" s="14"/>
       <c r="F280" s="13">
@@ -11021,7 +11313,7 @@
         <v>616</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="C282" s="53" t="s">
         <v>617</v>
@@ -11048,10 +11340,10 @@
         <v>618</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="C283" s="53" t="s">
-        <v>891</v>
+        <v>908</v>
       </c>
       <c r="D283" s="14" t="s">
         <v>39</v>
@@ -11075,13 +11367,13 @@
         <v>619</v>
       </c>
       <c r="B284" s="31" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="C284" s="40" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>894</v>
+        <v>911</v>
       </c>
       <c r="E284" s="40">
         <v>80</v>
@@ -11108,7 +11400,7 @@
         <v>622</v>
       </c>
       <c r="D285" s="40" t="s">
-        <v>894</v>
+        <v>911</v>
       </c>
       <c r="E285" s="14">
         <v>73</v>
@@ -11129,10 +11421,10 @@
         <v>623</v>
       </c>
       <c r="B286" s="56" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="C286" s="56" t="s">
-        <v>896</v>
+        <v>913</v>
       </c>
       <c r="D286" s="56" t="s">
         <v>624</v>
@@ -11156,13 +11448,13 @@
         <v>625</v>
       </c>
       <c r="B287" s="56" t="s">
-        <v>897</v>
+        <v>914</v>
       </c>
       <c r="C287" s="56" t="s">
-        <v>898</v>
+        <v>915</v>
       </c>
       <c r="D287" s="56" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
       <c r="E287" s="56">
         <v>88</v>
@@ -11174,7 +11466,7 @@
         <v>218</v>
       </c>
       <c r="H287" s="56">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I287" s="9"/>
     </row>
@@ -11183,7 +11475,7 @@
         <v>626</v>
       </c>
       <c r="B288" s="31" t="s">
-        <v>900</v>
+        <v>917</v>
       </c>
       <c r="C288" s="31" t="s">
         <v>627</v>
@@ -11231,7 +11523,7 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="15" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -11266,13 +11558,13 @@
         <v>635</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>902</v>
+        <v>919</v>
       </c>
       <c r="C291" s="64" t="s">
+        <v>920</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>636</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>637</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -11284,22 +11576,22 @@
         <v>220</v>
       </c>
       <c r="H291" s="64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I291" s="9"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>921</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>638</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>903</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>639</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>640</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -11317,13 +11609,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11344,16 +11636,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B294" s="22" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="C294" s="22" t="s">
-        <v>445</v>
+        <v>800</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="E294" s="22">
         <v>150</v>
@@ -11371,16 +11663,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>926</v>
+      </c>
+      <c r="C295" s="14" t="s">
         <v>643</v>
       </c>
-      <c r="B295" s="14" t="s">
-        <v>908</v>
-      </c>
-      <c r="C295" s="14" t="s">
+      <c r="D295" s="14" t="s">
         <v>644</v>
-      </c>
-      <c r="D295" s="14" t="s">
-        <v>645</v>
       </c>
       <c r="E295" s="14"/>
       <c r="F295" s="13"/>
@@ -11394,16 +11686,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="B296" s="39" t="s">
         <v>646</v>
       </c>
-      <c r="B296" s="39" t="s">
+      <c r="C296" s="39" t="s">
         <v>647</v>
       </c>
-      <c r="C296" s="39" t="s">
+      <c r="D296" s="39" t="s">
         <v>648</v>
-      </c>
-      <c r="D296" s="39" t="s">
-        <v>649</v>
       </c>
       <c r="E296" s="39"/>
       <c r="F296" s="40">
@@ -11419,16 +11711,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B297" s="22" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C297" s="22" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="D297" s="37" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="E297" s="22">
         <v>125</v>
@@ -11446,16 +11738,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B298" s="22" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="C298" s="22" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="D298" s="37" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="E298" s="22">
         <v>190</v>
@@ -11467,24 +11759,24 @@
         <v>225</v>
       </c>
       <c r="H298" s="22">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I298" s="15" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B299" s="55" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="C299" s="55" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="D299" s="55" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="E299" s="55">
         <v>124</v>
@@ -11499,12 +11791,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="58" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B300" s="40"/>
       <c r="C300" s="40"/>
@@ -11517,7 +11809,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B301" s="40"/>
       <c r="C301" s="40"/>
@@ -11530,16 +11822,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B302" s="15" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="E302" s="15">
         <v>150</v>
@@ -11557,16 +11849,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="B303" s="14" t="s">
         <v>656</v>
       </c>
-      <c r="B303" s="14" t="s">
+      <c r="C303" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="C303" s="14" t="s">
-        <v>658</v>
-      </c>
       <c r="D303" s="14" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="E303" s="15">
         <v>140</v>
@@ -11584,16 +11876,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>659</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>941</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>660</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>661</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11608,21 +11900,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="41" t="s">
-        <v>923</v>
+        <v>942</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B305" s="40" t="s">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="C305" s="40" t="s">
-        <v>925</v>
+        <v>944</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="E305" s="40">
         <v>215</v>
@@ -11634,13 +11926,13 @@
         <v>225</v>
       </c>
       <c r="H305" s="9">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I305" s="9"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B306" s="40"/>
       <c r="C306" s="40"/>
@@ -11653,7 +11945,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B307" s="40"/>
       <c r="C307" s="40"/>
@@ -11666,7 +11958,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B308" s="40"/>
       <c r="C308" s="40"/>
@@ -11679,7 +11971,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B309" s="40"/>
       <c r="C309" s="40"/>
@@ -11692,7 +11984,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="13" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B310" s="40"/>
       <c r="C310" s="40"/>
@@ -11705,16 +11997,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="39" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="39" t="s">
-        <v>669</v>
-      </c>
       <c r="C311" s="39" t="s">
+        <v>946</v>
+      </c>
+      <c r="D311" s="39" t="s">
         <v>670</v>
-      </c>
-      <c r="D311" s="39" t="s">
-        <v>671</v>
       </c>
       <c r="E311" s="39">
         <v>85</v>
@@ -11732,16 +12024,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="B312" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="B312" s="14" t="s">
+      <c r="C312" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="D312" s="14" t="s">
         <v>673</v>
-      </c>
-      <c r="C312" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="D312" s="14" t="s">
-        <v>674</v>
       </c>
       <c r="E312" s="14">
         <v>73</v>
@@ -11759,7 +12051,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B313" s="40"/>
       <c r="C313" s="40"/>
@@ -11772,7 +12064,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B314" s="40"/>
       <c r="C314" s="40"/>
@@ -11785,16 +12077,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B315" s="40" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="C315" s="40" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="E315" s="40">
         <v>116</v>
@@ -11809,21 +12101,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="9" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B316" s="40" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="C316" s="40" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="E316" s="40">
         <v>160</v>
@@ -11838,21 +12130,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="E317" s="15">
         <v>110</v>
@@ -11867,21 +12159,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="15" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="E318" s="15">
         <v>110</v>
@@ -11899,16 +12191,16 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B319" s="22" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="C319" s="22" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="E319" s="22">
         <v>205</v>
@@ -11920,24 +12212,24 @@
         <v>215</v>
       </c>
       <c r="H319" s="22">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I319" s="15" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B320" s="22" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="C320" s="22" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="E320" s="22">
         <v>182</v>
@@ -11949,24 +12241,24 @@
         <v>220</v>
       </c>
       <c r="H320" s="22">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I320" s="15" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B321" s="22" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="C321" s="22" t="s">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="E321" s="22">
         <v>138</v>
@@ -11981,21 +12273,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="15" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B322" s="22" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="C322" s="22" t="s">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="E322" s="22">
         <v>225</v>
@@ -12007,24 +12299,24 @@
         <v>215</v>
       </c>
       <c r="H322" s="22">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I322" s="15" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B323" s="22" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="C323" s="22" t="s">
-        <v>88</v>
+        <v>974</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="E323" s="22">
         <v>155</v>
@@ -12039,21 +12331,21 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="15" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B324" s="22" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="C324" s="22" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="E324" s="22">
         <v>220</v>
@@ -12065,15 +12357,15 @@
         <v>218</v>
       </c>
       <c r="H324" s="22">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I324" s="15" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B325" s="40"/>
       <c r="C325" s="40"/>
@@ -12086,7 +12378,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B326" s="40"/>
       <c r="C326" s="40"/>
@@ -12099,7 +12391,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B327" s="40"/>
       <c r="C327" s="40"/>
@@ -12112,7 +12404,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B328" s="40"/>
       <c r="C328" s="40"/>
@@ -12125,7 +12417,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B329" s="40"/>
       <c r="C329" s="40"/>
@@ -12138,7 +12430,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="13" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B330" s="40"/>
       <c r="C330" s="40"/>
@@ -12151,7 +12443,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B331" s="40"/>
       <c r="C331" s="40"/>
@@ -12164,7 +12456,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B332" s="40"/>
       <c r="C332" s="40"/>
@@ -12177,7 +12469,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B333" s="40"/>
       <c r="C333" s="40"/>
@@ -12190,7 +12482,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="13" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B334" s="40"/>
       <c r="C334" s="40"/>
@@ -12203,7 +12495,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B335" s="40"/>
       <c r="C335" s="40"/>
@@ -12216,7 +12508,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B336" s="40"/>
       <c r="C336" s="40"/>
@@ -12229,7 +12521,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B337" s="40"/>
       <c r="C337" s="40"/>
@@ -12242,7 +12534,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B338" s="40"/>
       <c r="C338" s="40"/>
@@ -12255,7 +12547,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B339" s="40"/>
       <c r="C339" s="40"/>
@@ -12268,7 +12560,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B340" s="40"/>
       <c r="C340" s="40"/>
@@ -12281,7 +12573,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B341" s="40"/>
       <c r="C341" s="40"/>
@@ -12294,7 +12586,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B342" s="40"/>
       <c r="C342" s="40"/>
@@ -12307,7 +12599,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B343" s="40"/>
       <c r="C343" s="40"/>
@@ -12320,7 +12612,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B344" s="40"/>
       <c r="C344" s="40"/>
@@ -12333,7 +12625,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B345" s="40"/>
       <c r="C345" s="40"/>
@@ -12346,7 +12638,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B346" s="40"/>
       <c r="C346" s="40"/>
@@ -12359,7 +12651,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B347" s="40"/>
       <c r="C347" s="40"/>
@@ -12372,7 +12664,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B348" s="40"/>
       <c r="C348" s="40"/>
@@ -12385,7 +12677,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B349" s="40"/>
       <c r="C349" s="40"/>
@@ -12398,7 +12690,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B350" s="40"/>
       <c r="C350" s="40"/>
@@ -12411,7 +12703,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B351" s="40"/>
       <c r="C351" s="40"/>
@@ -12424,7 +12716,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B352" s="40"/>
       <c r="C352" s="40"/>
@@ -12437,7 +12729,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B353" s="40"/>
       <c r="C353" s="40"/>
@@ -12450,7 +12742,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B354" s="40"/>
       <c r="C354" s="40"/>
@@ -12463,7 +12755,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B355" s="40"/>
       <c r="C355" s="40"/>
@@ -12476,7 +12768,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B356" s="40"/>
       <c r="C356" s="40"/>
@@ -12489,7 +12781,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B357" s="40"/>
       <c r="C357" s="40"/>
@@ -12502,7 +12794,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B358" s="40"/>
       <c r="C358" s="40"/>
@@ -12515,7 +12807,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B359" s="40"/>
       <c r="C359" s="40"/>
@@ -12528,7 +12820,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B360" s="40"/>
       <c r="C360" s="40"/>
@@ -12541,7 +12833,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B361" s="40"/>
       <c r="C361" s="40"/>
@@ -12554,7 +12846,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B362" s="40"/>
       <c r="C362" s="40"/>
@@ -12567,7 +12859,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B363" s="40"/>
       <c r="C363" s="40"/>
@@ -12580,7 +12872,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B364" s="40"/>
       <c r="C364" s="40"/>
@@ -12593,7 +12885,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B365" s="40"/>
       <c r="C365" s="40"/>
@@ -12606,7 +12898,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B366" s="40"/>
       <c r="C366" s="40"/>
@@ -12619,7 +12911,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B367" s="40"/>
       <c r="C367" s="40"/>
@@ -12632,7 +12924,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="13" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B368" s="40"/>
       <c r="C368" s="40"/>
@@ -12645,7 +12937,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B369" s="40"/>
       <c r="C369" s="40"/>
@@ -12658,7 +12950,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B370" s="40"/>
       <c r="C370" s="40"/>
@@ -12671,7 +12963,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B371" s="40"/>
       <c r="C371" s="40"/>
@@ -12684,7 +12976,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B372" s="40"/>
       <c r="C372" s="40"/>
@@ -12697,7 +12989,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B373" s="40"/>
       <c r="C373" s="40"/>
@@ -12710,7 +13002,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B374" s="40"/>
       <c r="C374" s="40"/>
@@ -12723,7 +13015,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B375" s="40"/>
       <c r="C375" s="40"/>
@@ -12736,7 +13028,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B376" s="40"/>
       <c r="C376" s="40"/>
@@ -12749,7 +13041,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B377" s="40"/>
       <c r="C377" s="40"/>
@@ -12762,7 +13054,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B378" s="40"/>
       <c r="C378" s="40"/>
@@ -12775,7 +13067,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B379" s="40"/>
       <c r="C379" s="40"/>
@@ -12788,7 +13080,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B380" s="40"/>
       <c r="C380" s="40"/>
@@ -12801,7 +13093,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B381" s="40"/>
       <c r="C381" s="40"/>
@@ -12814,7 +13106,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B382" s="40"/>
       <c r="C382" s="40"/>
@@ -12827,7 +13119,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B383" s="40"/>
       <c r="C383" s="40"/>
@@ -12840,7 +13132,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B384" s="40"/>
       <c r="C384" s="40"/>
@@ -12853,7 +13145,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B385" s="40"/>
       <c r="C385" s="40"/>
@@ -12866,7 +13158,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B386" s="40"/>
       <c r="C386" s="40"/>
@@ -12879,7 +13171,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B387" s="40"/>
       <c r="C387" s="40"/>
@@ -12892,7 +13184,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="13" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B388" s="40"/>
       <c r="C388" s="40"/>
@@ -12905,7 +13197,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B389" s="40"/>
       <c r="C389" s="40"/>
@@ -12918,7 +13210,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B390" s="40"/>
       <c r="C390" s="40"/>
@@ -12931,7 +13223,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B391" s="40"/>
       <c r="C391" s="40"/>
@@ -12944,7 +13236,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B392" s="40"/>
       <c r="C392" s="40"/>
@@ -12957,7 +13249,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B393" s="40"/>
       <c r="C393" s="40"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="964">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1228,9 +1228,6 @@
   </si>
   <si>
     <t>T400王者归来</t>
-  </si>
-  <si>
-    <t>18*3*47</t>
   </si>
   <si>
     <t>XC158</t>
@@ -2382,515 +2379,11 @@
     <t>XC392</t>
   </si>
   <si>
-    <t>XC001</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>1*1半光横条</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*2*25</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*26</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*50S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*40S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>13.5*4*35</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC186</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75DT400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*215*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*150T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*46</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75消*75T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*5*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*3*39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>X字格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*46</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条2*1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4+28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>238克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*4</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4+38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯200米克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75闪电斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*28</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*2T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克385</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*35</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平0.5格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>17*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克370</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平3/3斜-45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*45</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克375</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>15*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克300</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克350</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*29</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*150T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克380</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平牛津</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*34</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*300T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克368</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D酷丝绵变化斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*210</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*2*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -3226,6 +2719,345 @@
   <si>
     <t>16*4*31</t>
     <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC001</t>
+  </si>
+  <si>
+    <t>1*1半光横条</t>
+  </si>
+  <si>
+    <t>22*3*38</t>
+  </si>
+  <si>
+    <t>22*3*39</t>
+  </si>
+  <si>
+    <t>14*2*25</t>
+  </si>
+  <si>
+    <t>17*3*28</t>
+  </si>
+  <si>
+    <t>17*3*44</t>
+  </si>
+  <si>
+    <t>25梭T400无捻牛津</t>
+  </si>
+  <si>
+    <t>27梭T400无捻牛津</t>
+  </si>
+  <si>
+    <t>26梭T400无捻牛津</t>
+  </si>
+  <si>
+    <t>17*2*26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>17*2*30</t>
+  </si>
+  <si>
+    <t>50S*50S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>40S*40S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+  </si>
+  <si>
+    <t>50S*75D 酷丝棉绮兵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+  </si>
+  <si>
+    <t>XC186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+  </si>
+  <si>
+    <t>40S*75DT400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+  </si>
+  <si>
+    <t>100*150T8 4/2斜</t>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+  </si>
+  <si>
+    <t>100D*150T800</t>
+  </si>
+  <si>
+    <t>75*150T400 消3/3斜</t>
+  </si>
+  <si>
+    <t>75*75T400消 3/3斜</t>
+  </si>
+  <si>
+    <t>75*75 半光2/2 斜</t>
+  </si>
+  <si>
+    <t>18*4*46</t>
+  </si>
+  <si>
+    <t>75*75 消光2/2 斜</t>
+  </si>
+  <si>
+    <t>75*150 消光2/2 斜</t>
+  </si>
+  <si>
+    <t>75*75-T800消光骑士斜</t>
+  </si>
+  <si>
+    <t>75消*75T800</t>
+  </si>
+  <si>
+    <t>19*5*45</t>
+  </si>
+  <si>
+    <t>19*3*39</t>
+  </si>
+  <si>
+    <t>X字格</t>
+  </si>
+  <si>
+    <t>16*4*46</t>
+  </si>
+  <si>
+    <t>T400横条2*1</t>
+  </si>
+  <si>
+    <t>16*4+28</t>
+  </si>
+  <si>
+    <t>238克</t>
+  </si>
+  <si>
+    <t>T400横条1*4</t>
+  </si>
+  <si>
+    <t>17*4+38</t>
+  </si>
+  <si>
+    <t>白坯200米克</t>
+  </si>
+  <si>
+    <t>T400横条1*1</t>
+  </si>
+  <si>
+    <t>16*4*30</t>
+  </si>
+  <si>
+    <t>40S*75闪电斜</t>
+  </si>
+  <si>
+    <t>18*3*38</t>
+  </si>
+  <si>
+    <t>40S*75</t>
+  </si>
+  <si>
+    <t>40S*150酷丝绵 小钻石斜</t>
+  </si>
+  <si>
+    <t>40S*150酷丝绵 大钻石斜</t>
+  </si>
+  <si>
+    <t>40S*300 3/2变化斜</t>
+  </si>
+  <si>
+    <t>13.5*4*28</t>
+  </si>
+  <si>
+    <t>40S*150*2T400</t>
+  </si>
+  <si>
+    <t>米克385</t>
+  </si>
+  <si>
+    <t>100D半光*35S-3/3斜</t>
+  </si>
+  <si>
+    <t>16*4*40</t>
+  </si>
+  <si>
+    <t>100*35</t>
+  </si>
+  <si>
+    <t>100D消光*35S-3/3斜</t>
+  </si>
+  <si>
+    <t>100*35S</t>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
+  </si>
+  <si>
+    <t>17*4*44</t>
+  </si>
+  <si>
+    <t>120*35S</t>
+  </si>
+  <si>
+    <t>米克370</t>
+  </si>
+  <si>
+    <t>120D扁平3/3斜-45</t>
+  </si>
+  <si>
+    <t>16*4*45</t>
+  </si>
+  <si>
+    <t>120D扁平4/4斜</t>
+  </si>
+  <si>
+    <t>17*4*45</t>
+  </si>
+  <si>
+    <t>米克375</t>
+  </si>
+  <si>
+    <t>100D消光多乐3/3斜</t>
+  </si>
+  <si>
+    <t>15*4*43</t>
+  </si>
+  <si>
+    <t>米克300</t>
+  </si>
+  <si>
+    <t>120D扁平1/2斜</t>
+  </si>
+  <si>
+    <t>17*4*34</t>
+  </si>
+  <si>
+    <t>米克350</t>
+  </si>
+  <si>
+    <t>120D扁平T800变化斜</t>
+  </si>
+  <si>
+    <t>17*4*29</t>
+  </si>
+  <si>
+    <t>120*150T800</t>
+  </si>
+  <si>
+    <t>米克380</t>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+  </si>
+  <si>
+    <t>13.5*4*34</t>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/1斜 31</t>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/2斜 39</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1 30</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+  </si>
+  <si>
+    <t>40S*300 酷丝棉3/2斜</t>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+  </si>
+  <si>
+    <t>40S*300酷丝绵珍珠点</t>
+  </si>
+  <si>
+    <t>40S*150*300T400</t>
+  </si>
+  <si>
+    <t>米克368</t>
+  </si>
+  <si>
+    <t>40S*75D酷丝绵变化斜</t>
+  </si>
+  <si>
+    <t>40S*150T400+300T400</t>
+  </si>
+  <si>
+    <t>80S*75双线格酷丝绵</t>
+  </si>
+  <si>
+    <t>75 T800半光0.5格</t>
+  </si>
+  <si>
+    <t>75*75*210</t>
+  </si>
+  <si>
+    <t>50D经纬 T8 0.5格</t>
+  </si>
+  <si>
+    <t>22*2*40</t>
   </si>
 </sst>
 </file>
@@ -4363,54 +4195,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>698</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>689</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="13" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>771</v>
+        <v>852</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>772</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14">
         <v>79</v>
@@ -4424,13 +4256,13 @@
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5097,7 +4929,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>773</v>
+        <v>853</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>46</v>
@@ -5122,7 +4954,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>774</v>
+        <v>854</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>46</v>
@@ -5774,7 +5606,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>775</v>
+        <v>855</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>135</v>
@@ -6301,7 +6133,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>776</v>
+        <v>73</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>144</v>
@@ -6464,7 +6296,7 @@
         <v>165</v>
       </c>
       <c r="H83" s="14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I83" s="15"/>
     </row>
@@ -7651,7 +7483,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>777</v>
+        <v>856</v>
       </c>
       <c r="D131" s="28" t="s">
         <v>148</v>
@@ -7664,7 +7496,7 @@
         <v>165</v>
       </c>
       <c r="H131" s="28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I131" s="15"/>
     </row>
@@ -7912,7 +7744,7 @@
         <v>165</v>
       </c>
       <c r="H141" s="30">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I141" s="15"/>
     </row>
@@ -8336,7 +8168,7 @@
         <v>403</v>
       </c>
       <c r="C158" s="31" t="s">
-        <v>404</v>
+        <v>857</v>
       </c>
       <c r="D158" s="31" t="s">
         <v>393</v>
@@ -8357,13 +8189,13 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B159" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="C159" s="14" t="s">
         <v>406</v>
-      </c>
-      <c r="C159" s="14" t="s">
-        <v>407</v>
       </c>
       <c r="D159" s="14" t="s">
         <v>135</v>
@@ -8382,16 +8214,16 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B160" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="C160" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="D160" s="14" t="s">
         <v>410</v>
-      </c>
-      <c r="D160" s="14" t="s">
-        <v>411</v>
       </c>
       <c r="E160" s="14">
         <v>85</v>
@@ -8407,16 +8239,16 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>858</v>
+      </c>
+      <c r="C161" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="B161" s="26" t="s">
-        <v>778</v>
-      </c>
-      <c r="C161" s="26" t="s">
+      <c r="D161" s="26" t="s">
         <v>413</v>
-      </c>
-      <c r="D161" s="26" t="s">
-        <v>414</v>
       </c>
       <c r="E161" s="26">
         <v>104</v>
@@ -8434,16 +8266,16 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="B162" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="B162" s="26" t="s">
+      <c r="C162" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="C162" s="26" t="s">
-        <v>417</v>
-      </c>
       <c r="D162" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E162" s="26">
         <v>117</v>
@@ -8461,16 +8293,16 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B163" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="B163" s="26" t="s">
+      <c r="C163" s="26" t="s">
         <v>419</v>
       </c>
-      <c r="C163" s="26" t="s">
-        <v>420</v>
-      </c>
       <c r="D163" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E163" s="26">
         <v>117</v>
@@ -8488,16 +8320,16 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>859</v>
+      </c>
+      <c r="C164" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="B164" s="26" t="s">
-        <v>779</v>
-      </c>
-      <c r="C164" s="26" t="s">
-        <v>422</v>
-      </c>
       <c r="D164" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E164" s="26">
         <v>110</v>
@@ -8515,16 +8347,16 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B165" s="26" t="s">
-        <v>780</v>
+        <v>860</v>
       </c>
       <c r="C165" s="26" t="s">
-        <v>781</v>
+        <v>861</v>
       </c>
       <c r="D165" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E165" s="26">
         <v>108</v>
@@ -8542,7 +8374,7 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B166" s="34"/>
       <c r="C166" s="34"/>
@@ -8555,16 +8387,16 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>782</v>
+        <v>862</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>783</v>
+        <v>863</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>784</v>
+        <v>864</v>
       </c>
       <c r="E167" s="22">
         <v>80</v>
@@ -8582,16 +8414,16 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>785</v>
+        <v>865</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>786</v>
+        <v>416</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>787</v>
+        <v>866</v>
       </c>
       <c r="E168" s="22">
         <v>110</v>
@@ -8609,16 +8441,16 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="B169" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="C169" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="B169" s="22" t="s">
-        <v>788</v>
-      </c>
-      <c r="C169" s="22" t="s">
+      <c r="D169" s="22" t="s">
         <v>428</v>
-      </c>
-      <c r="D169" s="22" t="s">
-        <v>429</v>
       </c>
       <c r="E169" s="22">
         <v>83</v>
@@ -8636,16 +8468,16 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="35" t="s">
+        <v>429</v>
+      </c>
+      <c r="B170" s="22" t="s">
+        <v>868</v>
+      </c>
+      <c r="C170" s="22" t="s">
         <v>430</v>
       </c>
-      <c r="B170" s="22" t="s">
-        <v>789</v>
-      </c>
-      <c r="C170" s="22" t="s">
-        <v>431</v>
-      </c>
       <c r="D170" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E170" s="36">
         <v>110</v>
@@ -8663,16 +8495,16 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>790</v>
+        <v>869</v>
       </c>
       <c r="C171" s="22" t="s">
         <v>238</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E171" s="36">
         <v>112</v>
@@ -8690,16 +8522,16 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="B172" s="22" t="s">
         <v>433</v>
-      </c>
-      <c r="B172" s="22" t="s">
-        <v>434</v>
       </c>
       <c r="C172" s="22" t="s">
         <v>238</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E172" s="22">
         <v>112</v>
@@ -8717,16 +8549,16 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="B173" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="C173" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="B173" s="22" t="s">
-        <v>791</v>
-      </c>
-      <c r="C173" s="22" t="s">
+      <c r="D173" s="22" t="s">
         <v>436</v>
-      </c>
-      <c r="D173" s="22" t="s">
-        <v>437</v>
       </c>
       <c r="E173" s="22">
         <v>102</v>
@@ -8744,16 +8576,16 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="B174" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="C174" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="B174" s="22" t="s">
-        <v>792</v>
-      </c>
-      <c r="C174" s="22" t="s">
-        <v>439</v>
-      </c>
       <c r="D174" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E174" s="36">
         <v>130</v>
@@ -8765,22 +8597,22 @@
         <v>215</v>
       </c>
       <c r="H174" s="36">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I174" s="36"/>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>793</v>
+        <v>872</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E175" s="36">
         <v>135</v>
@@ -8792,22 +8624,22 @@
         <v>215</v>
       </c>
       <c r="H175" s="36">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I175" s="36"/>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="B176" s="22" t="s">
         <v>441</v>
-      </c>
-      <c r="B176" s="22" t="s">
-        <v>442</v>
       </c>
       <c r="C176" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E176" s="22">
         <v>135</v>
@@ -8819,22 +8651,22 @@
         <v>215</v>
       </c>
       <c r="H176" s="22">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I176" s="36"/>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="B177" s="22" t="s">
         <v>443</v>
       </c>
-      <c r="B177" s="22" t="s">
+      <c r="C177" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="C177" s="22" t="s">
-        <v>445</v>
-      </c>
       <c r="D177" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E177" s="22">
         <v>150</v>
@@ -8852,16 +8684,16 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="35" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>794</v>
+        <v>873</v>
       </c>
       <c r="C178" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E178" s="22">
         <v>106</v>
@@ -8879,16 +8711,16 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="B179" s="22" t="s">
         <v>447</v>
       </c>
-      <c r="B179" s="22" t="s">
+      <c r="C179" s="22" t="s">
         <v>448</v>
       </c>
-      <c r="C179" s="22" t="s">
-        <v>449</v>
-      </c>
       <c r="D179" s="37" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E179" s="22">
         <v>110</v>
@@ -8906,16 +8738,16 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="B180" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="C180" s="22" t="s">
         <v>450</v>
       </c>
-      <c r="B180" s="22" t="s">
-        <v>795</v>
-      </c>
-      <c r="C180" s="22" t="s">
-        <v>451</v>
-      </c>
       <c r="D180" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E180" s="22">
         <v>96</v>
@@ -8933,16 +8765,16 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>796</v>
+        <v>875</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E181" s="22">
         <v>150</v>
@@ -8960,16 +8792,16 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B182" s="38" t="s">
-        <v>797</v>
+        <v>876</v>
       </c>
       <c r="C182" s="38" t="s">
         <v>309</v>
       </c>
       <c r="D182" s="38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E182" s="38">
         <v>108</v>
@@ -8987,16 +8819,16 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B183" s="38" t="s">
-        <v>798</v>
+        <v>877</v>
       </c>
       <c r="C183" s="38" t="s">
         <v>309</v>
       </c>
       <c r="D183" s="38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E183" s="38">
         <v>108</v>
@@ -9014,16 +8846,16 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="B184" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="B184" s="39" t="s">
+      <c r="C184" s="39" t="s">
         <v>457</v>
       </c>
-      <c r="C184" s="39" t="s">
+      <c r="D184" s="39" t="s">
         <v>458</v>
-      </c>
-      <c r="D184" s="39" t="s">
-        <v>459</v>
       </c>
       <c r="E184" s="39">
         <v>150</v>
@@ -9041,16 +8873,16 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>799</v>
+        <v>878</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>800</v>
+        <v>444</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>801</v>
+        <v>428</v>
       </c>
       <c r="E185" s="22">
         <v>112</v>
@@ -9068,16 +8900,16 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B186" s="38" t="s">
-        <v>802</v>
+        <v>879</v>
       </c>
       <c r="C186" s="38" t="s">
         <v>309</v>
       </c>
       <c r="D186" s="38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E186" s="38">
         <v>108</v>
@@ -9095,16 +8927,16 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="13" t="s">
-        <v>803</v>
+        <v>880</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>804</v>
+        <v>238</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E187" s="22">
         <v>150</v>
@@ -9122,16 +8954,16 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>805</v>
+        <v>881</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>806</v>
+        <v>272</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>807</v>
+        <v>882</v>
       </c>
       <c r="E188" s="22">
         <v>110</v>
@@ -9149,16 +8981,16 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>808</v>
+        <v>883</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E189" s="22">
         <v>150</v>
@@ -9176,16 +9008,16 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>809</v>
+        <v>884</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>810</v>
+        <v>885</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>811</v>
+        <v>886</v>
       </c>
       <c r="E190" s="15">
         <v>152</v>
@@ -9197,22 +9029,22 @@
         <v>215</v>
       </c>
       <c r="H190" s="14">
-        <v>5.0999999999999996</v>
+        <v>5.4</v>
       </c>
       <c r="I190" s="15"/>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>793</v>
+        <v>872</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>804</v>
+        <v>238</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E191" s="36">
         <v>150</v>
@@ -9230,7 +9062,7 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B192" s="31"/>
       <c r="C192" s="31"/>
@@ -9243,7 +9075,7 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B193" s="31"/>
       <c r="C193" s="31"/>
@@ -9256,13 +9088,13 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B194" s="45" t="s">
-        <v>812</v>
+        <v>887</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>813</v>
+        <v>385</v>
       </c>
       <c r="D194" s="47" t="s">
         <v>148</v>
@@ -9283,13 +9115,13 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="B195" s="45" t="s">
+        <v>888</v>
+      </c>
+      <c r="C195" s="46" t="s">
         <v>469</v>
-      </c>
-      <c r="B195" s="45" t="s">
-        <v>814</v>
-      </c>
-      <c r="C195" s="46" t="s">
-        <v>470</v>
       </c>
       <c r="D195" s="47" t="s">
         <v>39</v>
@@ -9310,16 +9142,16 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="B196" s="49" t="s">
+        <v>889</v>
+      </c>
+      <c r="C196" s="49" t="s">
+        <v>890</v>
+      </c>
+      <c r="D196" s="49" t="s">
         <v>471</v>
-      </c>
-      <c r="B196" s="49" t="s">
-        <v>815</v>
-      </c>
-      <c r="C196" s="49" t="s">
-        <v>816</v>
-      </c>
-      <c r="D196" s="49" t="s">
-        <v>472</v>
       </c>
       <c r="E196" s="49">
         <v>105</v>
@@ -9337,13 +9169,13 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B197" s="49" t="s">
-        <v>817</v>
+        <v>891</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>818</v>
+        <v>389</v>
       </c>
       <c r="D197" s="49" t="s">
         <v>386</v>
@@ -9364,16 +9196,16 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B198" s="49" t="s">
+        <v>892</v>
+      </c>
+      <c r="C198" s="49" t="s">
         <v>474</v>
       </c>
-      <c r="B198" s="49" t="s">
-        <v>819</v>
-      </c>
-      <c r="C198" s="49" t="s">
+      <c r="D198" s="49" t="s">
         <v>475</v>
-      </c>
-      <c r="D198" s="49" t="s">
-        <v>476</v>
       </c>
       <c r="E198" s="49">
         <v>129</v>
@@ -9391,16 +9223,16 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>820</v>
+        <v>893</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>821</v>
+        <v>401</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>822</v>
+        <v>894</v>
       </c>
       <c r="E199" s="49">
         <v>95</v>
@@ -9418,7 +9250,7 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B200" s="34"/>
       <c r="C200" s="34"/>
@@ -9431,7 +9263,7 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -9444,7 +9276,7 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -9457,7 +9289,7 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -9470,16 +9302,16 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="B204" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="B204" s="28" t="s">
+      <c r="C204" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="C204" s="28" t="s">
+      <c r="D204" s="28" t="s">
         <v>484</v>
-      </c>
-      <c r="D204" s="28" t="s">
-        <v>485</v>
       </c>
       <c r="E204" s="28"/>
       <c r="F204" s="51">
@@ -9495,16 +9327,16 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="B205" s="28" t="s">
         <v>486</v>
       </c>
-      <c r="B205" s="28" t="s">
+      <c r="C205" s="28" t="s">
         <v>487</v>
       </c>
-      <c r="C205" s="28" t="s">
+      <c r="D205" s="52" t="s">
         <v>488</v>
-      </c>
-      <c r="D205" s="52" t="s">
-        <v>489</v>
       </c>
       <c r="E205" s="28">
         <v>47</v>
@@ -9522,16 +9354,16 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="B206" s="28" t="s">
         <v>490</v>
       </c>
-      <c r="B206" s="28" t="s">
+      <c r="C206" s="28" t="s">
         <v>491</v>
       </c>
-      <c r="C206" s="28" t="s">
-        <v>492</v>
-      </c>
       <c r="D206" s="52" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E206" s="28">
         <v>47</v>
@@ -9549,10 +9381,10 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="B207" s="31" t="s">
         <v>493</v>
-      </c>
-      <c r="B207" s="31" t="s">
-        <v>494</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>53</v>
@@ -9572,22 +9404,22 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="B208" s="31" t="s">
         <v>495</v>
       </c>
-      <c r="B208" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="C208" s="14" t="s">
-        <v>823</v>
+        <v>895</v>
       </c>
       <c r="D208" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E208" s="14">
+        <v>125</v>
+      </c>
+      <c r="F208" s="40">
         <v>145</v>
-      </c>
-      <c r="F208" s="40">
-        <v>150</v>
       </c>
       <c r="G208" s="15">
         <v>170</v>
@@ -9599,10 +9431,10 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="B209" s="14" t="s">
         <v>497</v>
-      </c>
-      <c r="B209" s="14" t="s">
-        <v>498</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>153</v>
@@ -9622,7 +9454,7 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -9635,13 +9467,13 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="B211" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="B211" s="14" t="s">
-        <v>501</v>
-      </c>
       <c r="C211" s="14" t="s">
-        <v>824</v>
+        <v>896</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>39</v>
@@ -9660,13 +9492,13 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B212" s="39" t="s">
-        <v>825</v>
+        <v>897</v>
       </c>
       <c r="C212" s="39" t="s">
-        <v>826</v>
+        <v>898</v>
       </c>
       <c r="D212" s="39" t="s">
         <v>144</v>
@@ -9685,16 +9517,16 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="B213" s="14" t="s">
         <v>503</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="C213" s="14" t="s">
         <v>504</v>
       </c>
-      <c r="C213" s="14" t="s">
-        <v>505</v>
-      </c>
       <c r="D213" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E213" s="14">
         <v>52</v>
@@ -9712,13 +9544,13 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="B214" s="14" t="s">
         <v>506</v>
       </c>
-      <c r="B214" s="14" t="s">
-        <v>507</v>
-      </c>
       <c r="C214" s="39" t="s">
-        <v>826</v>
+        <v>898</v>
       </c>
       <c r="D214" s="39" t="s">
         <v>144</v>
@@ -9737,7 +9569,7 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B215" s="34"/>
       <c r="C215" s="34"/>
@@ -9750,16 +9582,16 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="B216" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="B216" s="14" t="s">
+      <c r="C216" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="C216" s="14" t="s">
+      <c r="D216" s="14" t="s">
         <v>511</v>
-      </c>
-      <c r="D216" s="14" t="s">
-        <v>512</v>
       </c>
       <c r="E216" s="14">
         <v>69</v>
@@ -9775,7 +9607,7 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B217" s="34"/>
       <c r="C217" s="34"/>
@@ -9788,7 +9620,7 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -9801,16 +9633,16 @@
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="B219" s="39" t="s">
         <v>515</v>
       </c>
-      <c r="B219" s="39" t="s">
+      <c r="C219" s="39" t="s">
         <v>516</v>
       </c>
-      <c r="C219" s="39" t="s">
+      <c r="D219" s="39" t="s">
         <v>517</v>
-      </c>
-      <c r="D219" s="39" t="s">
-        <v>518</v>
       </c>
       <c r="E219" s="39">
         <v>90</v>
@@ -9828,16 +9660,16 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B220" s="14" t="s">
+        <v>899</v>
+      </c>
+      <c r="C220" s="14" t="s">
+        <v>900</v>
+      </c>
+      <c r="D220" s="53" t="s">
         <v>519</v>
-      </c>
-      <c r="B220" s="14" t="s">
-        <v>827</v>
-      </c>
-      <c r="C220" s="14" t="s">
-        <v>828</v>
-      </c>
-      <c r="D220" s="53" t="s">
-        <v>520</v>
       </c>
       <c r="E220" s="14">
         <v>120</v>
@@ -9852,21 +9684,21 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="15" t="s">
-        <v>829</v>
+        <v>901</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>830</v>
+        <v>902</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>831</v>
+        <v>903</v>
       </c>
       <c r="D221" s="53" t="s">
-        <v>832</v>
+        <v>1</v>
       </c>
       <c r="E221" s="14">
         <v>100</v>
@@ -9881,21 +9713,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="41" t="s">
-        <v>833</v>
+        <v>904</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>834</v>
+        <v>905</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>835</v>
+        <v>906</v>
       </c>
       <c r="D222" s="53" t="s">
-        <v>836</v>
+        <v>519</v>
       </c>
       <c r="E222" s="14">
         <v>115</v>
@@ -9913,13 +9745,13 @@
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="B223" s="39" t="s">
         <v>523</v>
       </c>
-      <c r="B223" s="39" t="s">
+      <c r="C223" s="39" t="s">
         <v>524</v>
-      </c>
-      <c r="C223" s="39" t="s">
-        <v>525</v>
       </c>
       <c r="D223" s="54" t="s">
         <v>1</v>
@@ -9940,16 +9772,16 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" s="13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B224" s="39" t="s">
-        <v>837</v>
+        <v>907</v>
       </c>
       <c r="C224" s="39" t="s">
-        <v>838</v>
+        <v>908</v>
       </c>
       <c r="D224" s="39" t="s">
-        <v>839</v>
+        <v>909</v>
       </c>
       <c r="E224" s="39">
         <v>120</v>
@@ -9967,16 +9799,16 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="B225" s="31" t="s">
         <v>527</v>
       </c>
-      <c r="B225" s="31" t="s">
+      <c r="C225" s="39" t="s">
         <v>528</v>
       </c>
-      <c r="C225" s="39" t="s">
-        <v>529</v>
-      </c>
       <c r="D225" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E225" s="39">
         <v>135</v>
@@ -9994,16 +9826,16 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B226" s="39" t="s">
-        <v>840</v>
+        <v>910</v>
       </c>
       <c r="C226" s="39" t="s">
-        <v>804</v>
+        <v>238</v>
       </c>
       <c r="D226" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E226" s="39">
         <v>145</v>
@@ -10021,16 +9853,16 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B227" s="39" t="s">
-        <v>841</v>
+        <v>911</v>
       </c>
       <c r="C227" s="39" t="s">
-        <v>804</v>
+        <v>238</v>
       </c>
       <c r="D227" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E227" s="39">
         <v>145</v>
@@ -10048,16 +9880,16 @@
     </row>
     <row r="228" spans="1:9">
       <c r="A228" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B228" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="B228" s="39" t="s">
-        <v>533</v>
-      </c>
       <c r="C228" s="39" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D228" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E228" s="39">
         <v>150</v>
@@ -10075,16 +9907,16 @@
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="B229" s="39" t="s">
         <v>534</v>
       </c>
-      <c r="B229" s="39" t="s">
-        <v>535</v>
-      </c>
       <c r="C229" s="39" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D229" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E229" s="39">
         <v>150</v>
@@ -10102,16 +9934,16 @@
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="B230" s="55" t="s">
         <v>536</v>
       </c>
-      <c r="B230" s="55" t="s">
-        <v>537</v>
-      </c>
       <c r="C230" s="55" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D230" s="55" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E230" s="55">
         <v>145</v>
@@ -10129,7 +9961,7 @@
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="13" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B231" s="22"/>
       <c r="C231" s="22"/>
@@ -10142,7 +9974,7 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B232" s="39"/>
       <c r="C232" s="39"/>
@@ -10155,16 +9987,16 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="B233" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="B233" s="39" t="s">
+      <c r="C233" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="C233" s="39" t="s">
+      <c r="D233" s="39" t="s">
         <v>542</v>
-      </c>
-      <c r="D233" s="39" t="s">
-        <v>543</v>
       </c>
       <c r="E233" s="39"/>
       <c r="F233" s="40"/>
@@ -10178,16 +10010,16 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B234" s="56" t="s">
-        <v>842</v>
+        <v>912</v>
       </c>
       <c r="C234" s="56" t="s">
-        <v>843</v>
+        <v>913</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>844</v>
+        <v>914</v>
       </c>
       <c r="E234" s="56">
         <v>190</v>
@@ -10202,21 +10034,21 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="57" t="s">
-        <v>845</v>
+        <v>915</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>846</v>
+        <v>916</v>
       </c>
       <c r="C235" s="55" t="s">
-        <v>847</v>
+        <v>917</v>
       </c>
       <c r="D235" s="55" t="s">
-        <v>848</v>
+        <v>918</v>
       </c>
       <c r="E235" s="55">
         <v>155</v>
@@ -10231,12 +10063,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I235" s="58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" s="13" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B236" s="55"/>
       <c r="C236" s="55"/>
@@ -10249,16 +10081,16 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="B237" s="55" t="s">
+        <v>919</v>
+      </c>
+      <c r="C237" s="55" t="s">
         <v>548</v>
       </c>
-      <c r="B237" s="55" t="s">
-        <v>849</v>
-      </c>
-      <c r="C237" s="55" t="s">
-        <v>549</v>
-      </c>
       <c r="D237" s="55" t="s">
-        <v>850</v>
+        <v>920</v>
       </c>
       <c r="E237" s="55">
         <v>155</v>
@@ -10273,21 +10105,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I237" s="58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="13" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B238" s="55" t="s">
-        <v>851</v>
+        <v>921</v>
       </c>
       <c r="C238" s="55" t="s">
-        <v>852</v>
+        <v>922</v>
       </c>
       <c r="D238" s="55" t="s">
-        <v>853</v>
+        <v>923</v>
       </c>
       <c r="E238" s="56">
         <v>190</v>
@@ -10302,21 +10134,21 @@
         <v>5.7</v>
       </c>
       <c r="I238" s="57" t="s">
-        <v>854</v>
+        <v>924</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="13" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>855</v>
+        <v>925</v>
       </c>
       <c r="C239" s="55" t="s">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="D239" s="55" t="s">
-        <v>853</v>
+        <v>923</v>
       </c>
       <c r="E239" s="56">
         <v>180</v>
@@ -10331,21 +10163,21 @@
         <v>5.5</v>
       </c>
       <c r="I239" s="57" t="s">
-        <v>854</v>
+        <v>924</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" s="13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>857</v>
+        <v>927</v>
       </c>
       <c r="C240" s="55" t="s">
-        <v>858</v>
+        <v>928</v>
       </c>
       <c r="D240" s="55" t="s">
-        <v>853</v>
+        <v>923</v>
       </c>
       <c r="E240" s="56">
         <v>190</v>
@@ -10360,21 +10192,21 @@
         <v>5.6</v>
       </c>
       <c r="I240" s="57" t="s">
-        <v>859</v>
+        <v>929</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="B241" s="55" t="s">
+        <v>930</v>
+      </c>
+      <c r="C241" s="55" t="s">
+        <v>931</v>
+      </c>
+      <c r="D241" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="B241" s="55" t="s">
-        <v>860</v>
-      </c>
-      <c r="C241" s="55" t="s">
-        <v>861</v>
-      </c>
-      <c r="D241" s="15" t="s">
-        <v>554</v>
       </c>
       <c r="E241" s="55">
         <v>150</v>
@@ -10386,24 +10218,24 @@
         <v>220</v>
       </c>
       <c r="H241" s="56">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I241" s="58" t="s">
-        <v>862</v>
+        <v>932</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="13" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>863</v>
+        <v>933</v>
       </c>
       <c r="C242" s="55" t="s">
-        <v>864</v>
+        <v>934</v>
       </c>
       <c r="D242" s="55" t="s">
-        <v>853</v>
+        <v>923</v>
       </c>
       <c r="E242" s="56">
         <v>160</v>
@@ -10418,21 +10250,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="57" t="s">
-        <v>865</v>
+        <v>935</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" s="13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>866</v>
+        <v>936</v>
       </c>
       <c r="C243" s="55" t="s">
-        <v>867</v>
+        <v>937</v>
       </c>
       <c r="D243" s="55" t="s">
-        <v>868</v>
+        <v>938</v>
       </c>
       <c r="E243" s="56">
         <v>190</v>
@@ -10447,21 +10279,21 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="57" t="s">
-        <v>869</v>
+        <v>939</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="13" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="C244" s="55" t="s">
-        <v>871</v>
+        <v>941</v>
       </c>
       <c r="D244" s="55" t="s">
-        <v>868</v>
+        <v>938</v>
       </c>
       <c r="E244" s="55">
         <v>150</v>
@@ -10477,7 +10309,7 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B245" s="42"/>
       <c r="C245" s="42"/>
@@ -10490,16 +10322,16 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B246" s="22" t="s">
-        <v>872</v>
+        <v>942</v>
       </c>
       <c r="C246" s="22" t="s">
-        <v>873</v>
+        <v>943</v>
       </c>
       <c r="D246" s="37" t="s">
-        <v>801</v>
+        <v>428</v>
       </c>
       <c r="E246" s="22">
         <v>112</v>
@@ -10517,16 +10349,16 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" s="35" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B247" s="22" t="s">
-        <v>874</v>
+        <v>944</v>
       </c>
       <c r="C247" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D247" s="37" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E247" s="22">
         <v>135</v>
@@ -10544,16 +10376,16 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="B248" s="22" t="s">
+        <v>945</v>
+      </c>
+      <c r="C248" s="22" t="s">
         <v>561</v>
       </c>
-      <c r="B248" s="22" t="s">
-        <v>875</v>
-      </c>
-      <c r="C248" s="22" t="s">
-        <v>562</v>
-      </c>
       <c r="D248" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E248" s="22">
         <v>160</v>
@@ -10571,16 +10403,16 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="35" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B249" s="22" t="s">
-        <v>876</v>
+        <v>946</v>
       </c>
       <c r="C249" s="22" t="s">
-        <v>877</v>
+        <v>438</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E249" s="36">
         <v>105</v>
@@ -10598,16 +10430,16 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="35" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B250" s="22" t="s">
-        <v>878</v>
+        <v>947</v>
       </c>
       <c r="C250" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E250" s="36">
         <v>108</v>
@@ -10625,16 +10457,16 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="B251" s="22" t="s">
+        <v>948</v>
+      </c>
+      <c r="C251" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="B251" s="22" t="s">
-        <v>879</v>
-      </c>
-      <c r="C251" s="22" t="s">
-        <v>566</v>
-      </c>
       <c r="D251" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E251" s="22">
         <v>116</v>
@@ -10652,16 +10484,16 @@
     </row>
     <row r="252" spans="1:9">
       <c r="A252" s="35" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B252" s="22" t="s">
-        <v>880</v>
+        <v>949</v>
       </c>
       <c r="C252" s="22" t="s">
-        <v>877</v>
+        <v>438</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E252" s="22">
         <v>105</v>
@@ -10679,16 +10511,16 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" s="35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>881</v>
+        <v>950</v>
       </c>
       <c r="C253" s="22" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E253" s="22">
         <v>116</v>
@@ -10706,16 +10538,16 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254" s="35" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B254" s="22" t="s">
-        <v>882</v>
+        <v>951</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>883</v>
+        <v>952</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>844</v>
+        <v>914</v>
       </c>
       <c r="E254" s="22">
         <v>190</v>
@@ -10730,21 +10562,21 @@
         <v>5.3</v>
       </c>
       <c r="I254" s="57" t="s">
-        <v>869</v>
+        <v>939</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="B255" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="C255" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="B255" s="22" t="s">
-        <v>884</v>
-      </c>
-      <c r="C255" s="22" t="s">
-        <v>571</v>
-      </c>
       <c r="D255" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E255" s="61">
         <v>88</v>
@@ -10756,22 +10588,22 @@
         <v>208</v>
       </c>
       <c r="H255" s="61">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I255" s="57"/>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B256" s="56" t="s">
-        <v>885</v>
+        <v>954</v>
       </c>
       <c r="C256" s="22" t="s">
-        <v>886</v>
+        <v>161</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>887</v>
+        <v>955</v>
       </c>
       <c r="E256" s="56">
         <v>190</v>
@@ -10786,21 +10618,21 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="57" t="s">
-        <v>888</v>
+        <v>956</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" s="13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B257" s="40" t="s">
-        <v>889</v>
+        <v>957</v>
       </c>
       <c r="C257" s="40" t="s">
-        <v>890</v>
+        <v>321</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>801</v>
+        <v>428</v>
       </c>
       <c r="E257" s="40">
         <v>118</v>
@@ -10812,22 +10644,22 @@
         <v>215</v>
       </c>
       <c r="H257" s="10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I257" s="10"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="13" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B258" s="22" t="s">
-        <v>878</v>
+        <v>947</v>
       </c>
       <c r="C258" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E258" s="36">
         <v>108</v>
@@ -10845,7 +10677,7 @@
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B259" s="40"/>
       <c r="C259" s="40"/>
@@ -10858,7 +10690,7 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="13" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B260" s="40"/>
       <c r="C260" s="40"/>
@@ -10871,16 +10703,16 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="B261" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="B261" s="14" t="s">
+      <c r="C261" s="14" t="s">
         <v>578</v>
       </c>
-      <c r="C261" s="14" t="s">
-        <v>579</v>
-      </c>
       <c r="D261" s="53" t="s">
-        <v>891</v>
+        <v>958</v>
       </c>
       <c r="E261" s="14">
         <v>108</v>
@@ -10898,16 +10730,16 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="B262" s="14" t="s">
+        <v>959</v>
+      </c>
+      <c r="C262" s="14" t="s">
         <v>580</v>
       </c>
-      <c r="B262" s="14" t="s">
-        <v>892</v>
-      </c>
-      <c r="C262" s="14" t="s">
+      <c r="D262" s="53" t="s">
         <v>581</v>
-      </c>
-      <c r="D262" s="53" t="s">
-        <v>582</v>
       </c>
       <c r="E262" s="14">
         <v>87</v>
@@ -10925,16 +10757,16 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="B263" s="31" t="s">
         <v>583</v>
       </c>
-      <c r="B263" s="31" t="s">
+      <c r="C263" s="31" t="s">
         <v>584</v>
       </c>
-      <c r="C263" s="31" t="s">
+      <c r="D263" s="31" t="s">
         <v>585</v>
-      </c>
-      <c r="D263" s="31" t="s">
-        <v>586</v>
       </c>
       <c r="E263" s="31">
         <v>115</v>
@@ -10952,16 +10784,16 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="B264" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="B264" s="14" t="s">
+      <c r="C264" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="C264" s="14" t="s">
+      <c r="D264" s="14" t="s">
         <v>589</v>
-      </c>
-      <c r="D264" s="14" t="s">
-        <v>590</v>
       </c>
       <c r="E264" s="14">
         <v>70</v>
@@ -10973,22 +10805,22 @@
         <v>208</v>
       </c>
       <c r="H264" s="14">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I264" s="10"/>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="B265" s="39" t="s">
         <v>591</v>
       </c>
-      <c r="B265" s="39" t="s">
+      <c r="C265" s="39" t="s">
         <v>592</v>
       </c>
-      <c r="C265" s="39" t="s">
+      <c r="D265" s="39" t="s">
         <v>593</v>
-      </c>
-      <c r="D265" s="39" t="s">
-        <v>594</v>
       </c>
       <c r="E265" s="39">
         <v>102</v>
@@ -11006,16 +10838,16 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B266" s="39" t="s">
-        <v>893</v>
+        <v>960</v>
       </c>
       <c r="C266" s="39" t="s">
-        <v>871</v>
+        <v>941</v>
       </c>
       <c r="D266" s="39" t="s">
-        <v>894</v>
+        <v>961</v>
       </c>
       <c r="E266" s="39">
         <v>78</v>
@@ -11033,16 +10865,16 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>895</v>
+        <v>962</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>896</v>
+        <v>963</v>
       </c>
       <c r="D267" s="53" t="s">
-        <v>897</v>
+        <v>144</v>
       </c>
       <c r="E267" s="14">
         <v>60</v>
@@ -11060,7 +10892,7 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B268" s="40"/>
       <c r="C268" s="40"/>
@@ -11073,7 +10905,7 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B269" s="40"/>
       <c r="C269" s="40"/>
@@ -11086,7 +10918,7 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B270" s="40"/>
       <c r="C270" s="40"/>
@@ -11099,7 +10931,7 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B271" s="40"/>
       <c r="C271" s="40"/>
@@ -11112,7 +10944,7 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B272" s="40"/>
       <c r="C272" s="40"/>
@@ -11125,7 +10957,7 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B273" s="40"/>
       <c r="C273" s="40"/>
@@ -11138,7 +10970,7 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B274" s="40"/>
       <c r="C274" s="40"/>
@@ -11151,7 +10983,7 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B275" s="40"/>
       <c r="C275" s="40"/>
@@ -11164,7 +10996,7 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B276" s="40"/>
       <c r="C276" s="40"/>
@@ -11177,16 +11009,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="B277" s="56" t="s">
         <v>606</v>
       </c>
-      <c r="B277" s="56" t="s">
+      <c r="C277" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="C277" s="56" t="s">
+      <c r="D277" s="56" t="s">
         <v>608</v>
-      </c>
-      <c r="D277" s="56" t="s">
-        <v>609</v>
       </c>
       <c r="E277" s="56">
         <v>105</v>
@@ -11204,16 +11036,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B278" s="31" t="s">
-        <v>898</v>
+        <v>771</v>
       </c>
       <c r="C278" s="31" t="s">
-        <v>899</v>
+        <v>772</v>
       </c>
       <c r="D278" s="31" t="s">
-        <v>900</v>
+        <v>773</v>
       </c>
       <c r="E278" s="31">
         <v>159</v>
@@ -11231,13 +11063,13 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>901</v>
+        <v>774</v>
       </c>
       <c r="C279" s="53" t="s">
-        <v>902</v>
+        <v>775</v>
       </c>
       <c r="D279" s="14" t="s">
         <v>144</v>
@@ -11258,16 +11090,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>903</v>
+        <v>776</v>
       </c>
       <c r="C280" s="53" t="s">
-        <v>904</v>
+        <v>777</v>
       </c>
       <c r="D280" s="14" t="s">
-        <v>905</v>
+        <v>778</v>
       </c>
       <c r="E280" s="14"/>
       <c r="F280" s="13">
@@ -11283,13 +11115,13 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="B281" s="14" t="s">
         <v>613</v>
       </c>
-      <c r="B281" s="14" t="s">
+      <c r="C281" s="53" t="s">
         <v>614</v>
-      </c>
-      <c r="C281" s="53" t="s">
-        <v>615</v>
       </c>
       <c r="D281" s="14" t="s">
         <v>144</v>
@@ -11310,13 +11142,13 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="B282" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="C282" s="53" t="s">
         <v>616</v>
-      </c>
-      <c r="B282" s="14" t="s">
-        <v>906</v>
-      </c>
-      <c r="C282" s="53" t="s">
-        <v>617</v>
       </c>
       <c r="D282" s="14" t="s">
         <v>39</v>
@@ -11337,13 +11169,13 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>907</v>
+        <v>780</v>
       </c>
       <c r="C283" s="53" t="s">
-        <v>908</v>
+        <v>781</v>
       </c>
       <c r="D283" s="14" t="s">
         <v>39</v>
@@ -11364,16 +11196,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B284" s="31" t="s">
-        <v>909</v>
+        <v>782</v>
       </c>
       <c r="C284" s="40" t="s">
-        <v>910</v>
+        <v>783</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>911</v>
+        <v>784</v>
       </c>
       <c r="E284" s="40">
         <v>80</v>
@@ -11391,16 +11223,16 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="B285" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="B285" s="14" t="s">
+      <c r="C285" s="53" t="s">
         <v>621</v>
       </c>
-      <c r="C285" s="53" t="s">
-        <v>622</v>
-      </c>
       <c r="D285" s="40" t="s">
-        <v>911</v>
+        <v>784</v>
       </c>
       <c r="E285" s="14">
         <v>73</v>
@@ -11418,16 +11250,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="B286" s="56" t="s">
+        <v>785</v>
+      </c>
+      <c r="C286" s="56" t="s">
+        <v>786</v>
+      </c>
+      <c r="D286" s="56" t="s">
         <v>623</v>
-      </c>
-      <c r="B286" s="56" t="s">
-        <v>912</v>
-      </c>
-      <c r="C286" s="56" t="s">
-        <v>913</v>
-      </c>
-      <c r="D286" s="56" t="s">
-        <v>624</v>
       </c>
       <c r="E286" s="56">
         <v>85</v>
@@ -11445,16 +11277,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B287" s="56" t="s">
-        <v>914</v>
+        <v>787</v>
       </c>
       <c r="C287" s="56" t="s">
-        <v>915</v>
+        <v>788</v>
       </c>
       <c r="D287" s="56" t="s">
-        <v>916</v>
+        <v>789</v>
       </c>
       <c r="E287" s="56">
         <v>88</v>
@@ -11472,13 +11304,13 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B288" s="31" t="s">
+        <v>790</v>
+      </c>
+      <c r="C288" s="31" t="s">
         <v>626</v>
-      </c>
-      <c r="B288" s="31" t="s">
-        <v>917</v>
-      </c>
-      <c r="C288" s="31" t="s">
-        <v>627</v>
       </c>
       <c r="D288" s="54" t="s">
         <v>1</v>
@@ -11499,16 +11331,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B289" s="14" t="s">
         <v>628</v>
       </c>
-      <c r="B289" s="14" t="s">
+      <c r="C289" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="C289" s="14" t="s">
+      <c r="D289" s="53" t="s">
         <v>630</v>
-      </c>
-      <c r="D289" s="53" t="s">
-        <v>631</v>
       </c>
       <c r="E289" s="14">
         <v>135</v>
@@ -11523,18 +11355,18 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="15" t="s">
-        <v>918</v>
+        <v>791</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="B290" s="28" t="s">
         <v>632</v>
       </c>
-      <c r="B290" s="28" t="s">
+      <c r="C290" s="28" t="s">
         <v>633</v>
-      </c>
-      <c r="C290" s="28" t="s">
-        <v>634</v>
       </c>
       <c r="D290" s="63" t="s">
         <v>39</v>
@@ -11555,16 +11387,16 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="B291" s="64" t="s">
+        <v>792</v>
+      </c>
+      <c r="C291" s="64" t="s">
+        <v>793</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>635</v>
-      </c>
-      <c r="B291" s="64" t="s">
-        <v>919</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>920</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>636</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -11582,16 +11414,16 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>794</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>637</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>921</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>638</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>639</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -11609,13 +11441,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>922</v>
+        <v>795</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>923</v>
+        <v>796</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11636,16 +11468,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B294" s="22" t="s">
-        <v>924</v>
+        <v>797</v>
       </c>
       <c r="C294" s="22" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>925</v>
+        <v>798</v>
       </c>
       <c r="E294" s="22">
         <v>150</v>
@@ -11663,16 +11495,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="C295" s="14" t="s">
         <v>642</v>
       </c>
-      <c r="B295" s="14" t="s">
-        <v>926</v>
-      </c>
-      <c r="C295" s="14" t="s">
+      <c r="D295" s="14" t="s">
         <v>643</v>
-      </c>
-      <c r="D295" s="14" t="s">
-        <v>644</v>
       </c>
       <c r="E295" s="14"/>
       <c r="F295" s="13"/>
@@ -11686,16 +11518,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="B296" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="B296" s="39" t="s">
+      <c r="C296" s="39" t="s">
         <v>646</v>
       </c>
-      <c r="C296" s="39" t="s">
+      <c r="D296" s="39" t="s">
         <v>647</v>
-      </c>
-      <c r="D296" s="39" t="s">
-        <v>648</v>
       </c>
       <c r="E296" s="39"/>
       <c r="F296" s="40">
@@ -11711,16 +11543,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B297" s="22" t="s">
-        <v>927</v>
+        <v>800</v>
       </c>
       <c r="C297" s="22" t="s">
-        <v>928</v>
+        <v>801</v>
       </c>
       <c r="D297" s="37" t="s">
-        <v>929</v>
+        <v>802</v>
       </c>
       <c r="E297" s="22">
         <v>125</v>
@@ -11738,16 +11570,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B298" s="22" t="s">
-        <v>930</v>
+        <v>803</v>
       </c>
       <c r="C298" s="22" t="s">
-        <v>931</v>
+        <v>804</v>
       </c>
       <c r="D298" s="37" t="s">
-        <v>932</v>
+        <v>805</v>
       </c>
       <c r="E298" s="22">
         <v>190</v>
@@ -11762,21 +11594,21 @@
         <v>5.9</v>
       </c>
       <c r="I298" s="15" t="s">
-        <v>933</v>
+        <v>806</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B299" s="55" t="s">
-        <v>934</v>
+        <v>807</v>
       </c>
       <c r="C299" s="55" t="s">
-        <v>935</v>
+        <v>808</v>
       </c>
       <c r="D299" s="55" t="s">
-        <v>936</v>
+        <v>809</v>
       </c>
       <c r="E299" s="55">
         <v>124</v>
@@ -11791,12 +11623,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="58" t="s">
-        <v>937</v>
+        <v>810</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B300" s="40"/>
       <c r="C300" s="40"/>
@@ -11809,7 +11641,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B301" s="40"/>
       <c r="C301" s="40"/>
@@ -11822,16 +11654,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B302" s="15" t="s">
-        <v>938</v>
+        <v>811</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>939</v>
+        <v>812</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>940</v>
+        <v>813</v>
       </c>
       <c r="E302" s="15">
         <v>150</v>
@@ -11849,16 +11681,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="B303" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="B303" s="14" t="s">
+      <c r="C303" s="14" t="s">
         <v>656</v>
       </c>
-      <c r="C303" s="14" t="s">
-        <v>657</v>
-      </c>
       <c r="D303" s="14" t="s">
-        <v>940</v>
+        <v>813</v>
       </c>
       <c r="E303" s="15">
         <v>140</v>
@@ -11876,16 +11708,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>658</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>814</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>659</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>941</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>660</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11900,21 +11732,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="41" t="s">
-        <v>942</v>
+        <v>815</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B305" s="40" t="s">
-        <v>943</v>
+        <v>816</v>
       </c>
       <c r="C305" s="40" t="s">
-        <v>944</v>
+        <v>817</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>945</v>
+        <v>818</v>
       </c>
       <c r="E305" s="40">
         <v>215</v>
@@ -11932,7 +11764,7 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B306" s="40"/>
       <c r="C306" s="40"/>
@@ -11945,7 +11777,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B307" s="40"/>
       <c r="C307" s="40"/>
@@ -11958,7 +11790,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B308" s="40"/>
       <c r="C308" s="40"/>
@@ -11971,7 +11803,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B309" s="40"/>
       <c r="C309" s="40"/>
@@ -11984,7 +11816,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B310" s="40"/>
       <c r="C310" s="40"/>
@@ -11997,16 +11829,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="B311" s="39" t="s">
         <v>667</v>
       </c>
-      <c r="B311" s="39" t="s">
-        <v>668</v>
-      </c>
       <c r="C311" s="39" t="s">
-        <v>946</v>
+        <v>819</v>
       </c>
       <c r="D311" s="39" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E311" s="39">
         <v>85</v>
@@ -12024,16 +11856,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="13" t="s">
+        <v>670</v>
+      </c>
+      <c r="B312" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B312" s="14" t="s">
+      <c r="C312" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="D312" s="14" t="s">
         <v>672</v>
-      </c>
-      <c r="C312" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="D312" s="14" t="s">
-        <v>673</v>
       </c>
       <c r="E312" s="14">
         <v>73</v>
@@ -12051,7 +11883,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B313" s="40"/>
       <c r="C313" s="40"/>
@@ -12064,7 +11896,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B314" s="40"/>
       <c r="C314" s="40"/>
@@ -12077,16 +11909,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B315" s="40" t="s">
-        <v>947</v>
+        <v>820</v>
       </c>
       <c r="C315" s="40" t="s">
-        <v>852</v>
+        <v>770</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>948</v>
+        <v>821</v>
       </c>
       <c r="E315" s="40">
         <v>116</v>
@@ -12101,21 +11933,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="9" t="s">
-        <v>949</v>
+        <v>822</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B316" s="40" t="s">
-        <v>950</v>
+        <v>823</v>
       </c>
       <c r="C316" s="40" t="s">
-        <v>951</v>
+        <v>824</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>952</v>
+        <v>825</v>
       </c>
       <c r="E316" s="40">
         <v>160</v>
@@ -12130,21 +11962,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>953</v>
+        <v>826</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>954</v>
+        <v>827</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>955</v>
+        <v>828</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>956</v>
+        <v>829</v>
       </c>
       <c r="E317" s="15">
         <v>110</v>
@@ -12159,21 +11991,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="15" t="s">
-        <v>957</v>
+        <v>830</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>954</v>
+        <v>827</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>958</v>
+        <v>831</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>956</v>
+        <v>829</v>
       </c>
       <c r="E318" s="15">
         <v>110</v>
@@ -12191,16 +12023,16 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B319" s="22" t="s">
-        <v>959</v>
+        <v>832</v>
       </c>
       <c r="C319" s="22" t="s">
-        <v>960</v>
+        <v>833</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>961</v>
+        <v>834</v>
       </c>
       <c r="E319" s="22">
         <v>205</v>
@@ -12215,21 +12047,21 @@
         <v>5.5</v>
       </c>
       <c r="I319" s="15" t="s">
-        <v>962</v>
+        <v>835</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B320" s="22" t="s">
-        <v>963</v>
+        <v>836</v>
       </c>
       <c r="C320" s="22" t="s">
-        <v>964</v>
+        <v>837</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>965</v>
+        <v>838</v>
       </c>
       <c r="E320" s="22">
         <v>182</v>
@@ -12244,21 +12076,21 @@
         <v>6</v>
       </c>
       <c r="I320" s="15" t="s">
-        <v>933</v>
+        <v>806</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B321" s="22" t="s">
-        <v>966</v>
+        <v>839</v>
       </c>
       <c r="C321" s="22" t="s">
-        <v>967</v>
+        <v>840</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>968</v>
+        <v>841</v>
       </c>
       <c r="E321" s="22">
         <v>138</v>
@@ -12273,21 +12105,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="15" t="s">
-        <v>969</v>
+        <v>842</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B322" s="22" t="s">
-        <v>970</v>
+        <v>843</v>
       </c>
       <c r="C322" s="22" t="s">
-        <v>971</v>
+        <v>844</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>961</v>
+        <v>834</v>
       </c>
       <c r="E322" s="22">
         <v>225</v>
@@ -12302,21 +12134,21 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="15" t="s">
-        <v>972</v>
+        <v>845</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B323" s="22" t="s">
-        <v>973</v>
+        <v>846</v>
       </c>
       <c r="C323" s="22" t="s">
-        <v>974</v>
+        <v>847</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>968</v>
+        <v>841</v>
       </c>
       <c r="E323" s="22">
         <v>155</v>
@@ -12331,21 +12163,21 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="15" t="s">
-        <v>975</v>
+        <v>848</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B324" s="22" t="s">
-        <v>976</v>
+        <v>849</v>
       </c>
       <c r="C324" s="22" t="s">
-        <v>977</v>
+        <v>850</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>961</v>
+        <v>834</v>
       </c>
       <c r="E324" s="22">
         <v>220</v>
@@ -12360,12 +12192,12 @@
         <v>6.4</v>
       </c>
       <c r="I324" s="15" t="s">
-        <v>972</v>
+        <v>845</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B325" s="40"/>
       <c r="C325" s="40"/>
@@ -12378,7 +12210,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B326" s="40"/>
       <c r="C326" s="40"/>
@@ -12391,7 +12223,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B327" s="40"/>
       <c r="C327" s="40"/>
@@ -12404,7 +12236,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B328" s="40"/>
       <c r="C328" s="40"/>
@@ -12417,7 +12249,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B329" s="40"/>
       <c r="C329" s="40"/>
@@ -12430,7 +12262,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B330" s="40"/>
       <c r="C330" s="40"/>
@@ -12443,7 +12275,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="13" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B331" s="40"/>
       <c r="C331" s="40"/>
@@ -12456,7 +12288,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B332" s="40"/>
       <c r="C332" s="40"/>
@@ -12469,7 +12301,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B333" s="40"/>
       <c r="C333" s="40"/>
@@ -12482,7 +12314,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B334" s="40"/>
       <c r="C334" s="40"/>
@@ -12495,7 +12327,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="13" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B335" s="40"/>
       <c r="C335" s="40"/>
@@ -12508,7 +12340,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B336" s="40"/>
       <c r="C336" s="40"/>
@@ -12521,7 +12353,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B337" s="40"/>
       <c r="C337" s="40"/>
@@ -12534,7 +12366,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B338" s="40"/>
       <c r="C338" s="40"/>
@@ -12547,7 +12379,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B339" s="40"/>
       <c r="C339" s="40"/>
@@ -12560,7 +12392,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B340" s="40"/>
       <c r="C340" s="40"/>
@@ -12573,7 +12405,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B341" s="40"/>
       <c r="C341" s="40"/>
@@ -12586,7 +12418,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B342" s="40"/>
       <c r="C342" s="40"/>
@@ -12599,7 +12431,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B343" s="40"/>
       <c r="C343" s="40"/>
@@ -12612,7 +12444,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B344" s="40"/>
       <c r="C344" s="40"/>
@@ -12625,7 +12457,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B345" s="40"/>
       <c r="C345" s="40"/>
@@ -12638,7 +12470,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B346" s="40"/>
       <c r="C346" s="40"/>
@@ -12651,7 +12483,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B347" s="40"/>
       <c r="C347" s="40"/>
@@ -12664,7 +12496,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B348" s="40"/>
       <c r="C348" s="40"/>
@@ -12677,7 +12509,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B349" s="40"/>
       <c r="C349" s="40"/>
@@ -12690,7 +12522,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B350" s="40"/>
       <c r="C350" s="40"/>
@@ -12703,7 +12535,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B351" s="40"/>
       <c r="C351" s="40"/>
@@ -12716,7 +12548,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B352" s="40"/>
       <c r="C352" s="40"/>
@@ -12729,7 +12561,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B353" s="40"/>
       <c r="C353" s="40"/>
@@ -12742,7 +12574,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B354" s="40"/>
       <c r="C354" s="40"/>
@@ -12755,7 +12587,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B355" s="40"/>
       <c r="C355" s="40"/>
@@ -12768,7 +12600,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B356" s="40"/>
       <c r="C356" s="40"/>
@@ -12781,7 +12613,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B357" s="40"/>
       <c r="C357" s="40"/>
@@ -12794,7 +12626,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B358" s="40"/>
       <c r="C358" s="40"/>
@@ -12807,7 +12639,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B359" s="40"/>
       <c r="C359" s="40"/>
@@ -12820,7 +12652,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B360" s="40"/>
       <c r="C360" s="40"/>
@@ -12833,7 +12665,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B361" s="40"/>
       <c r="C361" s="40"/>
@@ -12846,7 +12678,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B362" s="40"/>
       <c r="C362" s="40"/>
@@ -12859,7 +12691,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B363" s="40"/>
       <c r="C363" s="40"/>
@@ -12872,7 +12704,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B364" s="40"/>
       <c r="C364" s="40"/>
@@ -12885,7 +12717,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B365" s="40"/>
       <c r="C365" s="40"/>
@@ -12898,7 +12730,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B366" s="40"/>
       <c r="C366" s="40"/>
@@ -12911,7 +12743,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B367" s="40"/>
       <c r="C367" s="40"/>
@@ -12924,7 +12756,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B368" s="40"/>
       <c r="C368" s="40"/>
@@ -12937,7 +12769,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="13" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B369" s="40"/>
       <c r="C369" s="40"/>
@@ -12950,7 +12782,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B370" s="40"/>
       <c r="C370" s="40"/>
@@ -12963,7 +12795,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B371" s="40"/>
       <c r="C371" s="40"/>
@@ -12976,7 +12808,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B372" s="40"/>
       <c r="C372" s="40"/>
@@ -12989,7 +12821,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B373" s="40"/>
       <c r="C373" s="40"/>
@@ -13002,7 +12834,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B374" s="40"/>
       <c r="C374" s="40"/>
@@ -13015,7 +12847,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B375" s="40"/>
       <c r="C375" s="40"/>
@@ -13028,7 +12860,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B376" s="40"/>
       <c r="C376" s="40"/>
@@ -13041,7 +12873,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B377" s="40"/>
       <c r="C377" s="40"/>
@@ -13054,7 +12886,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B378" s="40"/>
       <c r="C378" s="40"/>
@@ -13067,7 +12899,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B379" s="40"/>
       <c r="C379" s="40"/>
@@ -13080,7 +12912,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B380" s="40"/>
       <c r="C380" s="40"/>
@@ -13093,7 +12925,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B381" s="40"/>
       <c r="C381" s="40"/>
@@ -13106,7 +12938,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B382" s="40"/>
       <c r="C382" s="40"/>
@@ -13119,7 +12951,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B383" s="40"/>
       <c r="C383" s="40"/>
@@ -13132,7 +12964,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B384" s="40"/>
       <c r="C384" s="40"/>
@@ -13145,7 +12977,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B385" s="40"/>
       <c r="C385" s="40"/>
@@ -13158,7 +12990,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B386" s="40"/>
       <c r="C386" s="40"/>
@@ -13171,7 +13003,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B387" s="40"/>
       <c r="C387" s="40"/>
@@ -13184,7 +13016,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B388" s="40"/>
       <c r="C388" s="40"/>
@@ -13197,7 +13029,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="13" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B389" s="40"/>
       <c r="C389" s="40"/>
@@ -13210,7 +13042,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B390" s="40"/>
       <c r="C390" s="40"/>
@@ -13223,7 +13055,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B391" s="40"/>
       <c r="C391" s="40"/>
@@ -13236,7 +13068,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B392" s="40"/>
       <c r="C392" s="40"/>
@@ -13249,7 +13081,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B393" s="40"/>
       <c r="C393" s="40"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\2种产品规格\旭辰标签加二维码\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
   </bookViews>
@@ -11,12 +16,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="1000">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -364,9 +369,6 @@
   </si>
   <si>
     <t>XC047</t>
-  </si>
-  <si>
-    <t>消光珍珠点50*50*150</t>
   </si>
   <si>
     <t>22*3+40</t>
@@ -2387,86 +2389,722 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100半低*150半T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>23*2*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*57</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*53</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50DT8*50DT8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*49</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>T800双链条</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>空变T8平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯370克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*48</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75T8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯188克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150T8*300低弹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯米克245</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*三合一</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯195克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">生态棉 加厚 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC001</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*1半光横条</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>消半光珍珠点50*50*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*2*25</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*26</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*50S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*40S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC186</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75DT400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*46</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75消*75T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*5*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*3*39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>X字格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*46</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*46</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条2*1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4+28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>238克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条1*4</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4+38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯200米克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条1*1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75闪电斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*28</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150*2T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克385</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克370</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平3/3斜-44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*45</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克375</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>15*4*43</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克300</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克350</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*29</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克380</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*150T800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*34</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150*300T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*210</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*2*40</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
     <t>半光大猫眼</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100半低*150半T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>50D低弹*50T800 平纹</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>23*2*40</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>30D T8 平纹</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>22*3*57</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>30*30</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*3*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*53</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50DT8*50DT8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>T8五面埋伏</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>14*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*49</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>T800双链条</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>米克265</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2479,34 +3117,18 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*4*38</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
     <t>40S*150T800</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>空变T8平纹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>17.5*3*44</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2515,19 +3137,11 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>40S*300加厚超钛棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>14*4*27</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>40S*300T800</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
+    <t>40S*150*2-T800</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -2535,14 +3149,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>15.5*4*48</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75T8</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>米克250</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2563,26 +3169,10 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>白坯188克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>13.5*4*51</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>网纹3/3-180</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2591,19 +3181,11 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>白坯米克245</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>网纹3/3-220</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*35S+150DT8</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -2633,11 +3215,7 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>80S*三合一</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯195克</t>
+    <t>天丝棉</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -2649,7 +3227,55 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>14*4*26.5</t>
+    <t>白坯368克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*27</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*30S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯285克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*30</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯390克</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*31</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -2657,414 +3283,65 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>白坯365克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>生态棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*44</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*35S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>210-钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*27</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*30S</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯285克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>加厚钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*30</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>白坯390克</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>240-钛金棉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯310克</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">生态棉 加厚 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*31</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC001</t>
-  </si>
-  <si>
-    <t>1*1半光横条</t>
-  </si>
-  <si>
-    <t>22*3*38</t>
-  </si>
-  <si>
-    <t>22*3*39</t>
-  </si>
-  <si>
-    <t>14*2*25</t>
-  </si>
-  <si>
-    <t>17*3*28</t>
-  </si>
-  <si>
-    <t>17*3*44</t>
-  </si>
-  <si>
-    <t>25梭T400无捻牛津</t>
-  </si>
-  <si>
-    <t>27梭T400无捻牛津</t>
-  </si>
-  <si>
-    <t>26梭T400无捻牛津</t>
-  </si>
-  <si>
-    <t>17*2*26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-  </si>
-  <si>
-    <t>17*2*30</t>
-  </si>
-  <si>
-    <t>50S*50S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-  </si>
-  <si>
-    <t>40S*40S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-  </si>
-  <si>
-    <t>50S*75D 酷丝棉绮兵</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-  </si>
-  <si>
-    <t>XC186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-  </si>
-  <si>
-    <t>40S*75DT400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-  </si>
-  <si>
-    <t>100*150T8 4/2斜</t>
-  </si>
-  <si>
-    <t>17*4*215*40</t>
-  </si>
-  <si>
-    <t>100D*150T800</t>
-  </si>
-  <si>
-    <t>75*150T400 消3/3斜</t>
-  </si>
-  <si>
-    <t>75*75T400消 3/3斜</t>
-  </si>
-  <si>
-    <t>75*75 半光2/2 斜</t>
-  </si>
-  <si>
-    <t>18*4*46</t>
-  </si>
-  <si>
-    <t>75*75 消光2/2 斜</t>
-  </si>
-  <si>
-    <t>75*150 消光2/2 斜</t>
-  </si>
-  <si>
-    <t>75*75-T800消光骑士斜</t>
-  </si>
-  <si>
-    <t>75消*75T800</t>
-  </si>
-  <si>
-    <t>19*5*45</t>
-  </si>
-  <si>
-    <t>19*3*39</t>
-  </si>
-  <si>
-    <t>X字格</t>
-  </si>
-  <si>
-    <t>16*4*46</t>
-  </si>
-  <si>
-    <t>T400横条2*1</t>
-  </si>
-  <si>
-    <t>16*4+28</t>
-  </si>
-  <si>
-    <t>238克</t>
-  </si>
-  <si>
-    <t>T400横条1*4</t>
-  </si>
-  <si>
-    <t>17*4+38</t>
-  </si>
-  <si>
-    <t>白坯200米克</t>
-  </si>
-  <si>
-    <t>T400横条1*1</t>
-  </si>
-  <si>
-    <t>16*4*30</t>
-  </si>
-  <si>
-    <t>40S*75闪电斜</t>
-  </si>
-  <si>
-    <t>18*3*38</t>
-  </si>
-  <si>
-    <t>40S*75</t>
-  </si>
-  <si>
-    <t>40S*150酷丝绵 小钻石斜</t>
-  </si>
-  <si>
-    <t>40S*150酷丝绵 大钻石斜</t>
-  </si>
-  <si>
-    <t>40S*300 3/2变化斜</t>
-  </si>
-  <si>
-    <t>13.5*4*28</t>
-  </si>
-  <si>
-    <t>40S*150*2T400</t>
-  </si>
-  <si>
-    <t>米克385</t>
-  </si>
-  <si>
-    <t>100D半光*35S-3/3斜</t>
-  </si>
-  <si>
-    <t>16*4*40</t>
-  </si>
-  <si>
-    <t>100*35</t>
-  </si>
-  <si>
-    <t>100D消光*35S-3/3斜</t>
-  </si>
-  <si>
-    <t>100*35S</t>
-  </si>
-  <si>
-    <t>120D扁平0.5格</t>
-  </si>
-  <si>
-    <t>17*4*44</t>
-  </si>
-  <si>
-    <t>120*35S</t>
-  </si>
-  <si>
-    <t>米克370</t>
-  </si>
-  <si>
-    <t>120D扁平3/3斜-45</t>
-  </si>
-  <si>
-    <t>16*4*45</t>
-  </si>
-  <si>
-    <t>120D扁平4/4斜</t>
-  </si>
-  <si>
-    <t>17*4*45</t>
-  </si>
-  <si>
-    <t>米克375</t>
-  </si>
-  <si>
-    <t>100D消光多乐3/3斜</t>
-  </si>
-  <si>
-    <t>15*4*43</t>
-  </si>
-  <si>
-    <t>米克300</t>
-  </si>
-  <si>
-    <t>120D扁平1/2斜</t>
-  </si>
-  <si>
-    <t>17*4*34</t>
-  </si>
-  <si>
-    <t>米克350</t>
-  </si>
-  <si>
-    <t>120D扁平T800变化斜</t>
-  </si>
-  <si>
-    <t>17*4*29</t>
-  </si>
-  <si>
-    <t>120*150T800</t>
-  </si>
-  <si>
-    <t>米克380</t>
-  </si>
-  <si>
-    <t>120D扁平牛津</t>
-  </si>
-  <si>
-    <t>20*2*31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-  </si>
-  <si>
-    <t>13.5*4*34</t>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/1斜 31</t>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/2斜 39</t>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1 30</t>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-  </si>
-  <si>
-    <t>40S*300 酷丝棉3/2斜</t>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-  </si>
-  <si>
-    <t>40S*300酷丝绵珍珠点</t>
-  </si>
-  <si>
-    <t>40S*150*300T400</t>
-  </si>
-  <si>
-    <t>米克368</t>
-  </si>
-  <si>
-    <t>40S*75D酷丝绵变化斜</t>
-  </si>
-  <si>
-    <t>40S*150T400+300T400</t>
-  </si>
-  <si>
-    <t>80S*75双线格酷丝绵</t>
-  </si>
-  <si>
-    <t>75 T800半光0.5格</t>
-  </si>
-  <si>
-    <t>75*75*210</t>
-  </si>
-  <si>
-    <t>50D经纬 T8 0.5格</t>
-  </si>
-  <si>
-    <t>22*2*40</t>
+    <t>270单股钛金棉</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*18S</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山布</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.5*4*215*44</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*450</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10克</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40*300平纹</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*24</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300D</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -3896,11 +4173,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3942,7 +4227,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3974,9 +4259,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4008,6 +4294,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4183,9 +4470,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M393"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="9" width="9" style="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
@@ -4193,56 +4480,56 @@
     <col min="12" max="12" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>697</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>688</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="13" t="s">
-        <v>851</v>
+        <v>808</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>852</v>
+        <v>809</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1</v>
+        <v>810</v>
       </c>
       <c r="E2" s="14">
         <v>79</v>
@@ -4256,16 +4543,16 @@
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -4293,7 +4580,7 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
@@ -4321,7 +4608,7 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
@@ -4346,7 +4633,7 @@
       </c>
       <c r="I5" s="15"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
@@ -4371,7 +4658,7 @@
       </c>
       <c r="I6" s="15"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
@@ -4396,7 +4683,7 @@
       </c>
       <c r="I7" s="15"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
@@ -4421,7 +4708,7 @@
       </c>
       <c r="I8" s="15"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="13" t="s">
         <v>18</v>
       </c>
@@ -4446,7 +4733,7 @@
       </c>
       <c r="I9" s="15"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
         <v>20</v>
       </c>
@@ -4471,7 +4758,7 @@
       </c>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
         <v>22</v>
       </c>
@@ -4496,7 +4783,7 @@
       </c>
       <c r="I11" s="15"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
         <v>24</v>
       </c>
@@ -4521,7 +4808,7 @@
       </c>
       <c r="I12" s="15"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="13" t="s">
         <v>26</v>
       </c>
@@ -4546,7 +4833,7 @@
       </c>
       <c r="I13" s="15"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="13" t="s">
         <v>28</v>
       </c>
@@ -4571,7 +4858,7 @@
       </c>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="13" t="s">
         <v>30</v>
       </c>
@@ -4596,7 +4883,7 @@
       </c>
       <c r="I15" s="15"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="13" t="s">
         <v>33</v>
       </c>
@@ -4621,7 +4908,7 @@
       </c>
       <c r="I16" s="15"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="13" t="s">
         <v>35</v>
       </c>
@@ -4646,7 +4933,7 @@
       </c>
       <c r="I17" s="15"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="13" t="s">
         <v>37</v>
       </c>
@@ -4671,7 +4958,7 @@
       </c>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -4696,7 +4983,7 @@
       </c>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="13" t="s">
         <v>43</v>
       </c>
@@ -4721,7 +5008,7 @@
       </c>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="13" t="s">
         <v>47</v>
       </c>
@@ -4746,7 +5033,7 @@
       </c>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="13" t="s">
         <v>49</v>
       </c>
@@ -4771,7 +5058,7 @@
       </c>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
         <v>51</v>
       </c>
@@ -4796,7 +5083,7 @@
       </c>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="13" t="s">
         <v>54</v>
       </c>
@@ -4821,7 +5108,7 @@
       </c>
       <c r="I24" s="15"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="13" t="s">
         <v>56</v>
       </c>
@@ -4846,7 +5133,7 @@
       </c>
       <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="13" t="s">
         <v>58</v>
       </c>
@@ -4871,7 +5158,7 @@
       </c>
       <c r="I26" s="15"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="13" t="s">
         <v>61</v>
       </c>
@@ -4896,7 +5183,7 @@
       </c>
       <c r="I27" s="15"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="13" t="s">
         <v>64</v>
       </c>
@@ -4921,7 +5208,7 @@
       </c>
       <c r="I28" s="15"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
         <v>67</v>
       </c>
@@ -4929,7 +5216,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>853</v>
+        <v>811</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>46</v>
@@ -4946,7 +5233,7 @@
       </c>
       <c r="I29" s="15"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="13" t="s">
         <v>69</v>
       </c>
@@ -4954,7 +5241,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>854</v>
+        <v>812</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>46</v>
@@ -4971,7 +5258,7 @@
       </c>
       <c r="I30" s="15"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="13" t="s">
         <v>71</v>
       </c>
@@ -4996,7 +5283,7 @@
       </c>
       <c r="I31" s="15"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="13" t="s">
         <v>74</v>
       </c>
@@ -5021,7 +5308,7 @@
       </c>
       <c r="I32" s="15"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="13" t="s">
         <v>76</v>
       </c>
@@ -5046,7 +5333,7 @@
       </c>
       <c r="I33" s="15"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="13" t="s">
         <v>78</v>
       </c>
@@ -5071,7 +5358,7 @@
       </c>
       <c r="I34" s="15"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" s="13" t="s">
         <v>81</v>
       </c>
@@ -5096,7 +5383,7 @@
       </c>
       <c r="I35" s="15"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="13" t="s">
         <v>83</v>
       </c>
@@ -5121,7 +5408,7 @@
       </c>
       <c r="I36" s="15"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="13" t="s">
         <v>86</v>
       </c>
@@ -5146,7 +5433,7 @@
       </c>
       <c r="I37" s="15"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="13" t="s">
         <v>89</v>
       </c>
@@ -5171,7 +5458,7 @@
       </c>
       <c r="I38" s="15"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="13" t="s">
         <v>92</v>
       </c>
@@ -5196,7 +5483,7 @@
       </c>
       <c r="I39" s="15"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="13" t="s">
         <v>94</v>
       </c>
@@ -5221,7 +5508,7 @@
       </c>
       <c r="I40" s="15"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="13" t="s">
         <v>96</v>
       </c>
@@ -5246,7 +5533,7 @@
       </c>
       <c r="I41" s="15"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="13" t="s">
         <v>99</v>
       </c>
@@ -5271,7 +5558,7 @@
       </c>
       <c r="I42" s="15"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="13" t="s">
         <v>101</v>
       </c>
@@ -5296,7 +5583,7 @@
       </c>
       <c r="I43" s="15"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="13" t="s">
         <v>104</v>
       </c>
@@ -5321,7 +5608,7 @@
       </c>
       <c r="I44" s="15"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="13" t="s">
         <v>108</v>
       </c>
@@ -5346,7 +5633,7 @@
       </c>
       <c r="I45" s="15"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="13" t="s">
         <v>111</v>
       </c>
@@ -5371,7 +5658,7 @@
       </c>
       <c r="I46" s="15"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="13" t="s">
         <v>113</v>
       </c>
@@ -5396,15 +5683,15 @@
       </c>
       <c r="I47" s="15"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="13" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="18" t="s">
+        <v>813</v>
+      </c>
+      <c r="C48" s="18" t="s">
         <v>116</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>117</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>103</v>
@@ -5421,12 +5708,12 @@
       </c>
       <c r="I48" s="15"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="19" t="s">
         <v>118</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>119</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>32</v>
@@ -5446,18 +5733,18 @@
       </c>
       <c r="I49" s="15"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="19" t="s">
         <v>120</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>121</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E50" s="19">
         <v>92</v>
@@ -5471,18 +5758,18 @@
       </c>
       <c r="I50" s="15"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="19" t="s">
         <v>123</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>124</v>
       </c>
       <c r="C51" s="19" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E51" s="19">
         <v>92</v>
@@ -5496,12 +5783,12 @@
       </c>
       <c r="I51" s="15"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>126</v>
       </c>
       <c r="C52" s="19" t="s">
         <v>32</v>
@@ -5521,12 +5808,12 @@
       </c>
       <c r="I52" s="15"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="19" t="s">
         <v>127</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>128</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>32</v>
@@ -5546,15 +5833,15 @@
       </c>
       <c r="I53" s="15"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="C54" s="17" t="s">
         <v>130</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>131</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>1</v>
@@ -5571,18 +5858,18 @@
       </c>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="C55" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="D55" s="17" t="s">
         <v>134</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>135</v>
       </c>
       <c r="E55" s="17">
         <v>90</v>
@@ -5598,18 +5885,18 @@
       </c>
       <c r="I55" s="15"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B56" s="17" t="s">
-        <v>137</v>
-      </c>
       <c r="C56" s="17" t="s">
-        <v>855</v>
+        <v>814</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E56" s="17">
         <v>90</v>
@@ -5623,15 +5910,15 @@
       </c>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="C57" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>39</v>
@@ -5650,18 +5937,18 @@
       </c>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="C58" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="D58" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D58" s="17" t="s">
-        <v>144</v>
       </c>
       <c r="E58" s="17">
         <v>49</v>
@@ -5675,18 +5962,18 @@
       </c>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="C59" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="D59" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="E59" s="14">
         <v>100</v>
@@ -5700,18 +5987,18 @@
       </c>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="C60" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E60" s="14">
         <v>100</v>
@@ -5725,18 +6012,18 @@
       </c>
       <c r="I60" s="15"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="C61" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C61" s="22" t="s">
-        <v>153</v>
-      </c>
       <c r="D61" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E61" s="22">
         <v>95</v>
@@ -5750,18 +6037,18 @@
       </c>
       <c r="I61" s="15"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="C62" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="22" t="s">
-        <v>156</v>
-      </c>
       <c r="D62" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E62" s="22">
         <v>108</v>
@@ -5775,18 +6062,18 @@
       </c>
       <c r="I62" s="15"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="22" t="s">
         <v>157</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>158</v>
       </c>
       <c r="C63" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E63" s="22">
         <v>91</v>
@@ -5800,18 +6087,18 @@
       </c>
       <c r="I63" s="15"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="C64" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="D64" s="22" t="s">
         <v>161</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>162</v>
       </c>
       <c r="E64" s="22">
         <v>98</v>
@@ -5825,18 +6112,18 @@
       </c>
       <c r="I64" s="15"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="C65" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C65" s="22" t="s">
-        <v>165</v>
-      </c>
       <c r="D65" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E65" s="22">
         <v>103</v>
@@ -5850,18 +6137,18 @@
       </c>
       <c r="I65" s="15"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="22" t="s">
         <v>166</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>167</v>
       </c>
       <c r="C66" s="22" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E66" s="22">
         <v>108</v>
@@ -5875,18 +6162,18 @@
       </c>
       <c r="I66" s="15"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A67" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="C67" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="D67" s="23" t="s">
         <v>170</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>171</v>
       </c>
       <c r="E67" s="23">
         <v>105</v>
@@ -5900,15 +6187,15 @@
       </c>
       <c r="I67" s="15"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A68" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="C68" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>174</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>39</v>
@@ -5925,12 +6212,12 @@
       </c>
       <c r="I68" s="15"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>7</v>
@@ -5950,12 +6237,12 @@
       </c>
       <c r="I69" s="15"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="14" t="s">
         <v>177</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>178</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>7</v>
@@ -5975,12 +6262,12 @@
       </c>
       <c r="I70" s="15"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>180</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>7</v>
@@ -6000,15 +6287,15 @@
       </c>
       <c r="I71" s="15"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B72" s="14" t="s">
-        <v>182</v>
-      </c>
       <c r="C72" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>39</v>
@@ -6025,12 +6312,12 @@
       </c>
       <c r="I72" s="15"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" s="14" t="s">
         <v>183</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>184</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>7</v>
@@ -6050,15 +6337,15 @@
       </c>
       <c r="I73" s="15"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B74" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="C74" s="14" t="s">
         <v>186</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>187</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>39</v>
@@ -6075,15 +6362,15 @@
       </c>
       <c r="I74" s="15"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="C75" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>39</v>
@@ -6100,15 +6387,15 @@
       </c>
       <c r="I75" s="15"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B76" s="14" t="s">
-        <v>191</v>
-      </c>
       <c r="C76" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>39</v>
@@ -6125,18 +6412,18 @@
       </c>
       <c r="I76" s="15"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B77" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="C77" s="14" t="s">
-        <v>73</v>
+        <v>815</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E77" s="14">
         <v>60</v>
@@ -6150,18 +6437,18 @@
       </c>
       <c r="I77" s="15"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="C78" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="C78" s="14" t="s">
-        <v>196</v>
-      </c>
       <c r="D78" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E78" s="14">
         <v>63</v>
@@ -6175,18 +6462,18 @@
       </c>
       <c r="I78" s="15"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="C79" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C79" s="15" t="s">
-        <v>199</v>
-      </c>
       <c r="D79" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E79" s="14">
         <v>64</v>
@@ -6200,18 +6487,18 @@
       </c>
       <c r="I79" s="15"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="C80" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C80" s="14" t="s">
-        <v>202</v>
-      </c>
       <c r="D80" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E80" s="14">
         <v>65</v>
@@ -6225,18 +6512,18 @@
       </c>
       <c r="I80" s="15"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>204</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E81" s="14">
         <v>60</v>
@@ -6250,18 +6537,18 @@
       </c>
       <c r="I81" s="15"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="C82" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C82" s="14" t="s">
-        <v>207</v>
-      </c>
       <c r="D82" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E82" s="14">
         <v>68</v>
@@ -6275,15 +6562,15 @@
       </c>
       <c r="I82" s="15"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B83" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B83" s="14" t="s">
-        <v>209</v>
-      </c>
       <c r="C83" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>39</v>
@@ -6300,18 +6587,18 @@
       </c>
       <c r="I83" s="15"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="B84" s="25" t="s">
-        <v>211</v>
-      </c>
       <c r="C84" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E84" s="25">
         <v>64</v>
@@ -6325,18 +6612,18 @@
       </c>
       <c r="I84" s="15"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="B85" s="25" t="s">
-        <v>213</v>
-      </c>
       <c r="C85" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E85" s="25">
         <v>64</v>
@@ -6350,18 +6637,18 @@
       </c>
       <c r="I85" s="15"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B86" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B86" s="14" t="s">
-        <v>215</v>
-      </c>
       <c r="C86" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E86" s="14">
         <v>65</v>
@@ -6375,18 +6662,18 @@
       </c>
       <c r="I86" s="15"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B87" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B87" s="14" t="s">
-        <v>217</v>
-      </c>
       <c r="C87" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E87" s="14">
         <v>65</v>
@@ -6400,18 +6687,18 @@
       </c>
       <c r="I87" s="15"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="B88" s="14" t="s">
-        <v>219</v>
-      </c>
       <c r="C88" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E88" s="14">
         <v>65</v>
@@ -6425,18 +6712,18 @@
       </c>
       <c r="I88" s="15"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A89" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="C89" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C89" s="14" t="s">
-        <v>222</v>
-      </c>
       <c r="D89" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E89" s="14">
         <v>68</v>
@@ -6450,18 +6737,18 @@
       </c>
       <c r="I89" s="15"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B90" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="C90" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="D90" s="14" t="s">
         <v>224</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>225</v>
       </c>
       <c r="E90" s="14">
         <v>78</v>
@@ -6475,18 +6762,18 @@
       </c>
       <c r="I90" s="15"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="C91" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="14" t="s">
-        <v>228</v>
-      </c>
       <c r="D91" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E91" s="14">
         <v>82</v>
@@ -6500,15 +6787,15 @@
       </c>
       <c r="I91" s="15"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>230</v>
-      </c>
       <c r="C92" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>39</v>
@@ -6525,15 +6812,15 @@
       </c>
       <c r="I92" s="15"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B93" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="C93" s="14" t="s">
         <v>232</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>233</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>39</v>
@@ -6550,15 +6837,15 @@
       </c>
       <c r="I93" s="15"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B94" s="14" t="s">
-        <v>235</v>
-      </c>
       <c r="C94" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>39</v>
@@ -6575,15 +6862,15 @@
       </c>
       <c r="I94" s="15"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="C95" s="14" t="s">
         <v>237</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>238</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>39</v>
@@ -6600,15 +6887,15 @@
       </c>
       <c r="I95" s="15"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B96" s="14" t="s">
-        <v>240</v>
-      </c>
       <c r="C96" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>39</v>
@@ -6625,18 +6912,18 @@
       </c>
       <c r="I96" s="15"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B97" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="14" t="s">
-        <v>242</v>
-      </c>
       <c r="C97" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E97" s="14">
         <v>94</v>
@@ -6650,12 +6937,12 @@
       </c>
       <c r="I97" s="15"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B98" s="14" t="s">
         <v>243</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>244</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>7</v>
@@ -6675,18 +6962,18 @@
       </c>
       <c r="I98" s="15"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B99" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B99" s="15" t="s">
-        <v>246</v>
-      </c>
       <c r="C99" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E99" s="14">
         <v>68</v>
@@ -6700,18 +6987,18 @@
       </c>
       <c r="I99" s="15"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A100" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B100" s="15" t="s">
         <v>247</v>
-      </c>
-      <c r="B100" s="15" t="s">
-        <v>248</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E100" s="14">
         <v>63</v>
@@ -6725,18 +7012,18 @@
       </c>
       <c r="I100" s="15"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A101" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B101" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="C101" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="C101" s="14" t="s">
-        <v>251</v>
-      </c>
       <c r="D101" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E101" s="14">
         <v>65</v>
@@ -6750,18 +7037,18 @@
       </c>
       <c r="I101" s="15"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A102" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B102" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="B102" s="26" t="s">
+      <c r="C102" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C102" s="26" t="s">
+      <c r="D102" s="26" t="s">
         <v>254</v>
-      </c>
-      <c r="D102" s="26" t="s">
-        <v>255</v>
       </c>
       <c r="E102" s="26">
         <v>148</v>
@@ -6775,18 +7062,18 @@
       </c>
       <c r="I102" s="15"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A103" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B103" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B103" s="26" t="s">
+      <c r="C103" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="C103" s="26" t="s">
+      <c r="D103" s="26" t="s">
         <v>258</v>
-      </c>
-      <c r="D103" s="26" t="s">
-        <v>259</v>
       </c>
       <c r="E103" s="26">
         <v>113</v>
@@ -6800,18 +7087,18 @@
       </c>
       <c r="I103" s="15"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A104" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B104" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="B104" s="26" t="s">
+      <c r="C104" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C104" s="26" t="s">
+      <c r="D104" s="26" t="s">
         <v>262</v>
-      </c>
-      <c r="D104" s="26" t="s">
-        <v>263</v>
       </c>
       <c r="E104" s="26">
         <v>125</v>
@@ -6825,18 +7112,18 @@
       </c>
       <c r="I104" s="15"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A105" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B105" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B105" s="26" t="s">
+      <c r="C105" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C105" s="26" t="s">
-        <v>266</v>
-      </c>
       <c r="D105" s="26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E105" s="26">
         <v>118</v>
@@ -6850,18 +7137,18 @@
       </c>
       <c r="I105" s="15"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A106" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B106" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="B106" s="26" t="s">
+      <c r="C106" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D106" s="26" t="s">
         <v>268</v>
-      </c>
-      <c r="C106" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" s="26" t="s">
-        <v>269</v>
       </c>
       <c r="E106" s="26">
         <v>140</v>
@@ -6875,15 +7162,15 @@
       </c>
       <c r="I106" s="15"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A107" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B107" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="C107" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>272</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>1</v>
@@ -6900,18 +7187,18 @@
       </c>
       <c r="I107" s="15"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A108" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B108" s="14" t="s">
         <v>273</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>274</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>53</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E108" s="14">
         <v>70</v>
@@ -6925,12 +7212,12 @@
       </c>
       <c r="I108" s="15"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A109" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B109" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>277</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>88</v>
@@ -6950,18 +7237,18 @@
       </c>
       <c r="I109" s="15"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A110" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B110" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="B110" s="14" t="s">
-        <v>279</v>
-      </c>
       <c r="C110" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E110" s="14">
         <v>88</v>
@@ -6975,18 +7262,18 @@
       </c>
       <c r="I110" s="15"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A111" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B111" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="B111" s="14" t="s">
-        <v>281</v>
-      </c>
       <c r="C111" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E111" s="14">
         <v>60</v>
@@ -7000,18 +7287,18 @@
       </c>
       <c r="I111" s="15"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A112" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B112" s="14" t="s">
         <v>282</v>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>283</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E112" s="15">
         <v>93</v>
@@ -7025,12 +7312,12 @@
       </c>
       <c r="I112" s="15"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A113" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B113" s="15" t="s">
         <v>284</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>285</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>7</v>
@@ -7050,18 +7337,18 @@
       </c>
       <c r="I113" s="15"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A114" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B114" s="15" t="s">
         <v>286</v>
-      </c>
-      <c r="B114" s="15" t="s">
-        <v>287</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E114" s="14">
         <v>100</v>
@@ -7075,15 +7362,15 @@
       </c>
       <c r="I114" s="15"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B115" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="C115" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>290</v>
       </c>
       <c r="D115" s="14" t="s">
         <v>39</v>
@@ -7100,18 +7387,18 @@
       </c>
       <c r="I115" s="15"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B116" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="C116" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="C116" s="14" t="s">
-        <v>293</v>
-      </c>
       <c r="D116" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E116" s="14">
         <v>61</v>
@@ -7125,12 +7412,12 @@
       </c>
       <c r="I116" s="15"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B117" s="14" t="s">
         <v>294</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>295</v>
       </c>
       <c r="C117" s="14" t="s">
         <v>7</v>
@@ -7150,18 +7437,18 @@
       </c>
       <c r="I117" s="15"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B118" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="C118" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C118" s="14" t="s">
-        <v>298</v>
-      </c>
       <c r="D118" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E118" s="14">
         <v>76</v>
@@ -7175,18 +7462,18 @@
       </c>
       <c r="I118" s="15"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B119" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="B119" s="14" t="s">
-        <v>300</v>
-      </c>
       <c r="C119" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E119" s="14">
         <v>76</v>
@@ -7200,18 +7487,18 @@
       </c>
       <c r="I119" s="15"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B120" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>302</v>
       </c>
       <c r="C120" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E120" s="14">
         <v>92</v>
@@ -7225,15 +7512,15 @@
       </c>
       <c r="I120" s="15"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A121" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B121" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="B121" s="14" t="s">
-        <v>304</v>
-      </c>
       <c r="C121" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>39</v>
@@ -7250,18 +7537,18 @@
       </c>
       <c r="I121" s="15"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B122" s="14" t="s">
         <v>305</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>306</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E122" s="14">
         <v>92</v>
@@ -7275,18 +7562,18 @@
       </c>
       <c r="I122" s="15"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A123" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B123" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="B123" s="27" t="s">
+      <c r="C123" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="C123" s="27" t="s">
+      <c r="D123" s="27" t="s">
         <v>309</v>
-      </c>
-      <c r="D123" s="27" t="s">
-        <v>310</v>
       </c>
       <c r="E123" s="14">
         <v>68</v>
@@ -7300,18 +7587,18 @@
       </c>
       <c r="I123" s="15"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A124" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="B124" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="C124" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="D124" s="14" t="s">
         <v>313</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>314</v>
       </c>
       <c r="E124" s="14">
         <v>105</v>
@@ -7325,18 +7612,18 @@
       </c>
       <c r="I124" s="15"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A125" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="B125" s="14" t="s">
         <v>315</v>
-      </c>
-      <c r="B125" s="14" t="s">
-        <v>316</v>
       </c>
       <c r="C125" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E125" s="14">
         <v>92</v>
@@ -7350,12 +7637,12 @@
       </c>
       <c r="I125" s="15"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A126" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="B126" s="14" t="s">
         <v>317</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>318</v>
       </c>
       <c r="C126" s="14" t="s">
         <v>4</v>
@@ -7375,18 +7662,18 @@
       </c>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A127" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B127" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="C127" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C127" s="14" t="s">
+      <c r="D127" s="14" t="s">
         <v>321</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>322</v>
       </c>
       <c r="E127" s="14">
         <v>86</v>
@@ -7400,15 +7687,15 @@
       </c>
       <c r="I127" s="15"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A128" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B128" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="B128" s="14" t="s">
-        <v>324</v>
-      </c>
       <c r="C128" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D128" s="14" t="s">
         <v>1</v>
@@ -7425,12 +7712,12 @@
       </c>
       <c r="I128" s="15"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B129" s="14" t="s">
         <v>325</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>326</v>
       </c>
       <c r="C129" s="14" t="s">
         <v>32</v>
@@ -7450,12 +7737,12 @@
       </c>
       <c r="I129" s="15"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="B130" s="28" t="s">
         <v>327</v>
-      </c>
-      <c r="B130" s="28" t="s">
-        <v>328</v>
       </c>
       <c r="C130" s="28" t="s">
         <v>32</v>
@@ -7475,18 +7762,18 @@
       </c>
       <c r="I130" s="15"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A131" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B131" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="B131" s="28" t="s">
-        <v>330</v>
-      </c>
       <c r="C131" s="28" t="s">
-        <v>856</v>
+        <v>816</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131" s="28">
         <v>90</v>
@@ -7500,18 +7787,18 @@
       </c>
       <c r="I131" s="15"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A132" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="B132" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="B132" s="28" t="s">
+      <c r="C132" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="C132" s="28" t="s">
+      <c r="D132" s="28" t="s">
         <v>333</v>
-      </c>
-      <c r="D132" s="28" t="s">
-        <v>334</v>
       </c>
       <c r="E132" s="28">
         <v>120</v>
@@ -7525,18 +7812,18 @@
       </c>
       <c r="I132" s="15"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A133" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="B133" s="28" t="s">
         <v>335</v>
-      </c>
-      <c r="B133" s="28" t="s">
-        <v>336</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>7</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E133" s="28">
         <v>98</v>
@@ -7550,18 +7837,18 @@
       </c>
       <c r="I133" s="15"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A134" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="B134" s="29" t="s">
         <v>338</v>
-      </c>
-      <c r="B134" s="29" t="s">
-        <v>339</v>
       </c>
       <c r="C134" s="29" t="s">
         <v>32</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E134" s="29"/>
       <c r="F134" s="13"/>
@@ -7573,18 +7860,18 @@
       </c>
       <c r="I134" s="15"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B135" s="30" t="s">
         <v>341</v>
-      </c>
-      <c r="B135" s="30" t="s">
-        <v>342</v>
       </c>
       <c r="C135" s="30" t="s">
         <v>85</v>
       </c>
       <c r="D135" s="30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E135" s="30">
         <v>88</v>
@@ -7598,18 +7885,18 @@
       </c>
       <c r="I135" s="15"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B136" s="30" t="s">
         <v>343</v>
-      </c>
-      <c r="B136" s="30" t="s">
-        <v>344</v>
       </c>
       <c r="C136" s="30" t="s">
         <v>85</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E136" s="30">
         <v>88</v>
@@ -7623,18 +7910,18 @@
       </c>
       <c r="I136" s="15"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B137" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="B137" s="30" t="s">
+      <c r="C137" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="C137" s="30" t="s">
+      <c r="D137" s="30" t="s">
         <v>347</v>
-      </c>
-      <c r="D137" s="30" t="s">
-        <v>348</v>
       </c>
       <c r="E137" s="30">
         <v>103</v>
@@ -7648,18 +7935,18 @@
       </c>
       <c r="I137" s="15"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A138" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="B138" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="B138" s="30" t="s">
+      <c r="C138" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="C138" s="30" t="s">
-        <v>351</v>
-      </c>
       <c r="D138" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E138" s="30">
         <v>102</v>
@@ -7673,18 +7960,18 @@
       </c>
       <c r="I138" s="15"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B139" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="B139" s="30" t="s">
+      <c r="C139" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C139" s="30" t="s">
-        <v>354</v>
-      </c>
       <c r="D139" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E139" s="30">
         <v>110</v>
@@ -7698,18 +7985,18 @@
       </c>
       <c r="I139" s="15"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A140" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="B140" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="B140" s="30" t="s">
+      <c r="C140" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="C140" s="30" t="s">
-        <v>357</v>
-      </c>
       <c r="D140" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E140" s="30">
         <v>113</v>
@@ -7723,18 +8010,18 @@
       </c>
       <c r="I140" s="15"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B141" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="B141" s="30" t="s">
-        <v>359</v>
-      </c>
       <c r="C141" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D141" s="30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E141" s="30">
         <v>95</v>
@@ -7748,12 +8035,12 @@
       </c>
       <c r="I141" s="15"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A142" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="B142" s="15" t="s">
         <v>360</v>
-      </c>
-      <c r="B142" s="15" t="s">
-        <v>361</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>7</v>
@@ -7773,18 +8060,18 @@
       </c>
       <c r="I142" s="15"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A143" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="B143" s="14" t="s">
         <v>362</v>
-      </c>
-      <c r="B143" s="14" t="s">
-        <v>363</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E143" s="14">
         <v>57</v>
@@ -7798,18 +8085,18 @@
       </c>
       <c r="I143" s="15"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A144" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="B144" s="14" t="s">
         <v>364</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>365</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E144" s="14">
         <v>62</v>
@@ -7823,18 +8110,18 @@
       </c>
       <c r="I144" s="15"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A145" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B145" s="14" t="s">
         <v>366</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>367</v>
       </c>
       <c r="C145" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E145" s="14">
         <v>62</v>
@@ -7848,18 +8135,18 @@
       </c>
       <c r="I145" s="15"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A146" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="B146" s="14" t="s">
         <v>368</v>
-      </c>
-      <c r="B146" s="14" t="s">
-        <v>369</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E146" s="14">
         <v>62</v>
@@ -7873,18 +8160,18 @@
       </c>
       <c r="I146" s="15"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A147" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B147" s="14" t="s">
         <v>370</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>371</v>
       </c>
       <c r="C147" s="14" t="s">
         <v>73</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E147" s="14">
         <v>62</v>
@@ -7898,12 +8185,12 @@
       </c>
       <c r="I147" s="15"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A148" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B148" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="B148" s="15" t="s">
-        <v>373</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>7</v>
@@ -7923,15 +8210,15 @@
       </c>
       <c r="I148" s="15"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A149" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="B149" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B149" s="14" t="s">
+      <c r="C149" s="14" t="s">
         <v>375</v>
-      </c>
-      <c r="C149" s="14" t="s">
-        <v>376</v>
       </c>
       <c r="D149" s="14" t="s">
         <v>17</v>
@@ -7948,18 +8235,18 @@
       </c>
       <c r="I149" s="15"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A150" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="B150" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="B150" s="14" t="s">
+      <c r="C150" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="D150" s="14" t="s">
         <v>379</v>
-      </c>
-      <c r="D150" s="14" t="s">
-        <v>380</v>
       </c>
       <c r="E150" s="14">
         <v>97</v>
@@ -7973,12 +8260,12 @@
       </c>
       <c r="I150" s="15"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A151" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="B151" s="15" t="s">
         <v>381</v>
-      </c>
-      <c r="B151" s="15" t="s">
-        <v>382</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>7</v>
@@ -7998,18 +8285,18 @@
       </c>
       <c r="I151" s="15"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A152" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B152" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B152" s="17" t="s">
+      <c r="C152" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C152" s="17" t="s">
+      <c r="D152" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="D152" s="17" t="s">
-        <v>386</v>
       </c>
       <c r="E152" s="17">
         <v>90</v>
@@ -8021,22 +8308,22 @@
         <v>208</v>
       </c>
       <c r="H152" s="17">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I152" s="15"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A153" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="B153" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B153" s="17" t="s">
+      <c r="C153" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="17" t="s">
-        <v>389</v>
-      </c>
       <c r="D153" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E153" s="17">
         <v>100</v>
@@ -8048,22 +8335,22 @@
         <v>216</v>
       </c>
       <c r="H153" s="17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I153" s="15"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A154" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="B154" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="B154" s="14" t="s">
+      <c r="C154" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="C154" s="14" t="s">
+      <c r="D154" s="14" t="s">
         <v>392</v>
-      </c>
-      <c r="D154" s="14" t="s">
-        <v>393</v>
       </c>
       <c r="E154" s="14">
         <v>96</v>
@@ -8075,22 +8362,22 @@
         <v>208</v>
       </c>
       <c r="H154" s="14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I154" s="15"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A155" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="B155" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="B155" s="14" t="s">
-        <v>395</v>
-      </c>
       <c r="C155" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D155" s="14" t="s">
         <v>392</v>
-      </c>
-      <c r="D155" s="14" t="s">
-        <v>393</v>
       </c>
       <c r="E155" s="14">
         <v>95</v>
@@ -8106,18 +8393,18 @@
       </c>
       <c r="I155" s="15"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A156" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="B156" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="B156" s="14" t="s">
+      <c r="C156" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="C156" s="14" t="s">
-        <v>398</v>
-      </c>
       <c r="D156" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E156" s="14">
         <v>107</v>
@@ -8129,22 +8416,22 @@
         <v>215</v>
       </c>
       <c r="H156" s="14">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I156" s="15"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A157" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="B157" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="B157" s="17" t="s">
+      <c r="C157" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="C157" s="17" t="s">
-        <v>401</v>
-      </c>
       <c r="D157" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E157" s="17">
         <v>92</v>
@@ -8160,18 +8447,18 @@
       </c>
       <c r="I157" s="15"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A158" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="B158" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="B158" s="31" t="s">
-        <v>403</v>
-      </c>
       <c r="C158" s="31" t="s">
-        <v>857</v>
+        <v>817</v>
       </c>
       <c r="D158" s="31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E158" s="31">
         <v>94</v>
@@ -8187,18 +8474,18 @@
       </c>
       <c r="I158" s="15"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A159" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B159" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="C159" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="C159" s="14" t="s">
-        <v>406</v>
-      </c>
       <c r="D159" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E159" s="14">
         <v>120</v>
@@ -8212,18 +8499,18 @@
       </c>
       <c r="I159" s="15"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A160" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="B160" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="C160" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="D160" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="D160" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="E160" s="14">
         <v>85</v>
@@ -8237,18 +8524,18 @@
       </c>
       <c r="I160" s="15"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A161" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>818</v>
+      </c>
+      <c r="C161" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="B161" s="26" t="s">
-        <v>858</v>
-      </c>
-      <c r="C161" s="26" t="s">
+      <c r="D161" s="26" t="s">
         <v>412</v>
-      </c>
-      <c r="D161" s="26" t="s">
-        <v>413</v>
       </c>
       <c r="E161" s="26">
         <v>104</v>
@@ -8264,18 +8551,18 @@
       </c>
       <c r="I161" s="15"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A162" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="B162" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="B162" s="26" t="s">
+      <c r="C162" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="C162" s="26" t="s">
-        <v>416</v>
-      </c>
       <c r="D162" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E162" s="26">
         <v>117</v>
@@ -8291,18 +8578,18 @@
       </c>
       <c r="I162" s="15"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A163" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="B163" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="B163" s="26" t="s">
+      <c r="C163" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="C163" s="26" t="s">
-        <v>419</v>
-      </c>
       <c r="D163" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E163" s="26">
         <v>117</v>
@@ -8318,18 +8605,18 @@
       </c>
       <c r="I163" s="15"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A164" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="C164" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="B164" s="26" t="s">
-        <v>859</v>
-      </c>
-      <c r="C164" s="26" t="s">
-        <v>421</v>
-      </c>
       <c r="D164" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E164" s="26">
         <v>110</v>
@@ -8341,22 +8628,22 @@
         <v>208</v>
       </c>
       <c r="H164" s="26">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I164" s="15"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A165" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B165" s="26" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="C165" s="26" t="s">
-        <v>861</v>
+        <v>821</v>
       </c>
       <c r="D165" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E165" s="26">
         <v>108</v>
@@ -8372,9 +8659,9 @@
       </c>
       <c r="I165" s="15"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A166" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B166" s="34"/>
       <c r="C166" s="34"/>
@@ -8385,18 +8672,18 @@
       <c r="H166" s="34"/>
       <c r="I166" s="15"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A167" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>863</v>
+        <v>823</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>864</v>
+        <v>824</v>
       </c>
       <c r="E167" s="22">
         <v>80</v>
@@ -8412,18 +8699,18 @@
       </c>
       <c r="I167" s="15"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A168" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>865</v>
+        <v>825</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>416</v>
+        <v>826</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>866</v>
+        <v>827</v>
       </c>
       <c r="E168" s="22">
         <v>110</v>
@@ -8439,18 +8726,18 @@
       </c>
       <c r="I168" s="15"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A169" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="B169" s="22" t="s">
+        <v>828</v>
+      </c>
+      <c r="C169" s="22" t="s">
         <v>426</v>
       </c>
-      <c r="B169" s="22" t="s">
-        <v>867</v>
-      </c>
-      <c r="C169" s="22" t="s">
+      <c r="D169" s="22" t="s">
         <v>427</v>
-      </c>
-      <c r="D169" s="22" t="s">
-        <v>428</v>
       </c>
       <c r="E169" s="22">
         <v>83</v>
@@ -8462,22 +8749,22 @@
         <v>208</v>
       </c>
       <c r="H169" s="22">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I169" s="36"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A170" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="B170" s="22" t="s">
+        <v>829</v>
+      </c>
+      <c r="C170" s="22" t="s">
         <v>429</v>
       </c>
-      <c r="B170" s="22" t="s">
-        <v>868</v>
-      </c>
-      <c r="C170" s="22" t="s">
-        <v>430</v>
-      </c>
       <c r="D170" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E170" s="36">
         <v>110</v>
@@ -8493,18 +8780,18 @@
       </c>
       <c r="I170" s="36"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A171" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>869</v>
+        <v>830</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E171" s="36">
         <v>112</v>
@@ -8520,18 +8807,18 @@
       </c>
       <c r="I171" s="36"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A172" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="B172" s="22" t="s">
         <v>432</v>
       </c>
-      <c r="B172" s="22" t="s">
-        <v>433</v>
-      </c>
       <c r="C172" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E172" s="22">
         <v>112</v>
@@ -8547,18 +8834,18 @@
       </c>
       <c r="I172" s="36"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A173" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="B173" s="22" t="s">
+        <v>831</v>
+      </c>
+      <c r="C173" s="22" t="s">
         <v>434</v>
       </c>
-      <c r="B173" s="22" t="s">
-        <v>870</v>
-      </c>
-      <c r="C173" s="22" t="s">
+      <c r="D173" s="22" t="s">
         <v>435</v>
-      </c>
-      <c r="D173" s="22" t="s">
-        <v>436</v>
       </c>
       <c r="E173" s="22">
         <v>102</v>
@@ -8574,24 +8861,24 @@
       </c>
       <c r="I173" s="36"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A174" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="B174" s="22" t="s">
+        <v>832</v>
+      </c>
+      <c r="C174" s="22" t="s">
         <v>437</v>
       </c>
-      <c r="B174" s="22" t="s">
-        <v>871</v>
-      </c>
-      <c r="C174" s="22" t="s">
-        <v>438</v>
-      </c>
       <c r="D174" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E174" s="36">
         <v>130</v>
       </c>
       <c r="F174" s="35">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G174" s="36">
         <v>215</v>
@@ -8601,18 +8888,18 @@
       </c>
       <c r="I174" s="36"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A175" s="35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>872</v>
+        <v>833</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E175" s="36">
         <v>135</v>
@@ -8628,18 +8915,18 @@
       </c>
       <c r="I175" s="36"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A176" s="35" t="s">
+        <v>439</v>
+      </c>
+      <c r="B176" s="22" t="s">
         <v>440</v>
-      </c>
-      <c r="B176" s="22" t="s">
-        <v>441</v>
       </c>
       <c r="C176" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E176" s="22">
         <v>135</v>
@@ -8655,18 +8942,18 @@
       </c>
       <c r="I176" s="36"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A177" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="B177" s="22" t="s">
         <v>442</v>
       </c>
-      <c r="B177" s="22" t="s">
+      <c r="C177" s="22" t="s">
         <v>443</v>
       </c>
-      <c r="C177" s="22" t="s">
-        <v>444</v>
-      </c>
       <c r="D177" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E177" s="22">
         <v>150</v>
@@ -8678,22 +8965,22 @@
         <v>215</v>
       </c>
       <c r="H177" s="22">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I177" s="36"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A178" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>873</v>
+        <v>834</v>
       </c>
       <c r="C178" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E178" s="22">
         <v>106</v>
@@ -8709,18 +8996,18 @@
       </c>
       <c r="I178" s="36"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A179" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="B179" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B179" s="22" t="s">
+      <c r="C179" s="22" t="s">
         <v>447</v>
       </c>
-      <c r="C179" s="22" t="s">
-        <v>448</v>
-      </c>
       <c r="D179" s="37" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E179" s="22">
         <v>110</v>
@@ -8736,18 +9023,18 @@
       </c>
       <c r="I179" s="36"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A180" s="35" t="s">
+        <v>448</v>
+      </c>
+      <c r="B180" s="22" t="s">
+        <v>835</v>
+      </c>
+      <c r="C180" s="22" t="s">
         <v>449</v>
       </c>
-      <c r="B180" s="22" t="s">
-        <v>874</v>
-      </c>
-      <c r="C180" s="22" t="s">
-        <v>450</v>
-      </c>
       <c r="D180" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E180" s="22">
         <v>96</v>
@@ -8763,18 +9050,18 @@
       </c>
       <c r="I180" s="36"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A181" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>875</v>
+        <v>836</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E181" s="22">
         <v>150</v>
@@ -8786,22 +9073,22 @@
         <v>215</v>
       </c>
       <c r="H181" s="22">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I181" s="15"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A182" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B182" s="38" t="s">
+        <v>837</v>
+      </c>
+      <c r="C182" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="D182" s="38" t="s">
         <v>452</v>
-      </c>
-      <c r="B182" s="38" t="s">
-        <v>876</v>
-      </c>
-      <c r="C182" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="D182" s="38" t="s">
-        <v>453</v>
       </c>
       <c r="E182" s="38">
         <v>108</v>
@@ -8817,18 +9104,18 @@
       </c>
       <c r="I182" s="15"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A183" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B183" s="38" t="s">
-        <v>877</v>
+        <v>838</v>
       </c>
       <c r="C183" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D183" s="38" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E183" s="38">
         <v>108</v>
@@ -8844,18 +9131,18 @@
       </c>
       <c r="I183" s="15"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A184" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="B184" s="39" t="s">
         <v>455</v>
       </c>
-      <c r="B184" s="39" t="s">
+      <c r="C184" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="C184" s="39" t="s">
+      <c r="D184" s="39" t="s">
         <v>457</v>
-      </c>
-      <c r="D184" s="39" t="s">
-        <v>458</v>
       </c>
       <c r="E184" s="39">
         <v>150</v>
@@ -8871,18 +9158,18 @@
       </c>
       <c r="I184" s="42"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A185" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>878</v>
+        <v>839</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>444</v>
+        <v>768</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>428</v>
+        <v>840</v>
       </c>
       <c r="E185" s="22">
         <v>112</v>
@@ -8898,18 +9185,18 @@
       </c>
       <c r="I185" s="15"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A186" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B186" s="38" t="s">
-        <v>879</v>
+        <v>841</v>
       </c>
       <c r="C186" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D186" s="38" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E186" s="38">
         <v>108</v>
@@ -8925,18 +9212,18 @@
       </c>
       <c r="I186" s="15"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187" s="13" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>238</v>
+        <v>843</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E187" s="22">
         <v>150</v>
@@ -8948,22 +9235,22 @@
         <v>215</v>
       </c>
       <c r="H187" s="22">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="I187" s="15"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A188" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>881</v>
+        <v>844</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>272</v>
+        <v>845</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>882</v>
+        <v>846</v>
       </c>
       <c r="E188" s="22">
         <v>110</v>
@@ -8979,18 +9266,18 @@
       </c>
       <c r="I188" s="15"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A189" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>883</v>
+        <v>847</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E189" s="22">
         <v>150</v>
@@ -9002,22 +9289,22 @@
         <v>215</v>
       </c>
       <c r="H189" s="22">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I189" s="15"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A190" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>884</v>
+        <v>848</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>885</v>
+        <v>849</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>886</v>
+        <v>850</v>
       </c>
       <c r="E190" s="15">
         <v>152</v>
@@ -9033,18 +9320,18 @@
       </c>
       <c r="I190" s="15"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A191" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>238</v>
+        <v>843</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E191" s="36">
         <v>150</v>
@@ -9060,9 +9347,9 @@
       </c>
       <c r="I191" s="15"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A192" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B192" s="31"/>
       <c r="C192" s="31"/>
@@ -9073,9 +9360,9 @@
       <c r="H192" s="31"/>
       <c r="I192" s="15"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B193" s="31"/>
       <c r="C193" s="31"/>
@@ -9086,18 +9373,18 @@
       <c r="H193" s="43"/>
       <c r="I193" s="41"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A194" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B194" s="45" t="s">
-        <v>887</v>
+        <v>852</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>385</v>
+        <v>853</v>
       </c>
       <c r="D194" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E194" s="45">
         <v>138</v>
@@ -9113,15 +9400,15 @@
       </c>
       <c r="I194" s="41"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A195" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B195" s="45" t="s">
+        <v>854</v>
+      </c>
+      <c r="C195" s="46" t="s">
         <v>468</v>
-      </c>
-      <c r="B195" s="45" t="s">
-        <v>888</v>
-      </c>
-      <c r="C195" s="46" t="s">
-        <v>469</v>
       </c>
       <c r="D195" s="47" t="s">
         <v>39</v>
@@ -9140,18 +9427,18 @@
       </c>
       <c r="I195" s="41"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A196" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B196" s="49" t="s">
+        <v>855</v>
+      </c>
+      <c r="C196" s="49" t="s">
+        <v>856</v>
+      </c>
+      <c r="D196" s="49" t="s">
         <v>470</v>
-      </c>
-      <c r="B196" s="49" t="s">
-        <v>889</v>
-      </c>
-      <c r="C196" s="49" t="s">
-        <v>890</v>
-      </c>
-      <c r="D196" s="49" t="s">
-        <v>471</v>
       </c>
       <c r="E196" s="49">
         <v>105</v>
@@ -9167,18 +9454,18 @@
       </c>
       <c r="I196" s="15"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B197" s="49" t="s">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>389</v>
+        <v>858</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E197" s="49">
         <v>100</v>
@@ -9194,18 +9481,18 @@
       </c>
       <c r="I197" s="41"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A198" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="B198" s="49" t="s">
+        <v>859</v>
+      </c>
+      <c r="C198" s="49" t="s">
         <v>473</v>
       </c>
-      <c r="B198" s="49" t="s">
-        <v>892</v>
-      </c>
-      <c r="C198" s="49" t="s">
+      <c r="D198" s="49" t="s">
         <v>474</v>
-      </c>
-      <c r="D198" s="49" t="s">
-        <v>475</v>
       </c>
       <c r="E198" s="49">
         <v>129</v>
@@ -9221,18 +9508,18 @@
       </c>
       <c r="I198" s="41"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A199" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>893</v>
+        <v>860</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>401</v>
+        <v>861</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>894</v>
+        <v>862</v>
       </c>
       <c r="E199" s="49">
         <v>95</v>
@@ -9248,9 +9535,9 @@
       </c>
       <c r="I199" s="41"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A200" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B200" s="34"/>
       <c r="C200" s="34"/>
@@ -9261,9 +9548,9 @@
       <c r="H200" s="34"/>
       <c r="I200" s="41"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A201" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -9274,9 +9561,9 @@
       <c r="H201" s="14"/>
       <c r="I201" s="41"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A202" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -9287,9 +9574,9 @@
       <c r="H202" s="14"/>
       <c r="I202" s="41"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A203" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -9300,18 +9587,18 @@
       <c r="H203" s="14"/>
       <c r="I203" s="41"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A204" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B204" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="B204" s="28" t="s">
+      <c r="C204" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="C204" s="28" t="s">
+      <c r="D204" s="28" t="s">
         <v>483</v>
-      </c>
-      <c r="D204" s="28" t="s">
-        <v>484</v>
       </c>
       <c r="E204" s="28"/>
       <c r="F204" s="51">
@@ -9325,18 +9612,18 @@
       </c>
       <c r="I204" s="41"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A205" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B205" s="28" t="s">
         <v>485</v>
       </c>
-      <c r="B205" s="28" t="s">
+      <c r="C205" s="28" t="s">
         <v>486</v>
       </c>
-      <c r="C205" s="28" t="s">
+      <c r="D205" s="52" t="s">
         <v>487</v>
-      </c>
-      <c r="D205" s="52" t="s">
-        <v>488</v>
       </c>
       <c r="E205" s="28">
         <v>47</v>
@@ -9352,18 +9639,18 @@
       </c>
       <c r="I205" s="15"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A206" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B206" s="28" t="s">
         <v>489</v>
       </c>
-      <c r="B206" s="28" t="s">
+      <c r="C206" s="28" t="s">
         <v>490</v>
       </c>
-      <c r="C206" s="28" t="s">
-        <v>491</v>
-      </c>
       <c r="D206" s="52" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E206" s="28">
         <v>47</v>
@@ -9379,18 +9666,18 @@
       </c>
       <c r="I206" s="15"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A207" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="B207" s="31" t="s">
         <v>492</v>
-      </c>
-      <c r="B207" s="31" t="s">
-        <v>493</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>53</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E207" s="14"/>
       <c r="F207" s="40"/>
@@ -9402,15 +9689,15 @@
       </c>
       <c r="I207" s="41"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A208" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="B208" s="31" t="s">
         <v>494</v>
       </c>
-      <c r="B208" s="31" t="s">
-        <v>495</v>
-      </c>
       <c r="C208" s="14" t="s">
-        <v>895</v>
+        <v>863</v>
       </c>
       <c r="D208" s="14" t="s">
         <v>39</v>
@@ -9429,18 +9716,18 @@
       </c>
       <c r="I208" s="15"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A209" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="B209" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="B209" s="14" t="s">
-        <v>497</v>
-      </c>
       <c r="C209" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E209" s="14"/>
       <c r="F209" s="40"/>
@@ -9452,9 +9739,9 @@
       </c>
       <c r="I209" s="41"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A210" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -9465,15 +9752,15 @@
       <c r="H210" s="14"/>
       <c r="I210" s="41"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A211" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B211" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="B211" s="14" t="s">
-        <v>500</v>
-      </c>
       <c r="C211" s="14" t="s">
-        <v>896</v>
+        <v>864</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>39</v>
@@ -9490,18 +9777,18 @@
       </c>
       <c r="I211" s="41"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A212" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B212" s="39" t="s">
-        <v>897</v>
+        <v>865</v>
       </c>
       <c r="C212" s="39" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
       <c r="D212" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E212" s="39">
         <v>62</v>
@@ -9515,18 +9802,18 @@
       </c>
       <c r="I212" s="41"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A213" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="B213" s="14" t="s">
         <v>502</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="C213" s="14" t="s">
         <v>503</v>
       </c>
-      <c r="C213" s="14" t="s">
-        <v>504</v>
-      </c>
       <c r="D213" s="14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E213" s="14">
         <v>52</v>
@@ -9542,18 +9829,18 @@
       </c>
       <c r="I213" s="41"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A214" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="B214" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="B214" s="14" t="s">
-        <v>506</v>
-      </c>
       <c r="C214" s="39" t="s">
-        <v>898</v>
+        <v>867</v>
       </c>
       <c r="D214" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E214" s="14">
         <v>65</v>
@@ -9567,9 +9854,9 @@
       </c>
       <c r="I214" s="41"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A215" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B215" s="34"/>
       <c r="C215" s="34"/>
@@ -9580,18 +9867,18 @@
       <c r="H215" s="34"/>
       <c r="I215" s="41"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A216" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B216" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="B216" s="14" t="s">
+      <c r="C216" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="C216" s="14" t="s">
+      <c r="D216" s="14" t="s">
         <v>510</v>
-      </c>
-      <c r="D216" s="14" t="s">
-        <v>511</v>
       </c>
       <c r="E216" s="14">
         <v>69</v>
@@ -9605,9 +9892,9 @@
       </c>
       <c r="I216" s="41"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A217" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B217" s="34"/>
       <c r="C217" s="34"/>
@@ -9618,9 +9905,9 @@
       <c r="H217" s="34"/>
       <c r="I217" s="15"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A218" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -9631,18 +9918,18 @@
       <c r="H218" s="14"/>
       <c r="I218" s="41"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A219" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="B219" s="39" t="s">
         <v>514</v>
       </c>
-      <c r="B219" s="39" t="s">
+      <c r="C219" s="39" t="s">
         <v>515</v>
       </c>
-      <c r="C219" s="39" t="s">
+      <c r="D219" s="39" t="s">
         <v>516</v>
-      </c>
-      <c r="D219" s="39" t="s">
-        <v>517</v>
       </c>
       <c r="E219" s="39">
         <v>90</v>
@@ -9658,18 +9945,18 @@
       </c>
       <c r="I219" s="41"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A220" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B220" s="14" t="s">
+        <v>868</v>
+      </c>
+      <c r="C220" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="D220" s="53" t="s">
         <v>518</v>
-      </c>
-      <c r="B220" s="14" t="s">
-        <v>899</v>
-      </c>
-      <c r="C220" s="14" t="s">
-        <v>900</v>
-      </c>
-      <c r="D220" s="53" t="s">
-        <v>519</v>
       </c>
       <c r="E220" s="14">
         <v>120</v>
@@ -9684,21 +9971,21 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A221" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>902</v>
+        <v>871</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>903</v>
+        <v>872</v>
       </c>
       <c r="D221" s="53" t="s">
-        <v>1</v>
+        <v>873</v>
       </c>
       <c r="E221" s="14">
         <v>100</v>
@@ -9713,21 +10000,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="41" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A222" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>905</v>
+        <v>875</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>906</v>
+        <v>876</v>
       </c>
       <c r="D222" s="53" t="s">
-        <v>519</v>
+        <v>877</v>
       </c>
       <c r="E222" s="14">
         <v>115</v>
@@ -9743,15 +10030,15 @@
       </c>
       <c r="I222" s="41"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A223" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B223" s="39" t="s">
         <v>522</v>
       </c>
-      <c r="B223" s="39" t="s">
+      <c r="C223" s="39" t="s">
         <v>523</v>
-      </c>
-      <c r="C223" s="39" t="s">
-        <v>524</v>
       </c>
       <c r="D223" s="54" t="s">
         <v>1</v>
@@ -9770,18 +10057,18 @@
       </c>
       <c r="I223" s="41"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A224" s="13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B224" s="39" t="s">
-        <v>907</v>
+        <v>878</v>
       </c>
       <c r="C224" s="39" t="s">
-        <v>908</v>
+        <v>879</v>
       </c>
       <c r="D224" s="39" t="s">
-        <v>909</v>
+        <v>880</v>
       </c>
       <c r="E224" s="39">
         <v>120</v>
@@ -9797,18 +10084,18 @@
       </c>
       <c r="I224" s="41"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A225" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B225" s="31" t="s">
         <v>526</v>
       </c>
-      <c r="B225" s="31" t="s">
+      <c r="C225" s="39" t="s">
         <v>527</v>
       </c>
-      <c r="C225" s="39" t="s">
-        <v>528</v>
-      </c>
       <c r="D225" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E225" s="39">
         <v>135</v>
@@ -9824,18 +10111,18 @@
       </c>
       <c r="I225" s="15"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A226" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B226" s="39" t="s">
-        <v>910</v>
+        <v>881</v>
       </c>
       <c r="C226" s="39" t="s">
-        <v>238</v>
+        <v>843</v>
       </c>
       <c r="D226" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E226" s="39">
         <v>145</v>
@@ -9847,22 +10134,22 @@
         <v>215</v>
       </c>
       <c r="H226" s="39">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I226" s="41"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A227" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B227" s="39" t="s">
-        <v>911</v>
+        <v>882</v>
       </c>
       <c r="C227" s="39" t="s">
-        <v>238</v>
+        <v>843</v>
       </c>
       <c r="D227" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E227" s="39">
         <v>145</v>
@@ -9874,22 +10161,22 @@
         <v>215</v>
       </c>
       <c r="H227" s="39">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I227" s="41"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A228" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B228" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="B228" s="39" t="s">
-        <v>532</v>
-      </c>
       <c r="C228" s="39" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D228" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E228" s="39">
         <v>150</v>
@@ -9905,18 +10192,18 @@
       </c>
       <c r="I228" s="15"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A229" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B229" s="39" t="s">
         <v>533</v>
       </c>
-      <c r="B229" s="39" t="s">
-        <v>534</v>
-      </c>
       <c r="C229" s="39" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D229" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E229" s="39">
         <v>150</v>
@@ -9928,22 +10215,22 @@
         <v>215</v>
       </c>
       <c r="H229" s="39">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I229" s="15"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A230" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="B230" s="55" t="s">
         <v>535</v>
       </c>
-      <c r="B230" s="55" t="s">
-        <v>536</v>
-      </c>
       <c r="C230" s="55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D230" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E230" s="55">
         <v>145</v>
@@ -9955,13 +10242,13 @@
         <v>215</v>
       </c>
       <c r="H230" s="55">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I230" s="15"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A231" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B231" s="22"/>
       <c r="C231" s="22"/>
@@ -9972,9 +10259,9 @@
       <c r="H231" s="22"/>
       <c r="I231" s="15"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A232" s="13" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B232" s="39"/>
       <c r="C232" s="39"/>
@@ -9985,41 +10272,45 @@
       <c r="H232" s="39"/>
       <c r="I232" s="41"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A233" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="B233" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="B233" s="39" t="s">
+      <c r="C233" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="C233" s="39" t="s">
+      <c r="D233" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="D233" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="E233" s="39"/>
-      <c r="F233" s="40"/>
+      <c r="E233" s="39">
+        <v>185</v>
+      </c>
+      <c r="F233" s="40">
+        <v>270</v>
+      </c>
       <c r="G233" s="41">
         <v>215</v>
       </c>
       <c r="H233" s="39">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I233" s="41"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A234" s="13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B234" s="56" t="s">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="C234" s="56" t="s">
-        <v>913</v>
+        <v>884</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>914</v>
+        <v>885</v>
       </c>
       <c r="E234" s="56">
         <v>190</v>
@@ -10034,21 +10325,21 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="57" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A235" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>916</v>
+        <v>887</v>
       </c>
       <c r="C235" s="55" t="s">
-        <v>917</v>
+        <v>888</v>
       </c>
       <c r="D235" s="55" t="s">
-        <v>918</v>
+        <v>889</v>
       </c>
       <c r="E235" s="55">
         <v>155</v>
@@ -10060,15 +10351,15 @@
         <v>215</v>
       </c>
       <c r="H235" s="55">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I235" s="58" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A236" s="13" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9">
-      <c r="A236" s="13" t="s">
-        <v>546</v>
       </c>
       <c r="B236" s="55"/>
       <c r="C236" s="55"/>
@@ -10079,18 +10370,18 @@
       <c r="H236" s="55"/>
       <c r="I236" s="57"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A237" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="B237" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="C237" s="55" t="s">
         <v>547</v>
       </c>
-      <c r="B237" s="55" t="s">
-        <v>919</v>
-      </c>
-      <c r="C237" s="55" t="s">
-        <v>548</v>
-      </c>
       <c r="D237" s="55" t="s">
-        <v>920</v>
+        <v>891</v>
       </c>
       <c r="E237" s="55">
         <v>155</v>
@@ -10102,24 +10393,24 @@
         <v>218</v>
       </c>
       <c r="H237" s="55">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I237" s="58" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A238" s="13" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B238" s="55" t="s">
-        <v>921</v>
+        <v>892</v>
       </c>
       <c r="C238" s="55" t="s">
-        <v>922</v>
+        <v>769</v>
       </c>
       <c r="D238" s="55" t="s">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="E238" s="56">
         <v>190</v>
@@ -10134,50 +10425,50 @@
         <v>5.7</v>
       </c>
       <c r="I238" s="57" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A239" s="13" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="C239" s="55" t="s">
-        <v>926</v>
+        <v>896</v>
       </c>
       <c r="D239" s="55" t="s">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="E239" s="56">
         <v>180</v>
       </c>
       <c r="F239" s="40">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G239" s="58">
         <v>220</v>
       </c>
       <c r="H239" s="55">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I239" s="57" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A240" s="13" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="C240" s="55" t="s">
-        <v>928</v>
+        <v>898</v>
       </c>
       <c r="D240" s="55" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
       <c r="E240" s="56">
         <v>190</v>
@@ -10189,24 +10480,24 @@
         <v>225</v>
       </c>
       <c r="H240" s="39">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I240" s="57" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A241" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B241" s="55" t="s">
+        <v>901</v>
+      </c>
+      <c r="C241" s="55" t="s">
+        <v>902</v>
+      </c>
+      <c r="D241" s="15" t="s">
         <v>552</v>
-      </c>
-      <c r="B241" s="55" t="s">
-        <v>930</v>
-      </c>
-      <c r="C241" s="55" t="s">
-        <v>931</v>
-      </c>
-      <c r="D241" s="15" t="s">
-        <v>553</v>
       </c>
       <c r="E241" s="55">
         <v>150</v>
@@ -10221,21 +10512,21 @@
         <v>5.3</v>
       </c>
       <c r="I241" s="58" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A242" s="13" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>933</v>
+        <v>904</v>
       </c>
       <c r="C242" s="55" t="s">
-        <v>934</v>
+        <v>905</v>
       </c>
       <c r="D242" s="55" t="s">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="E242" s="56">
         <v>160</v>
@@ -10247,24 +10538,24 @@
         <v>225</v>
       </c>
       <c r="H242" s="39">
-        <v>4.9000000000000004</v>
+        <v>5.4</v>
       </c>
       <c r="I242" s="57" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A243" s="13" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="C243" s="55" t="s">
-        <v>937</v>
+        <v>908</v>
       </c>
       <c r="D243" s="55" t="s">
-        <v>938</v>
+        <v>909</v>
       </c>
       <c r="E243" s="56">
         <v>190</v>
@@ -10279,21 +10570,21 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="57" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244" s="13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>940</v>
+        <v>911</v>
       </c>
       <c r="C244" s="55" t="s">
-        <v>941</v>
+        <v>912</v>
       </c>
       <c r="D244" s="55" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="E244" s="55">
         <v>150</v>
@@ -10303,13 +10594,13 @@
         <v>220</v>
       </c>
       <c r="H244" s="39">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I244" s="57"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A245" s="13" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B245" s="42"/>
       <c r="C245" s="42"/>
@@ -10320,18 +10611,18 @@
       <c r="H245" s="42"/>
       <c r="I245" s="15"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A246" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B246" s="22" t="s">
-        <v>942</v>
+        <v>914</v>
       </c>
       <c r="C246" s="22" t="s">
-        <v>943</v>
+        <v>915</v>
       </c>
       <c r="D246" s="37" t="s">
-        <v>428</v>
+        <v>916</v>
       </c>
       <c r="E246" s="22">
         <v>112</v>
@@ -10343,22 +10634,22 @@
         <v>215</v>
       </c>
       <c r="H246" s="22">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I246" s="41"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A247" s="35" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B247" s="22" t="s">
-        <v>944</v>
+        <v>917</v>
       </c>
       <c r="C247" s="22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D247" s="37" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E247" s="22">
         <v>135</v>
@@ -10374,18 +10665,18 @@
       </c>
       <c r="I247" s="59"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A248" s="35" t="s">
+        <v>559</v>
+      </c>
+      <c r="B248" s="22" t="s">
+        <v>918</v>
+      </c>
+      <c r="C248" s="22" t="s">
         <v>560</v>
       </c>
-      <c r="B248" s="22" t="s">
-        <v>945</v>
-      </c>
-      <c r="C248" s="22" t="s">
-        <v>561</v>
-      </c>
       <c r="D248" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E248" s="22">
         <v>160</v>
@@ -10397,22 +10688,22 @@
         <v>215</v>
       </c>
       <c r="H248" s="22">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I248" s="12"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A249" s="35" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B249" s="22" t="s">
-        <v>946</v>
+        <v>919</v>
       </c>
       <c r="C249" s="22" t="s">
-        <v>438</v>
+        <v>920</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E249" s="36">
         <v>105</v>
@@ -10428,18 +10719,18 @@
       </c>
       <c r="I249" s="12"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A250" s="35" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B250" s="22" t="s">
-        <v>947</v>
+        <v>921</v>
       </c>
       <c r="C250" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E250" s="36">
         <v>108</v>
@@ -10455,18 +10746,18 @@
       </c>
       <c r="I250" s="36"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A251" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="B251" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="C251" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="B251" s="22" t="s">
-        <v>948</v>
-      </c>
-      <c r="C251" s="22" t="s">
-        <v>565</v>
-      </c>
       <c r="D251" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E251" s="22">
         <v>116</v>
@@ -10478,22 +10769,22 @@
         <v>215</v>
       </c>
       <c r="H251" s="22">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I251" s="36"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A252" s="35" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B252" s="22" t="s">
-        <v>949</v>
+        <v>923</v>
       </c>
       <c r="C252" s="22" t="s">
-        <v>438</v>
+        <v>924</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E252" s="22">
         <v>105</v>
@@ -10509,18 +10800,18 @@
       </c>
       <c r="I252" s="36"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A253" s="35" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="C253" s="22" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E253" s="22">
         <v>116</v>
@@ -10536,18 +10827,18 @@
       </c>
       <c r="I253" s="36"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A254" s="35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B254" s="22" t="s">
-        <v>951</v>
+        <v>926</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>952</v>
+        <v>927</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>914</v>
+        <v>885</v>
       </c>
       <c r="E254" s="22">
         <v>190</v>
@@ -10559,24 +10850,24 @@
         <v>215</v>
       </c>
       <c r="H254" s="22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I254" s="57" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A255" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="B255" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="C255" s="22" t="s">
         <v>569</v>
       </c>
-      <c r="B255" s="22" t="s">
-        <v>953</v>
-      </c>
-      <c r="C255" s="22" t="s">
-        <v>570</v>
-      </c>
       <c r="D255" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E255" s="61">
         <v>88</v>
@@ -10588,22 +10879,22 @@
         <v>208</v>
       </c>
       <c r="H255" s="61">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I255" s="57"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A256" s="13" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B256" s="56" t="s">
-        <v>954</v>
+        <v>929</v>
       </c>
       <c r="C256" s="22" t="s">
-        <v>161</v>
+        <v>930</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
       <c r="E256" s="56">
         <v>190</v>
@@ -10615,24 +10906,24 @@
         <v>215</v>
       </c>
       <c r="H256" s="10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I256" s="57" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A257" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B257" s="40" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
       <c r="C257" s="40" t="s">
-        <v>321</v>
+        <v>934</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>428</v>
+        <v>935</v>
       </c>
       <c r="E257" s="40">
         <v>118</v>
@@ -10644,22 +10935,22 @@
         <v>215</v>
       </c>
       <c r="H257" s="10">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I257" s="10"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258" s="13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B258" s="22" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="C258" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E258" s="36">
         <v>108</v>
@@ -10675,9 +10966,9 @@
       </c>
       <c r="I258" s="10"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A259" s="13" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B259" s="40"/>
       <c r="C259" s="40"/>
@@ -10688,9 +10979,9 @@
       <c r="H259" s="10"/>
       <c r="I259" s="10"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A260" s="13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B260" s="40"/>
       <c r="C260" s="40"/>
@@ -10701,18 +10992,18 @@
       <c r="H260" s="10"/>
       <c r="I260" s="10"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A261" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="B261" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="B261" s="14" t="s">
+      <c r="C261" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="C261" s="14" t="s">
-        <v>578</v>
-      </c>
       <c r="D261" s="53" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="E261" s="14">
         <v>108</v>
@@ -10724,22 +11015,22 @@
         <v>210</v>
       </c>
       <c r="H261" s="14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I261" s="10"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A262" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="B262" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C262" s="14" t="s">
         <v>579</v>
       </c>
-      <c r="B262" s="14" t="s">
-        <v>959</v>
-      </c>
-      <c r="C262" s="14" t="s">
+      <c r="D262" s="53" t="s">
         <v>580</v>
-      </c>
-      <c r="D262" s="53" t="s">
-        <v>581</v>
       </c>
       <c r="E262" s="14">
         <v>87</v>
@@ -10755,18 +11046,18 @@
       </c>
       <c r="I262" s="10"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A263" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="B263" s="31" t="s">
         <v>582</v>
       </c>
-      <c r="B263" s="31" t="s">
+      <c r="C263" s="31" t="s">
         <v>583</v>
       </c>
-      <c r="C263" s="31" t="s">
+      <c r="D263" s="31" t="s">
         <v>584</v>
-      </c>
-      <c r="D263" s="31" t="s">
-        <v>585</v>
       </c>
       <c r="E263" s="31">
         <v>115</v>
@@ -10782,18 +11073,18 @@
       </c>
       <c r="I263" s="10"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A264" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="B264" s="14" t="s">
         <v>586</v>
       </c>
-      <c r="B264" s="14" t="s">
+      <c r="C264" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="C264" s="14" t="s">
+      <c r="D264" s="14" t="s">
         <v>588</v>
-      </c>
-      <c r="D264" s="14" t="s">
-        <v>589</v>
       </c>
       <c r="E264" s="14">
         <v>70</v>
@@ -10809,18 +11100,18 @@
       </c>
       <c r="I264" s="10"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="B265" s="39" t="s">
         <v>590</v>
       </c>
-      <c r="B265" s="39" t="s">
+      <c r="C265" s="39" t="s">
         <v>591</v>
       </c>
-      <c r="C265" s="39" t="s">
+      <c r="D265" s="39" t="s">
         <v>592</v>
-      </c>
-      <c r="D265" s="39" t="s">
-        <v>593</v>
       </c>
       <c r="E265" s="39">
         <v>102</v>
@@ -10836,18 +11127,18 @@
       </c>
       <c r="I265" s="10"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266" s="13" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B266" s="39" t="s">
-        <v>960</v>
+        <v>939</v>
       </c>
       <c r="C266" s="39" t="s">
-        <v>941</v>
+        <v>912</v>
       </c>
       <c r="D266" s="39" t="s">
-        <v>961</v>
+        <v>940</v>
       </c>
       <c r="E266" s="39">
         <v>78</v>
@@ -10859,22 +11150,22 @@
         <v>215</v>
       </c>
       <c r="H266" s="39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I266" s="10"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>962</v>
+        <v>941</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>963</v>
+        <v>942</v>
       </c>
       <c r="D267" s="53" t="s">
-        <v>144</v>
+        <v>943</v>
       </c>
       <c r="E267" s="14">
         <v>60</v>
@@ -10886,13 +11177,13 @@
         <v>220</v>
       </c>
       <c r="H267" s="14">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I267" s="9"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B268" s="40"/>
       <c r="C268" s="40"/>
@@ -10903,9 +11194,9 @@
       <c r="H268" s="10"/>
       <c r="I268" s="10"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269" s="13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B269" s="40"/>
       <c r="C269" s="40"/>
@@ -10916,9 +11207,9 @@
       <c r="H269" s="10"/>
       <c r="I269" s="10"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A270" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B270" s="40"/>
       <c r="C270" s="40"/>
@@ -10929,9 +11220,9 @@
       <c r="H270" s="10"/>
       <c r="I270" s="10"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A271" s="13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B271" s="40"/>
       <c r="C271" s="40"/>
@@ -10942,9 +11233,9 @@
       <c r="H271" s="10"/>
       <c r="I271" s="10"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A272" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B272" s="40"/>
       <c r="C272" s="40"/>
@@ -10955,9 +11246,9 @@
       <c r="H272" s="10"/>
       <c r="I272" s="10"/>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A273" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B273" s="40"/>
       <c r="C273" s="40"/>
@@ -10968,9 +11259,9 @@
       <c r="H273" s="10"/>
       <c r="I273" s="10"/>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A274" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B274" s="40"/>
       <c r="C274" s="40"/>
@@ -10981,9 +11272,9 @@
       <c r="H274" s="10"/>
       <c r="I274" s="10"/>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B275" s="40"/>
       <c r="C275" s="40"/>
@@ -10994,9 +11285,9 @@
       <c r="H275" s="10"/>
       <c r="I275" s="10"/>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B276" s="40"/>
       <c r="C276" s="40"/>
@@ -11007,18 +11298,18 @@
       <c r="H276" s="10"/>
       <c r="I276" s="10"/>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="B277" s="56" t="s">
         <v>605</v>
       </c>
-      <c r="B277" s="56" t="s">
+      <c r="C277" s="56" t="s">
         <v>606</v>
       </c>
-      <c r="C277" s="56" t="s">
+      <c r="D277" s="56" t="s">
         <v>607</v>
-      </c>
-      <c r="D277" s="56" t="s">
-        <v>608</v>
       </c>
       <c r="E277" s="56">
         <v>105</v>
@@ -11034,18 +11325,18 @@
       </c>
       <c r="I277" s="10"/>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B278" s="31" t="s">
+        <v>944</v>
+      </c>
+      <c r="C278" s="31" t="s">
+        <v>770</v>
+      </c>
+      <c r="D278" s="31" t="s">
         <v>771</v>
-      </c>
-      <c r="C278" s="31" t="s">
-        <v>772</v>
-      </c>
-      <c r="D278" s="31" t="s">
-        <v>773</v>
       </c>
       <c r="E278" s="31">
         <v>159</v>
@@ -11061,18 +11352,18 @@
       </c>
       <c r="I278" s="10"/>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A279" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>774</v>
+        <v>945</v>
       </c>
       <c r="C279" s="53" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D279" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E279" s="14">
         <v>50</v>
@@ -11088,18 +11379,18 @@
       </c>
       <c r="I279" s="10"/>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>776</v>
+        <v>946</v>
       </c>
       <c r="C280" s="53" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="D280" s="14" t="s">
-        <v>778</v>
+        <v>947</v>
       </c>
       <c r="E280" s="14"/>
       <c r="F280" s="13">
@@ -11113,18 +11404,18 @@
       </c>
       <c r="I280" s="10"/>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A281" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="B281" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="B281" s="14" t="s">
+      <c r="C281" s="53" t="s">
         <v>613</v>
       </c>
-      <c r="C281" s="53" t="s">
-        <v>614</v>
-      </c>
       <c r="D281" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E281" s="14">
         <v>55</v>
@@ -11136,19 +11427,19 @@
         <v>222</v>
       </c>
       <c r="H281" s="14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I281" s="10"/>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282" s="13" t="s">
+        <v>614</v>
+      </c>
+      <c r="B282" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="C282" s="53" t="s">
         <v>615</v>
-      </c>
-      <c r="B282" s="14" t="s">
-        <v>779</v>
-      </c>
-      <c r="C282" s="53" t="s">
-        <v>616</v>
       </c>
       <c r="D282" s="14" t="s">
         <v>39</v>
@@ -11167,15 +11458,15 @@
       </c>
       <c r="I282" s="10"/>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A283" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="C283" s="53" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="D283" s="14" t="s">
         <v>39</v>
@@ -11194,18 +11485,18 @@
       </c>
       <c r="I283" s="10"/>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A284" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B284" s="31" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C284" s="40" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="E284" s="40">
         <v>80</v>
@@ -11217,22 +11508,22 @@
         <v>208</v>
       </c>
       <c r="H284" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I284" s="10"/>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A285" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="14" t="s">
+      <c r="C285" s="53" t="s">
         <v>620</v>
       </c>
-      <c r="C285" s="53" t="s">
-        <v>621</v>
-      </c>
       <c r="D285" s="40" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="E285" s="14">
         <v>73</v>
@@ -11248,18 +11539,18 @@
       </c>
       <c r="I285" s="10"/>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A286" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="B286" s="56" t="s">
+        <v>948</v>
+      </c>
+      <c r="C286" s="56" t="s">
+        <v>780</v>
+      </c>
+      <c r="D286" s="56" t="s">
         <v>622</v>
-      </c>
-      <c r="B286" s="56" t="s">
-        <v>785</v>
-      </c>
-      <c r="C286" s="56" t="s">
-        <v>786</v>
-      </c>
-      <c r="D286" s="56" t="s">
-        <v>623</v>
       </c>
       <c r="E286" s="56">
         <v>85</v>
@@ -11275,18 +11566,18 @@
       </c>
       <c r="I286" s="10"/>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A287" s="13" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B287" s="56" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C287" s="56" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="D287" s="56" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="E287" s="56">
         <v>88</v>
@@ -11302,15 +11593,15 @@
       </c>
       <c r="I287" s="9"/>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A288" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="31" t="s">
+        <v>784</v>
+      </c>
+      <c r="C288" s="31" t="s">
         <v>625</v>
-      </c>
-      <c r="B288" s="31" t="s">
-        <v>790</v>
-      </c>
-      <c r="C288" s="31" t="s">
-        <v>626</v>
       </c>
       <c r="D288" s="54" t="s">
         <v>1</v>
@@ -11329,18 +11620,18 @@
       </c>
       <c r="I288" s="9"/>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A289" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="B289" s="14" t="s">
         <v>627</v>
       </c>
-      <c r="B289" s="14" t="s">
+      <c r="C289" s="14" t="s">
         <v>628</v>
       </c>
-      <c r="C289" s="14" t="s">
+      <c r="D289" s="53" t="s">
         <v>629</v>
-      </c>
-      <c r="D289" s="53" t="s">
-        <v>630</v>
       </c>
       <c r="E289" s="14">
         <v>135</v>
@@ -11352,21 +11643,21 @@
         <v>215</v>
       </c>
       <c r="H289" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I289" s="15" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A290" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="B290" s="28" t="s">
         <v>631</v>
       </c>
-      <c r="B290" s="28" t="s">
+      <c r="C290" s="28" t="s">
         <v>632</v>
-      </c>
-      <c r="C290" s="28" t="s">
-        <v>633</v>
       </c>
       <c r="D290" s="63" t="s">
         <v>39</v>
@@ -11385,18 +11676,18 @@
       </c>
       <c r="I290" s="9"/>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A291" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="B291" s="64" t="s">
+        <v>950</v>
+      </c>
+      <c r="C291" s="64" t="s">
+        <v>951</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>634</v>
-      </c>
-      <c r="B291" s="64" t="s">
-        <v>792</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>793</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>635</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -11412,18 +11703,18 @@
       </c>
       <c r="I291" s="9"/>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A292" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>785</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>636</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>794</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>637</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>638</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -11439,15 +11730,15 @@
       </c>
       <c r="I292" s="9"/>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A293" s="13" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11466,18 +11757,18 @@
       </c>
       <c r="I293" s="9"/>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A294" s="13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B294" s="22" t="s">
-        <v>797</v>
+        <v>952</v>
       </c>
       <c r="C294" s="22" t="s">
-        <v>769</v>
+        <v>953</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>798</v>
+        <v>954</v>
       </c>
       <c r="E294" s="22">
         <v>150</v>
@@ -11493,18 +11784,18 @@
       </c>
       <c r="I294" s="9"/>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A295" s="13" t="s">
+        <v>640</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>788</v>
+      </c>
+      <c r="C295" s="14" t="s">
         <v>641</v>
       </c>
-      <c r="B295" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="C295" s="14" t="s">
+      <c r="D295" s="14" t="s">
         <v>642</v>
-      </c>
-      <c r="D295" s="14" t="s">
-        <v>643</v>
       </c>
       <c r="E295" s="14"/>
       <c r="F295" s="13"/>
@@ -11516,18 +11807,18 @@
       </c>
       <c r="I295" s="9"/>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A296" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="B296" s="39" t="s">
         <v>644</v>
       </c>
-      <c r="B296" s="39" t="s">
+      <c r="C296" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="C296" s="39" t="s">
+      <c r="D296" s="39" t="s">
         <v>646</v>
-      </c>
-      <c r="D296" s="39" t="s">
-        <v>647</v>
       </c>
       <c r="E296" s="39"/>
       <c r="F296" s="40">
@@ -11541,18 +11832,18 @@
       </c>
       <c r="I296" s="9"/>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A297" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B297" s="22" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C297" s="22" t="s">
-        <v>801</v>
+        <v>955</v>
       </c>
       <c r="D297" s="37" t="s">
-        <v>802</v>
+        <v>956</v>
       </c>
       <c r="E297" s="22">
         <v>125</v>
@@ -11564,22 +11855,22 @@
         <v>215</v>
       </c>
       <c r="H297" s="22">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I297" s="57"/>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A298" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B298" s="22" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="C298" s="22" t="s">
-        <v>804</v>
+        <v>957</v>
       </c>
       <c r="D298" s="37" t="s">
-        <v>805</v>
+        <v>958</v>
       </c>
       <c r="E298" s="22">
         <v>190</v>
@@ -11591,24 +11882,24 @@
         <v>225</v>
       </c>
       <c r="H298" s="22">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I298" s="15" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A299" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B299" s="55" t="s">
-        <v>807</v>
+        <v>959</v>
       </c>
       <c r="C299" s="55" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="D299" s="55" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="E299" s="55">
         <v>124</v>
@@ -11620,15 +11911,15 @@
         <v>218</v>
       </c>
       <c r="H299" s="55">
-        <v>4.5999999999999996</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I299" s="58" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A300" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B300" s="40"/>
       <c r="C300" s="40"/>
@@ -11639,9 +11930,9 @@
       <c r="H300" s="9"/>
       <c r="I300" s="9"/>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A301" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B301" s="40"/>
       <c r="C301" s="40"/>
@@ -11652,18 +11943,18 @@
       <c r="H301" s="9"/>
       <c r="I301" s="9"/>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A302" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B302" s="15" t="s">
-        <v>811</v>
+        <v>961</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>812</v>
+        <v>962</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="E302" s="15">
         <v>150</v>
@@ -11675,22 +11966,22 @@
         <v>215</v>
       </c>
       <c r="H302" s="15">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I302" s="9"/>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A303" s="13" t="s">
+        <v>653</v>
+      </c>
+      <c r="B303" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="B303" s="14" t="s">
+      <c r="C303" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="C303" s="14" t="s">
-        <v>656</v>
-      </c>
       <c r="D303" s="14" t="s">
-        <v>813</v>
+        <v>963</v>
       </c>
       <c r="E303" s="15">
         <v>140</v>
@@ -11702,22 +11993,22 @@
         <v>215</v>
       </c>
       <c r="H303" s="14">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I303" s="9"/>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A304" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>657</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>964</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>658</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>814</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>659</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11732,21 +12023,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="41" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A305" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B305" s="40" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="C305" s="40" t="s">
-        <v>817</v>
+        <v>965</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="E305" s="40">
         <v>215</v>
@@ -11758,13 +12049,13 @@
         <v>225</v>
       </c>
       <c r="H305" s="9">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I305" s="9"/>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A306" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B306" s="40"/>
       <c r="C306" s="40"/>
@@ -11775,9 +12066,9 @@
       <c r="H306" s="9"/>
       <c r="I306" s="9"/>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A307" s="13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B307" s="40"/>
       <c r="C307" s="40"/>
@@ -11788,9 +12079,9 @@
       <c r="H307" s="9"/>
       <c r="I307" s="9"/>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A308" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B308" s="40"/>
       <c r="C308" s="40"/>
@@ -11801,9 +12092,9 @@
       <c r="H308" s="9"/>
       <c r="I308" s="9"/>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A309" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B309" s="40"/>
       <c r="C309" s="40"/>
@@ -11814,9 +12105,9 @@
       <c r="H309" s="9"/>
       <c r="I309" s="9"/>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A310" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B310" s="40"/>
       <c r="C310" s="40"/>
@@ -11827,18 +12118,18 @@
       <c r="H310" s="9"/>
       <c r="I310" s="9"/>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A311" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="B311" s="39" t="s">
         <v>666</v>
       </c>
-      <c r="B311" s="39" t="s">
-        <v>667</v>
-      </c>
       <c r="C311" s="39" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="D311" s="39" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E311" s="39">
         <v>85</v>
@@ -11854,18 +12145,18 @@
       </c>
       <c r="I311" s="9"/>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A312" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="14" t="s">
+      <c r="C312" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="D312" s="14" t="s">
         <v>671</v>
-      </c>
-      <c r="C312" s="14" t="s">
-        <v>668</v>
-      </c>
-      <c r="D312" s="14" t="s">
-        <v>672</v>
       </c>
       <c r="E312" s="14">
         <v>73</v>
@@ -11881,9 +12172,9 @@
       </c>
       <c r="I312" s="9"/>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A313" s="13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B313" s="40"/>
       <c r="C313" s="40"/>
@@ -11894,9 +12185,9 @@
       <c r="H313" s="9"/>
       <c r="I313" s="9"/>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A314" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B314" s="40"/>
       <c r="C314" s="40"/>
@@ -11907,18 +12198,18 @@
       <c r="H314" s="9"/>
       <c r="I314" s="9"/>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A315" s="13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B315" s="40" t="s">
-        <v>820</v>
+        <v>966</v>
       </c>
       <c r="C315" s="40" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>821</v>
+        <v>967</v>
       </c>
       <c r="E315" s="40">
         <v>116</v>
@@ -11933,21 +12224,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="9" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A316" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B316" s="40" t="s">
-        <v>823</v>
+        <v>968</v>
       </c>
       <c r="C316" s="40" t="s">
-        <v>824</v>
+        <v>969</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>825</v>
+        <v>801</v>
       </c>
       <c r="E316" s="40">
         <v>160</v>
@@ -11962,21 +12253,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A317" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>827</v>
+        <v>971</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>828</v>
+        <v>972</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>829</v>
+        <v>802</v>
       </c>
       <c r="E317" s="15">
         <v>110</v>
@@ -11991,21 +12282,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="15" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A318" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>827</v>
+        <v>973</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>831</v>
+        <v>974</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>829</v>
+        <v>802</v>
       </c>
       <c r="E318" s="15">
         <v>110</v>
@@ -12021,47 +12312,47 @@
       </c>
       <c r="I318" s="15"/>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A319" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B319" s="22" t="s">
-        <v>832</v>
+        <v>975</v>
       </c>
       <c r="C319" s="22" t="s">
-        <v>833</v>
+        <v>791</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>834</v>
+        <v>804</v>
       </c>
       <c r="E319" s="22">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="F319" s="35">
         <v>270</v>
       </c>
       <c r="G319" s="36">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="H319" s="22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I319" s="15" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A320" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B320" s="22" t="s">
-        <v>836</v>
+        <v>977</v>
       </c>
       <c r="C320" s="22" t="s">
-        <v>837</v>
+        <v>978</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>838</v>
+        <v>979</v>
       </c>
       <c r="E320" s="22">
         <v>182</v>
@@ -12073,24 +12364,24 @@
         <v>220</v>
       </c>
       <c r="H320" s="22">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I320" s="15" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A321" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B321" s="22" t="s">
-        <v>839</v>
+        <v>805</v>
       </c>
       <c r="C321" s="22" t="s">
-        <v>840</v>
+        <v>980</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>841</v>
+        <v>981</v>
       </c>
       <c r="E321" s="22">
         <v>138</v>
@@ -12102,24 +12393,24 @@
         <v>220</v>
       </c>
       <c r="H321" s="22">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="I321" s="15" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A322" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B322" s="22" t="s">
-        <v>843</v>
+        <v>983</v>
       </c>
       <c r="C322" s="22" t="s">
-        <v>844</v>
+        <v>984</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>834</v>
+        <v>804</v>
       </c>
       <c r="E322" s="22">
         <v>225</v>
@@ -12134,50 +12425,50 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="15" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A323" s="13" t="s">
+        <v>682</v>
+      </c>
+      <c r="B323" s="22" t="s">
+        <v>986</v>
+      </c>
+      <c r="C323" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="D323" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="E323" s="22">
+        <v>150</v>
+      </c>
+      <c r="F323" s="35">
+        <v>230</v>
+      </c>
+      <c r="G323" s="36">
+        <v>220</v>
+      </c>
+      <c r="H323" s="22">
+        <v>4.7</v>
+      </c>
+      <c r="I323" s="15" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A324" s="13" t="s">
         <v>683</v>
       </c>
-      <c r="B323" s="22" t="s">
-        <v>846</v>
-      </c>
-      <c r="C323" s="22" t="s">
-        <v>847</v>
-      </c>
-      <c r="D323" s="22" t="s">
-        <v>841</v>
-      </c>
-      <c r="E323" s="22">
-        <v>155</v>
-      </c>
-      <c r="F323" s="35">
-        <v>235</v>
-      </c>
-      <c r="G323" s="36">
-        <v>215</v>
-      </c>
-      <c r="H323" s="22">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I323" s="15" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9">
-      <c r="A324" s="13" t="s">
-        <v>684</v>
-      </c>
       <c r="B324" s="22" t="s">
-        <v>849</v>
+        <v>806</v>
       </c>
       <c r="C324" s="22" t="s">
-        <v>850</v>
+        <v>807</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>834</v>
+        <v>989</v>
       </c>
       <c r="E324" s="22">
         <v>220</v>
@@ -12189,54 +12480,98 @@
         <v>218</v>
       </c>
       <c r="H324" s="22">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I324" s="15" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A325" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B325" s="40"/>
-      <c r="C325" s="40"/>
-      <c r="D325" s="40"/>
-      <c r="E325" s="40"/>
-      <c r="F325" s="40"/>
-      <c r="G325" s="40"/>
-      <c r="H325" s="9"/>
-      <c r="I325" s="9"/>
-    </row>
-    <row r="326" spans="1:9">
+        <v>684</v>
+      </c>
+      <c r="B325" s="22" t="s">
+        <v>991</v>
+      </c>
+      <c r="C325" s="22" t="s">
+        <v>957</v>
+      </c>
+      <c r="D325" s="22" t="s">
+        <v>992</v>
+      </c>
+      <c r="E325" s="22">
+        <v>185</v>
+      </c>
+      <c r="F325" s="35">
+        <v>270</v>
+      </c>
+      <c r="G325" s="36">
+        <v>225</v>
+      </c>
+      <c r="H325" s="22">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I325" s="15" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A326" s="13" t="s">
+        <v>700</v>
+      </c>
+      <c r="B326" s="40" t="s">
+        <v>993</v>
+      </c>
+      <c r="C326" s="40" t="s">
+        <v>994</v>
+      </c>
+      <c r="D326" s="40" t="s">
+        <v>995</v>
+      </c>
+      <c r="E326" s="40">
+        <v>145</v>
+      </c>
+      <c r="F326" s="40"/>
+      <c r="G326" s="40">
+        <v>220</v>
+      </c>
+      <c r="H326" s="9">
+        <v>5.7</v>
+      </c>
+      <c r="I326" s="9" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A327" s="13" t="s">
         <v>701</v>
       </c>
-      <c r="B326" s="40"/>
-      <c r="C326" s="40"/>
-      <c r="D326" s="40"/>
-      <c r="E326" s="40"/>
-      <c r="F326" s="40"/>
-      <c r="G326" s="40"/>
-      <c r="H326" s="9"/>
-      <c r="I326" s="9"/>
-    </row>
-    <row r="327" spans="1:9">
-      <c r="A327" s="13" t="s">
+      <c r="B327" s="40" t="s">
+        <v>997</v>
+      </c>
+      <c r="C327" s="40" t="s">
+        <v>998</v>
+      </c>
+      <c r="D327" s="40" t="s">
+        <v>999</v>
+      </c>
+      <c r="E327" s="40">
+        <v>150</v>
+      </c>
+      <c r="F327" s="40">
+        <v>225</v>
+      </c>
+      <c r="G327" s="40">
+        <v>208</v>
+      </c>
+      <c r="H327" s="9">
+        <v>5</v>
+      </c>
+      <c r="I327" s="9"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A328" s="13" t="s">
         <v>702</v>
-      </c>
-      <c r="B327" s="40"/>
-      <c r="C327" s="40"/>
-      <c r="D327" s="40"/>
-      <c r="E327" s="40"/>
-      <c r="F327" s="40"/>
-      <c r="G327" s="40"/>
-      <c r="H327" s="9"/>
-      <c r="I327" s="9"/>
-    </row>
-    <row r="328" spans="1:9">
-      <c r="A328" s="13" t="s">
-        <v>703</v>
       </c>
       <c r="B328" s="40"/>
       <c r="C328" s="40"/>
@@ -12247,9 +12582,9 @@
       <c r="H328" s="9"/>
       <c r="I328" s="9"/>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A329" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B329" s="40"/>
       <c r="C329" s="40"/>
@@ -12260,9 +12595,9 @@
       <c r="H329" s="9"/>
       <c r="I329" s="9"/>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A330" s="13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B330" s="40"/>
       <c r="C330" s="40"/>
@@ -12273,9 +12608,9 @@
       <c r="H330" s="9"/>
       <c r="I330" s="9"/>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A331" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B331" s="40"/>
       <c r="C331" s="40"/>
@@ -12286,9 +12621,9 @@
       <c r="H331" s="9"/>
       <c r="I331" s="9"/>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A332" s="13" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B332" s="40"/>
       <c r="C332" s="40"/>
@@ -12299,9 +12634,9 @@
       <c r="H332" s="9"/>
       <c r="I332" s="9"/>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A333" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B333" s="40"/>
       <c r="C333" s="40"/>
@@ -12312,9 +12647,9 @@
       <c r="H333" s="9"/>
       <c r="I333" s="9"/>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A334" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B334" s="40"/>
       <c r="C334" s="40"/>
@@ -12325,9 +12660,9 @@
       <c r="H334" s="9"/>
       <c r="I334" s="9"/>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A335" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B335" s="40"/>
       <c r="C335" s="40"/>
@@ -12338,9 +12673,9 @@
       <c r="H335" s="9"/>
       <c r="I335" s="9"/>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A336" s="13" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B336" s="40"/>
       <c r="C336" s="40"/>
@@ -12351,9 +12686,9 @@
       <c r="H336" s="9"/>
       <c r="I336" s="9"/>
     </row>
-    <row r="337" spans="1:9">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A337" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B337" s="40"/>
       <c r="C337" s="40"/>
@@ -12364,9 +12699,9 @@
       <c r="H337" s="9"/>
       <c r="I337" s="9"/>
     </row>
-    <row r="338" spans="1:9">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A338" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B338" s="40"/>
       <c r="C338" s="40"/>
@@ -12377,9 +12712,9 @@
       <c r="H338" s="9"/>
       <c r="I338" s="9"/>
     </row>
-    <row r="339" spans="1:9">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A339" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B339" s="40"/>
       <c r="C339" s="40"/>
@@ -12390,9 +12725,9 @@
       <c r="H339" s="9"/>
       <c r="I339" s="9"/>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A340" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B340" s="40"/>
       <c r="C340" s="40"/>
@@ -12403,9 +12738,9 @@
       <c r="H340" s="9"/>
       <c r="I340" s="9"/>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A341" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B341" s="40"/>
       <c r="C341" s="40"/>
@@ -12416,9 +12751,9 @@
       <c r="H341" s="9"/>
       <c r="I341" s="9"/>
     </row>
-    <row r="342" spans="1:9">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A342" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B342" s="40"/>
       <c r="C342" s="40"/>
@@ -12429,9 +12764,9 @@
       <c r="H342" s="9"/>
       <c r="I342" s="9"/>
     </row>
-    <row r="343" spans="1:9">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A343" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B343" s="40"/>
       <c r="C343" s="40"/>
@@ -12442,9 +12777,9 @@
       <c r="H343" s="9"/>
       <c r="I343" s="9"/>
     </row>
-    <row r="344" spans="1:9">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A344" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B344" s="40"/>
       <c r="C344" s="40"/>
@@ -12455,9 +12790,9 @@
       <c r="H344" s="9"/>
       <c r="I344" s="9"/>
     </row>
-    <row r="345" spans="1:9">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A345" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B345" s="40"/>
       <c r="C345" s="40"/>
@@ -12468,9 +12803,9 @@
       <c r="H345" s="9"/>
       <c r="I345" s="9"/>
     </row>
-    <row r="346" spans="1:9">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A346" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B346" s="40"/>
       <c r="C346" s="40"/>
@@ -12481,9 +12816,9 @@
       <c r="H346" s="9"/>
       <c r="I346" s="9"/>
     </row>
-    <row r="347" spans="1:9">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A347" s="13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B347" s="40"/>
       <c r="C347" s="40"/>
@@ -12494,9 +12829,9 @@
       <c r="H347" s="9"/>
       <c r="I347" s="9"/>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A348" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B348" s="40"/>
       <c r="C348" s="40"/>
@@ -12507,9 +12842,9 @@
       <c r="H348" s="9"/>
       <c r="I348" s="9"/>
     </row>
-    <row r="349" spans="1:9">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A349" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B349" s="40"/>
       <c r="C349" s="40"/>
@@ -12520,9 +12855,9 @@
       <c r="H349" s="9"/>
       <c r="I349" s="9"/>
     </row>
-    <row r="350" spans="1:9">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A350" s="13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B350" s="40"/>
       <c r="C350" s="40"/>
@@ -12533,9 +12868,9 @@
       <c r="H350" s="9"/>
       <c r="I350" s="9"/>
     </row>
-    <row r="351" spans="1:9">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A351" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B351" s="40"/>
       <c r="C351" s="40"/>
@@ -12546,9 +12881,9 @@
       <c r="H351" s="9"/>
       <c r="I351" s="9"/>
     </row>
-    <row r="352" spans="1:9">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A352" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B352" s="40"/>
       <c r="C352" s="40"/>
@@ -12559,9 +12894,9 @@
       <c r="H352" s="9"/>
       <c r="I352" s="9"/>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A353" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B353" s="40"/>
       <c r="C353" s="40"/>
@@ -12572,9 +12907,9 @@
       <c r="H353" s="9"/>
       <c r="I353" s="9"/>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A354" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B354" s="40"/>
       <c r="C354" s="40"/>
@@ -12585,9 +12920,9 @@
       <c r="H354" s="9"/>
       <c r="I354" s="9"/>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A355" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B355" s="40"/>
       <c r="C355" s="40"/>
@@ -12598,9 +12933,9 @@
       <c r="H355" s="9"/>
       <c r="I355" s="9"/>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A356" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B356" s="40"/>
       <c r="C356" s="40"/>
@@ -12611,9 +12946,9 @@
       <c r="H356" s="9"/>
       <c r="I356" s="9"/>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A357" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B357" s="40"/>
       <c r="C357" s="40"/>
@@ -12624,9 +12959,9 @@
       <c r="H357" s="9"/>
       <c r="I357" s="9"/>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A358" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B358" s="40"/>
       <c r="C358" s="40"/>
@@ -12637,9 +12972,9 @@
       <c r="H358" s="9"/>
       <c r="I358" s="9"/>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A359" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B359" s="40"/>
       <c r="C359" s="40"/>
@@ -12650,9 +12985,9 @@
       <c r="H359" s="9"/>
       <c r="I359" s="9"/>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A360" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B360" s="40"/>
       <c r="C360" s="40"/>
@@ -12663,9 +12998,9 @@
       <c r="H360" s="9"/>
       <c r="I360" s="9"/>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A361" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B361" s="40"/>
       <c r="C361" s="40"/>
@@ -12676,9 +13011,9 @@
       <c r="H361" s="9"/>
       <c r="I361" s="9"/>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A362" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B362" s="40"/>
       <c r="C362" s="40"/>
@@ -12689,9 +13024,9 @@
       <c r="H362" s="9"/>
       <c r="I362" s="9"/>
     </row>
-    <row r="363" spans="1:9">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A363" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B363" s="40"/>
       <c r="C363" s="40"/>
@@ -12702,9 +13037,9 @@
       <c r="H363" s="9"/>
       <c r="I363" s="9"/>
     </row>
-    <row r="364" spans="1:9">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A364" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B364" s="40"/>
       <c r="C364" s="40"/>
@@ -12715,9 +13050,9 @@
       <c r="H364" s="9"/>
       <c r="I364" s="9"/>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A365" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B365" s="40"/>
       <c r="C365" s="40"/>
@@ -12728,9 +13063,9 @@
       <c r="H365" s="9"/>
       <c r="I365" s="9"/>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A366" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B366" s="40"/>
       <c r="C366" s="40"/>
@@ -12741,9 +13076,9 @@
       <c r="H366" s="9"/>
       <c r="I366" s="9"/>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A367" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B367" s="40"/>
       <c r="C367" s="40"/>
@@ -12754,9 +13089,9 @@
       <c r="H367" s="9"/>
       <c r="I367" s="9"/>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A368" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B368" s="40"/>
       <c r="C368" s="40"/>
@@ -12767,9 +13102,9 @@
       <c r="H368" s="9"/>
       <c r="I368" s="9"/>
     </row>
-    <row r="369" spans="1:9">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A369" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B369" s="40"/>
       <c r="C369" s="40"/>
@@ -12780,9 +13115,9 @@
       <c r="H369" s="9"/>
       <c r="I369" s="9"/>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A370" s="13" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B370" s="40"/>
       <c r="C370" s="40"/>
@@ -12793,9 +13128,9 @@
       <c r="H370" s="9"/>
       <c r="I370" s="9"/>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A371" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B371" s="40"/>
       <c r="C371" s="40"/>
@@ -12806,9 +13141,9 @@
       <c r="H371" s="9"/>
       <c r="I371" s="9"/>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A372" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B372" s="40"/>
       <c r="C372" s="40"/>
@@ -12819,9 +13154,9 @@
       <c r="H372" s="9"/>
       <c r="I372" s="9"/>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A373" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B373" s="40"/>
       <c r="C373" s="40"/>
@@ -12832,9 +13167,9 @@
       <c r="H373" s="9"/>
       <c r="I373" s="9"/>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A374" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B374" s="40"/>
       <c r="C374" s="40"/>
@@ -12845,9 +13180,9 @@
       <c r="H374" s="9"/>
       <c r="I374" s="9"/>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A375" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B375" s="40"/>
       <c r="C375" s="40"/>
@@ -12858,9 +13193,9 @@
       <c r="H375" s="9"/>
       <c r="I375" s="9"/>
     </row>
-    <row r="376" spans="1:9">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A376" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B376" s="40"/>
       <c r="C376" s="40"/>
@@ -12871,9 +13206,9 @@
       <c r="H376" s="9"/>
       <c r="I376" s="9"/>
     </row>
-    <row r="377" spans="1:9">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A377" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B377" s="40"/>
       <c r="C377" s="40"/>
@@ -12884,9 +13219,9 @@
       <c r="H377" s="9"/>
       <c r="I377" s="9"/>
     </row>
-    <row r="378" spans="1:9">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A378" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B378" s="40"/>
       <c r="C378" s="40"/>
@@ -12897,9 +13232,9 @@
       <c r="H378" s="9"/>
       <c r="I378" s="9"/>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A379" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B379" s="40"/>
       <c r="C379" s="40"/>
@@ -12910,9 +13245,9 @@
       <c r="H379" s="9"/>
       <c r="I379" s="9"/>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A380" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B380" s="40"/>
       <c r="C380" s="40"/>
@@ -12923,9 +13258,9 @@
       <c r="H380" s="9"/>
       <c r="I380" s="9"/>
     </row>
-    <row r="381" spans="1:9">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A381" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B381" s="40"/>
       <c r="C381" s="40"/>
@@ -12936,9 +13271,9 @@
       <c r="H381" s="9"/>
       <c r="I381" s="9"/>
     </row>
-    <row r="382" spans="1:9">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A382" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B382" s="40"/>
       <c r="C382" s="40"/>
@@ -12949,9 +13284,9 @@
       <c r="H382" s="9"/>
       <c r="I382" s="9"/>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A383" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B383" s="40"/>
       <c r="C383" s="40"/>
@@ -12962,9 +13297,9 @@
       <c r="H383" s="9"/>
       <c r="I383" s="9"/>
     </row>
-    <row r="384" spans="1:9">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A384" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B384" s="40"/>
       <c r="C384" s="40"/>
@@ -12975,9 +13310,9 @@
       <c r="H384" s="9"/>
       <c r="I384" s="9"/>
     </row>
-    <row r="385" spans="1:9">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A385" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B385" s="40"/>
       <c r="C385" s="40"/>
@@ -12988,9 +13323,9 @@
       <c r="H385" s="9"/>
       <c r="I385" s="9"/>
     </row>
-    <row r="386" spans="1:9">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A386" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B386" s="40"/>
       <c r="C386" s="40"/>
@@ -13001,9 +13336,9 @@
       <c r="H386" s="9"/>
       <c r="I386" s="9"/>
     </row>
-    <row r="387" spans="1:9">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A387" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B387" s="40"/>
       <c r="C387" s="40"/>
@@ -13014,9 +13349,9 @@
       <c r="H387" s="9"/>
       <c r="I387" s="9"/>
     </row>
-    <row r="388" spans="1:9">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A388" s="13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B388" s="40"/>
       <c r="C388" s="40"/>
@@ -13027,9 +13362,9 @@
       <c r="H388" s="9"/>
       <c r="I388" s="9"/>
     </row>
-    <row r="389" spans="1:9">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A389" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B389" s="40"/>
       <c r="C389" s="40"/>
@@ -13040,9 +13375,9 @@
       <c r="H389" s="9"/>
       <c r="I389" s="9"/>
     </row>
-    <row r="390" spans="1:9">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A390" s="13" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B390" s="40"/>
       <c r="C390" s="40"/>
@@ -13053,9 +13388,9 @@
       <c r="H390" s="9"/>
       <c r="I390" s="9"/>
     </row>
-    <row r="391" spans="1:9">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A391" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B391" s="40"/>
       <c r="C391" s="40"/>
@@ -13066,9 +13401,9 @@
       <c r="H391" s="9"/>
       <c r="I391" s="9"/>
     </row>
-    <row r="392" spans="1:9">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A392" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B392" s="40"/>
       <c r="C392" s="40"/>
@@ -13079,9 +13414,9 @@
       <c r="H392" s="9"/>
       <c r="I392" s="9"/>
     </row>
-    <row r="393" spans="1:9">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A393" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B393" s="40"/>
       <c r="C393" s="40"/>
@@ -13100,9 +13435,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13110,9 +13445,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
